--- a/Treinamentos Normativos.xlsx
+++ b/Treinamentos Normativos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://inpasabr-my.sharepoint.com/personal/gabriel_oliveira_inpasa_com_br/Documents/Área de Trabalho/CarteirinhaTreinamentos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="814" documentId="8_{FF07DBE4-2E43-45A4-A665-4C1273F6EE3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E03E6C9E-0217-4FDA-BBE6-B057DBF7E02D}"/>
+  <xr:revisionPtr revIDLastSave="818" documentId="8_{FF07DBE4-2E43-45A4-A665-4C1273F6EE3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{078108DD-B6E5-4D21-BDD8-713570A7F6DE}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{593E7210-4473-4407-B4A2-ADC98FF555AA}"/>
   </bookViews>
@@ -602,7 +602,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -653,9 +653,6 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1708,8 +1705,8 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{CC51E1EE-5D8F-4463-B3AC-3E0288975F6D}" name="Tabela1" displayName="Tabela1" ref="A1:AA94" totalsRowShown="0" headerRowDxfId="30" dataDxfId="28" headerRowBorderDxfId="29" tableBorderDxfId="27">
   <autoFilter ref="A1:AA94" xr:uid="{CC51E1EE-5D8F-4463-B3AC-3E0288975F6D}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A11:AA93">
-    <sortCondition ref="A1:A93"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AA94">
+    <sortCondition ref="A1:A94"/>
   </sortState>
   <tableColumns count="27">
     <tableColumn id="1" xr3:uid="{184AE877-3641-41C7-900B-1E7AD0E1F8A3}" name="COD_FUNCIONARIO" dataDxfId="26"/>
@@ -2083,29 +2080,29 @@
   <cols>
     <col min="1" max="1" width="20.33203125" customWidth="1"/>
     <col min="2" max="2" width="30.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.33203125" customWidth="1"/>
-    <col min="4" max="4" width="14.33203125" customWidth="1"/>
-    <col min="5" max="5" width="15.77734375" customWidth="1"/>
-    <col min="6" max="6" width="35.5546875" customWidth="1"/>
-    <col min="7" max="7" width="29.44140625" customWidth="1"/>
-    <col min="8" max="8" width="20" customWidth="1"/>
-    <col min="9" max="9" width="21.6640625" customWidth="1"/>
-    <col min="10" max="10" width="16.88671875" customWidth="1"/>
-    <col min="11" max="11" width="35.44140625" customWidth="1"/>
-    <col min="12" max="12" width="27.6640625" customWidth="1"/>
-    <col min="13" max="13" width="9.44140625" customWidth="1"/>
-    <col min="14" max="14" width="58.33203125" customWidth="1"/>
-    <col min="15" max="15" width="10.21875" customWidth="1"/>
-    <col min="16" max="16" width="11.88671875" customWidth="1"/>
-    <col min="17" max="17" width="13.77734375" customWidth="1"/>
-    <col min="18" max="18" width="10.5546875" customWidth="1"/>
-    <col min="19" max="19" width="11.21875" customWidth="1"/>
-    <col min="20" max="20" width="23.21875" customWidth="1"/>
-    <col min="21" max="21" width="17.33203125" customWidth="1"/>
-    <col min="22" max="22" width="21.77734375" customWidth="1"/>
-    <col min="23" max="23" width="13.77734375" customWidth="1"/>
-    <col min="24" max="24" width="29.88671875" customWidth="1"/>
-    <col min="25" max="25" width="24.109375" customWidth="1"/>
+    <col min="3" max="3" width="15.33203125" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="14.33203125" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="15.77734375" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="35.5546875" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="29.44140625" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="20" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="21.6640625" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="16.88671875" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="35.44140625" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="27.6640625" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="9.44140625" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="58.33203125" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="10.21875" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="11.88671875" hidden="1" customWidth="1"/>
+    <col min="17" max="17" width="13.77734375" hidden="1" customWidth="1"/>
+    <col min="18" max="18" width="10.5546875" hidden="1" customWidth="1"/>
+    <col min="19" max="19" width="11.21875" hidden="1" customWidth="1"/>
+    <col min="20" max="20" width="23.21875" hidden="1" customWidth="1"/>
+    <col min="21" max="21" width="17.33203125" hidden="1" customWidth="1"/>
+    <col min="22" max="22" width="21.77734375" hidden="1" customWidth="1"/>
+    <col min="23" max="23" width="13.77734375" hidden="1" customWidth="1"/>
+    <col min="24" max="24" width="29.88671875" hidden="1" customWidth="1"/>
+    <col min="25" max="25" width="24.109375" hidden="1" customWidth="1"/>
     <col min="26" max="26" width="31.21875" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="111.88671875" style="16" bestFit="1" customWidth="1"/>
   </cols>
@@ -2194,14 +2191,14 @@
       </c>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A2" s="19">
-        <v>3</v>
+      <c r="A2" s="10">
+        <v>1</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C2" s="8">
-        <v>43683</v>
+        <v>43570</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>110</v>
@@ -2219,22 +2216,22 @@
         <v>125</v>
       </c>
       <c r="I2" s="6">
-        <v>134</v>
+        <v>172</v>
       </c>
       <c r="J2" s="6">
-        <v>5076</v>
+        <v>5058</v>
       </c>
       <c r="K2" s="7" t="s">
         <v>126</v>
       </c>
       <c r="L2" s="6">
-        <v>123</v>
+        <v>317</v>
       </c>
       <c r="M2" s="7" t="s">
         <v>99</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="O2" s="9"/>
       <c r="P2" s="9" t="s">
@@ -2247,19 +2244,19 @@
         <v>1</v>
       </c>
       <c r="S2" s="10">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="T2" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="U2" s="11">
-        <v>45243</v>
+        <v>45405</v>
       </c>
       <c r="V2" s="9" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="W2" s="10">
-        <v>-384</v>
+        <v>-181</v>
       </c>
       <c r="X2" s="12" t="str">
         <f ca="1">IF(Tabela1[[#This Row],[DATA_CURSO]]="",
@@ -2271,7 +2268,7 @@
 "VENCIDO – "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa"),
 "EM DIA – vence em "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa")),
 "NÃO É NECESSÁRIO RENOVAR")))</f>
-        <v>EM DIA – vence em 12/11/26</v>
+        <v>EM DIA – vence em 23/04/26</v>
       </c>
       <c r="Y2" s="12" t="str">
         <f>IF(Tabela1[[#This Row],[FILIAL]]=1,"SINOP",IF(Tabela1[[#This Row],[FILIAL]]=2,"DOURADOS",IF(Tabela1[[#This Row],[FILIAL]]=3,"NOVA MUTUM",IF(Tabela1[[#This Row],[FILIAL]]=4,"FULLING",IF(Tabela1[[#This Row],[FILIAL]]=5,"SÃO PAULO",IF(Tabela1[[#This Row],[FILIAL]]=6,"SIDROLÂNDIA",IF(Tabela1[[#This Row],[FILIAL]]=8,"BALSAS",IF(Tabela1[[#This Row],[FILIAL]]=10,"LUIS EDUARDO MAGALHÃES",""))))))))</f>
@@ -2284,18 +2281,18 @@
       <c r="AA2" t="str">
         <f ca="1">CONCATENATE("• ",
     Tabela1[[#This Row],[DESCRICAO]], " - ",Tabela1[[#This Row],[STATUS_GERAL]])</f>
-        <v>• NR 20 - SEG. E TRAB. INFLAMÁVEIS E COMBUSTIVEIS CLASSE III - BASICO - EM DIA – vence em 12/11/26</v>
-      </c>
-    </row>
-    <row r="3" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A3" s="19">
-        <v>3</v>
+        <v>• NR 35 - TRABALHO EM ALTURA - EM DIA – vence em 23/04/26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A3" s="10">
+        <v>7</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C3" s="8">
-        <v>43683</v>
+        <v>43570</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>110</v>
@@ -2313,22 +2310,22 @@
         <v>125</v>
       </c>
       <c r="I3" s="6">
-        <v>134</v>
+        <v>172</v>
       </c>
       <c r="J3" s="6">
-        <v>5076</v>
+        <v>5058</v>
       </c>
       <c r="K3" s="7" t="s">
         <v>126</v>
       </c>
       <c r="L3" s="6">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="M3" s="7" t="s">
         <v>99</v>
       </c>
       <c r="N3" s="9" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="O3" s="9"/>
       <c r="P3" s="9" t="s">
@@ -2341,19 +2338,19 @@
         <v>1</v>
       </c>
       <c r="S3" s="10">
-        <v>80</v>
+        <v>117</v>
       </c>
       <c r="T3" s="9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="U3" s="11">
-        <v>45812</v>
+        <v>45875</v>
       </c>
       <c r="V3" s="9" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="W3" s="10">
-        <v>-588</v>
+        <v>-1016</v>
       </c>
       <c r="X3" s="12" t="str">
         <f ca="1">IF(Tabela1[[#This Row],[DATA_CURSO]]="",
@@ -2365,7 +2362,7 @@
 "VENCIDO – "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa"),
 "EM DIA – vence em "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa")),
 "NÃO É NECESSÁRIO RENOVAR")))</f>
-        <v>EM DIA – vence em 04/06/27</v>
+        <v>EM DIA – vence em 05/08/28</v>
       </c>
       <c r="Y3" s="12" t="str">
         <f>IF(Tabela1[[#This Row],[FILIAL]]=1,"SINOP",IF(Tabela1[[#This Row],[FILIAL]]=2,"DOURADOS",IF(Tabela1[[#This Row],[FILIAL]]=3,"NOVA MUTUM",IF(Tabela1[[#This Row],[FILIAL]]=4,"FULLING",IF(Tabela1[[#This Row],[FILIAL]]=5,"SÃO PAULO",IF(Tabela1[[#This Row],[FILIAL]]=6,"SIDROLÂNDIA",IF(Tabela1[[#This Row],[FILIAL]]=8,"BALSAS",IF(Tabela1[[#This Row],[FILIAL]]=10,"LUIS EDUARDO MAGALHÃES",""))))))))</f>
@@ -2378,18 +2375,18 @@
       <c r="AA3" t="str">
         <f ca="1">CONCATENATE("• ",
     Tabela1[[#This Row],[DESCRICAO]], " - ",Tabela1[[#This Row],[STATUS_GERAL]])</f>
-        <v>• NR 20 - SEG. E TRAB. INFLAMÁVEIS E COMBUSTIVEIS CLASSE III - INTERMEDIÁRIO - EM DIA – vence em 04/06/27</v>
-      </c>
-    </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A4" s="19">
-        <v>3</v>
+        <v>• NR 20 - SEG. E TRAB. INFLAMÁVEIS E COMBUSTIVEIS CLASSE III - BASICO - EM DIA – vence em 05/08/28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A4" s="10">
+        <v>7</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C4" s="8">
-        <v>43683</v>
+        <v>43570</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>110</v>
@@ -2407,22 +2404,22 @@
         <v>125</v>
       </c>
       <c r="I4" s="6">
-        <v>134</v>
+        <v>172</v>
       </c>
       <c r="J4" s="6">
-        <v>5076</v>
+        <v>5058</v>
       </c>
       <c r="K4" s="7" t="s">
         <v>126</v>
       </c>
       <c r="L4" s="6">
-        <v>28</v>
+        <v>200</v>
       </c>
       <c r="M4" s="7" t="s">
         <v>99</v>
       </c>
       <c r="N4" s="9" t="s">
-        <v>49</v>
+        <v>109</v>
       </c>
       <c r="O4" s="9"/>
       <c r="P4" s="9" t="s">
@@ -2435,20 +2432,18 @@
         <v>1</v>
       </c>
       <c r="S4" s="10">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="T4" s="9" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="U4" s="11">
-        <v>45349</v>
+        <v>44883</v>
       </c>
       <c r="V4" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="W4" s="10">
-        <v>-125</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="W4" s="10"/>
       <c r="X4" s="12" t="str">
         <f ca="1">IF(Tabela1[[#This Row],[DATA_CURSO]]="",
 "PENDENTE",
@@ -2459,7 +2454,7 @@
 "VENCIDO – "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa"),
 "EM DIA – vence em "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa")),
 "NÃO É NECESSÁRIO RENOVAR")))</f>
-        <v>EM DIA – vence em 26/02/26</v>
+        <v>EM DIA – não é necessário renovar</v>
       </c>
       <c r="Y4" s="12" t="str">
         <f>IF(Tabela1[[#This Row],[FILIAL]]=1,"SINOP",IF(Tabela1[[#This Row],[FILIAL]]=2,"DOURADOS",IF(Tabela1[[#This Row],[FILIAL]]=3,"NOVA MUTUM",IF(Tabela1[[#This Row],[FILIAL]]=4,"FULLING",IF(Tabela1[[#This Row],[FILIAL]]=5,"SÃO PAULO",IF(Tabela1[[#This Row],[FILIAL]]=6,"SIDROLÂNDIA",IF(Tabela1[[#This Row],[FILIAL]]=8,"BALSAS",IF(Tabela1[[#This Row],[FILIAL]]=10,"LUIS EDUARDO MAGALHÃES",""))))))))</f>
@@ -2472,18 +2467,18 @@
       <c r="AA4" t="str">
         <f ca="1">CONCATENATE("• ",
     Tabela1[[#This Row],[DESCRICAO]], " - ",Tabela1[[#This Row],[STATUS_GERAL]])</f>
-        <v>• NR 35 - TRABALHO EM ALTURA - EM DIA – vence em 26/02/26</v>
-      </c>
-    </row>
-    <row r="5" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A5" s="19">
-        <v>3</v>
+        <v>• BLOQUEIO E SINALIZAÇÃO DE ENERGIAS PERIGOSAS - LOCKOUT/TAGOUT - NR10 E NR12 - EM DIA – não é necessário renovar</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A5" s="10">
+        <v>7</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C5" s="8">
-        <v>43683</v>
+        <v>43570</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>110</v>
@@ -2501,22 +2496,22 @@
         <v>125</v>
       </c>
       <c r="I5" s="6">
-        <v>134</v>
+        <v>172</v>
       </c>
       <c r="J5" s="6">
-        <v>5076</v>
+        <v>5058</v>
       </c>
       <c r="K5" s="7" t="s">
         <v>126</v>
       </c>
       <c r="L5" s="6">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M5" s="7" t="s">
         <v>99</v>
       </c>
       <c r="N5" s="9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="O5" s="9"/>
       <c r="P5" s="9" t="s">
@@ -2535,13 +2530,13 @@
         <v>104</v>
       </c>
       <c r="U5" s="11">
-        <v>44333</v>
+        <v>45349</v>
       </c>
       <c r="V5" s="9" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="W5" s="10">
-        <v>1256</v>
+        <v>-125</v>
       </c>
       <c r="X5" s="12" t="str">
         <f ca="1">IF(Tabela1[[#This Row],[DATA_CURSO]]="",
@@ -2553,7 +2548,7 @@
 "VENCIDO – "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa"),
 "EM DIA – vence em "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa")),
 "NÃO É NECESSÁRIO RENOVAR")))</f>
-        <v>VENCIDO – 17/05/22</v>
+        <v>EM DIA – vence em 26/02/26</v>
       </c>
       <c r="Y5" s="12" t="str">
         <f>IF(Tabela1[[#This Row],[FILIAL]]=1,"SINOP",IF(Tabela1[[#This Row],[FILIAL]]=2,"DOURADOS",IF(Tabela1[[#This Row],[FILIAL]]=3,"NOVA MUTUM",IF(Tabela1[[#This Row],[FILIAL]]=4,"FULLING",IF(Tabela1[[#This Row],[FILIAL]]=5,"SÃO PAULO",IF(Tabela1[[#This Row],[FILIAL]]=6,"SIDROLÂNDIA",IF(Tabela1[[#This Row],[FILIAL]]=8,"BALSAS",IF(Tabela1[[#This Row],[FILIAL]]=10,"LUIS EDUARDO MAGALHÃES",""))))))))</f>
@@ -2566,18 +2561,18 @@
       <c r="AA5" t="str">
         <f ca="1">CONCATENATE("• ",
     Tabela1[[#This Row],[DESCRICAO]], " - ",Tabela1[[#This Row],[STATUS_GERAL]])</f>
-        <v>• NR 33 - SEGURANÇA E SAUDE NOS TRABALHOS EM ESPAÇOS CONFINADOS - VIGIA E TRABALHADOR - VENCIDO – 17/05/22</v>
+        <v>• NR 35 - TRABALHO EM ALTURA - EM DIA – vence em 26/02/26</v>
       </c>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A6" s="19">
-        <v>3</v>
+      <c r="A6" s="10">
+        <v>7</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C6" s="8">
-        <v>43683</v>
+        <v>43570</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>110</v>
@@ -2595,10 +2590,10 @@
         <v>125</v>
       </c>
       <c r="I6" s="6">
-        <v>134</v>
+        <v>172</v>
       </c>
       <c r="J6" s="6">
-        <v>5076</v>
+        <v>5058</v>
       </c>
       <c r="K6" s="7" t="s">
         <v>126</v>
@@ -2610,7 +2605,7 @@
         <v>99</v>
       </c>
       <c r="N6" s="9" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="O6" s="9"/>
       <c r="P6" s="9" t="s">
@@ -2629,13 +2624,13 @@
         <v>101</v>
       </c>
       <c r="U6" s="11">
-        <v>45871</v>
+        <v>45349</v>
       </c>
       <c r="V6" s="9" t="s">
         <v>36</v>
       </c>
       <c r="W6" s="10">
-        <v>-647</v>
+        <v>-125</v>
       </c>
       <c r="X6" s="12" t="str">
         <f ca="1">IF(Tabela1[[#This Row],[DATA_CURSO]]="",
@@ -2647,7 +2642,7 @@
 "VENCIDO – "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa"),
 "EM DIA – vence em "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa")),
 "NÃO É NECESSÁRIO RENOVAR")))</f>
-        <v>EM DIA – vence em 02/08/27</v>
+        <v>EM DIA – vence em 26/02/26</v>
       </c>
       <c r="Y6" s="12" t="str">
         <f>IF(Tabela1[[#This Row],[FILIAL]]=1,"SINOP",IF(Tabela1[[#This Row],[FILIAL]]=2,"DOURADOS",IF(Tabela1[[#This Row],[FILIAL]]=3,"NOVA MUTUM",IF(Tabela1[[#This Row],[FILIAL]]=4,"FULLING",IF(Tabela1[[#This Row],[FILIAL]]=5,"SÃO PAULO",IF(Tabela1[[#This Row],[FILIAL]]=6,"SIDROLÂNDIA",IF(Tabela1[[#This Row],[FILIAL]]=8,"BALSAS",IF(Tabela1[[#This Row],[FILIAL]]=10,"LUIS EDUARDO MAGALHÃES",""))))))))</f>
@@ -2660,18 +2655,18 @@
       <c r="AA6" t="str">
         <f ca="1">CONCATENATE("• ",
     Tabela1[[#This Row],[DESCRICAO]], " - ",Tabela1[[#This Row],[STATUS_GERAL]])</f>
-        <v>• NR 11 - OPERADOR PA CARREGADEIRA - EM DIA – vence em 02/08/27</v>
+        <v>• NR 35 - TRABALHO EM ALTURA - EM DIA – vence em 26/02/26</v>
       </c>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A7" s="19">
-        <v>3</v>
+      <c r="A7" s="10">
+        <v>33</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C7" s="8">
-        <v>43683</v>
+        <v>43570</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>110</v>
@@ -2689,22 +2684,22 @@
         <v>125</v>
       </c>
       <c r="I7" s="6">
-        <v>134</v>
+        <v>172</v>
       </c>
       <c r="J7" s="6">
-        <v>5076</v>
+        <v>5058</v>
       </c>
       <c r="K7" s="7" t="s">
         <v>126</v>
       </c>
       <c r="L7" s="6">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="M7" s="7" t="s">
         <v>99</v>
       </c>
       <c r="N7" s="9" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="O7" s="9"/>
       <c r="P7" s="9" t="s">
@@ -2714,7 +2709,7 @@
         <v>1</v>
       </c>
       <c r="R7" s="10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S7" s="10">
         <v>102</v>
@@ -2723,14 +2718,12 @@
         <v>106</v>
       </c>
       <c r="U7" s="11">
-        <v>45581</v>
+        <v>45042</v>
       </c>
       <c r="V7" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="W7" s="10">
-        <v>-357</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="W7" s="10"/>
       <c r="X7" s="12" t="str">
         <f ca="1">IF(Tabela1[[#This Row],[DATA_CURSO]]="",
 "PENDENTE",
@@ -2741,11 +2734,11 @@
 "VENCIDO – "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa"),
 "EM DIA – vence em "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa")),
 "NÃO É NECESSÁRIO RENOVAR")))</f>
-        <v>EM DIA – vence em 16/10/26</v>
+        <v>EM DIA – não é necessário renovar</v>
       </c>
       <c r="Y7" s="12" t="str">
         <f>IF(Tabela1[[#This Row],[FILIAL]]=1,"SINOP",IF(Tabela1[[#This Row],[FILIAL]]=2,"DOURADOS",IF(Tabela1[[#This Row],[FILIAL]]=3,"NOVA MUTUM",IF(Tabela1[[#This Row],[FILIAL]]=4,"FULLING",IF(Tabela1[[#This Row],[FILIAL]]=5,"SÃO PAULO",IF(Tabela1[[#This Row],[FILIAL]]=6,"SIDROLÂNDIA",IF(Tabela1[[#This Row],[FILIAL]]=8,"BALSAS",IF(Tabela1[[#This Row],[FILIAL]]=10,"LUIS EDUARDO MAGALHÃES",""))))))))</f>
-        <v>NOVA MUTUM</v>
+        <v>SINOP</v>
       </c>
       <c r="Z7" s="13" t="str">
         <f>VLOOKUP(N7,RENOVAÇÃO!A:D,4,0)</f>
@@ -2754,18 +2747,18 @@
       <c r="AA7" t="str">
         <f ca="1">CONCATENATE("• ",
     Tabela1[[#This Row],[DESCRICAO]], " - ",Tabela1[[#This Row],[STATUS_GERAL]])</f>
-        <v>• NR 35 - TRABALHO EM ALTURA - EM DIA – vence em 16/10/26</v>
+        <v>• NR 13 - SEGURANÇA NA OPERAÇÃO DE CALDEIRAS - EM DIA – não é necessário renovar</v>
       </c>
     </row>
     <row r="8" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A8" s="19">
-        <v>3</v>
+      <c r="A8" s="10">
+        <v>33</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C8" s="8">
-        <v>43683</v>
+        <v>43570</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>110</v>
@@ -2783,16 +2776,16 @@
         <v>125</v>
       </c>
       <c r="I8" s="6">
-        <v>134</v>
+        <v>172</v>
       </c>
       <c r="J8" s="6">
-        <v>5076</v>
+        <v>5058</v>
       </c>
       <c r="K8" s="7" t="s">
         <v>126</v>
       </c>
       <c r="L8" s="6">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="M8" s="7" t="s">
         <v>99</v>
@@ -2808,7 +2801,7 @@
         <v>1</v>
       </c>
       <c r="R8" s="10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S8" s="10">
         <v>102</v>
@@ -2817,7 +2810,7 @@
         <v>106</v>
       </c>
       <c r="U8" s="11">
-        <v>44820</v>
+        <v>45125</v>
       </c>
       <c r="V8" s="9" t="s">
         <v>5</v>
@@ -2837,7 +2830,7 @@
       </c>
       <c r="Y8" s="12" t="str">
         <f>IF(Tabela1[[#This Row],[FILIAL]]=1,"SINOP",IF(Tabela1[[#This Row],[FILIAL]]=2,"DOURADOS",IF(Tabela1[[#This Row],[FILIAL]]=3,"NOVA MUTUM",IF(Tabela1[[#This Row],[FILIAL]]=4,"FULLING",IF(Tabela1[[#This Row],[FILIAL]]=5,"SÃO PAULO",IF(Tabela1[[#This Row],[FILIAL]]=6,"SIDROLÂNDIA",IF(Tabela1[[#This Row],[FILIAL]]=8,"BALSAS",IF(Tabela1[[#This Row],[FILIAL]]=10,"LUIS EDUARDO MAGALHÃES",""))))))))</f>
-        <v>NOVA MUTUM</v>
+        <v>SINOP</v>
       </c>
       <c r="Z8" s="13" t="str">
         <f>VLOOKUP(N8,RENOVAÇÃO!A:D,4,0)</f>
@@ -2849,15 +2842,15 @@
         <v>• BLOQUEIO E SINALIZAÇÃO DE ENERGIAS PERIGOSAS - LOCKOUT/TAGOUT - NR10 E NR12 - EM DIA – não é necessário renovar</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A9" s="19">
-        <v>3</v>
+    <row r="9" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A9" s="10">
+        <v>33</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C9" s="8">
-        <v>43683</v>
+        <v>43570</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>110</v>
@@ -2875,22 +2868,22 @@
         <v>125</v>
       </c>
       <c r="I9" s="6">
-        <v>134</v>
+        <v>172</v>
       </c>
       <c r="J9" s="6">
-        <v>5076</v>
+        <v>5058</v>
       </c>
       <c r="K9" s="7" t="s">
         <v>126</v>
       </c>
       <c r="L9" s="6">
-        <v>308</v>
+        <v>26</v>
       </c>
       <c r="M9" s="7" t="s">
         <v>99</v>
       </c>
       <c r="N9" s="9" t="s">
-        <v>49</v>
+        <v>111</v>
       </c>
       <c r="O9" s="9"/>
       <c r="P9" s="9" t="s">
@@ -2900,22 +2893,22 @@
         <v>1</v>
       </c>
       <c r="R9" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S9" s="10">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="T9" s="9" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="U9" s="11">
-        <v>45350</v>
+        <v>45401</v>
       </c>
       <c r="V9" s="9" t="s">
         <v>36</v>
       </c>
       <c r="W9" s="10">
-        <v>-126</v>
+        <v>-177</v>
       </c>
       <c r="X9" s="12" t="str">
         <f ca="1">IF(Tabela1[[#This Row],[DATA_CURSO]]="",
@@ -2927,11 +2920,11 @@
 "VENCIDO – "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa"),
 "EM DIA – vence em "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa")),
 "NÃO É NECESSÁRIO RENOVAR")))</f>
-        <v>EM DIA – vence em 27/02/26</v>
+        <v>EM DIA – vence em 19/04/26</v>
       </c>
       <c r="Y9" s="12" t="str">
         <f>IF(Tabela1[[#This Row],[FILIAL]]=1,"SINOP",IF(Tabela1[[#This Row],[FILIAL]]=2,"DOURADOS",IF(Tabela1[[#This Row],[FILIAL]]=3,"NOVA MUTUM",IF(Tabela1[[#This Row],[FILIAL]]=4,"FULLING",IF(Tabela1[[#This Row],[FILIAL]]=5,"SÃO PAULO",IF(Tabela1[[#This Row],[FILIAL]]=6,"SIDROLÂNDIA",IF(Tabela1[[#This Row],[FILIAL]]=8,"BALSAS",IF(Tabela1[[#This Row],[FILIAL]]=10,"LUIS EDUARDO MAGALHÃES",""))))))))</f>
-        <v>SINOP</v>
+        <v>DOURADOS</v>
       </c>
       <c r="Z9" s="13" t="str">
         <f>VLOOKUP(N9,RENOVAÇÃO!A:D,4,0)</f>
@@ -2940,18 +2933,18 @@
       <c r="AA9" t="str">
         <f ca="1">CONCATENATE("• ",
     Tabela1[[#This Row],[DESCRICAO]], " - ",Tabela1[[#This Row],[STATUS_GERAL]])</f>
-        <v>• NR 35 - TRABALHO EM ALTURA - EM DIA – vence em 27/02/26</v>
-      </c>
-    </row>
-    <row r="10" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A10" s="19">
-        <v>3</v>
+        <v>• NR 10 - SEGURANÇA EM INSTALAÇÕES E SERVIÇOS EM ELETRICIDADE ( BASÍCO) - EM DIA – vence em 19/04/26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A10" s="10">
+        <v>33</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C10" s="8">
-        <v>43683</v>
+        <v>43570</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>110</v>
@@ -2969,22 +2962,22 @@
         <v>125</v>
       </c>
       <c r="I10" s="6">
-        <v>134</v>
+        <v>172</v>
       </c>
       <c r="J10" s="6">
-        <v>5076</v>
+        <v>5058</v>
       </c>
       <c r="K10" s="7" t="s">
         <v>126</v>
       </c>
       <c r="L10" s="6">
-        <v>321</v>
+        <v>8</v>
       </c>
       <c r="M10" s="7" t="s">
         <v>99</v>
       </c>
       <c r="N10" s="9" t="s">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="O10" s="9"/>
       <c r="P10" s="9" t="s">
@@ -2994,23 +2987,21 @@
         <v>1</v>
       </c>
       <c r="R10" s="10">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="S10" s="10">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="T10" s="9" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="U10" s="11">
-        <v>45693</v>
+        <v>44568</v>
       </c>
       <c r="V10" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="W10" s="10">
-        <v>-469</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="W10" s="10"/>
       <c r="X10" s="12" t="str">
         <f ca="1">IF(Tabela1[[#This Row],[DATA_CURSO]]="",
 "PENDENTE",
@@ -3021,11 +3012,11 @@
 "VENCIDO – "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa"),
 "EM DIA – vence em "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa")),
 "NÃO É NECESSÁRIO RENOVAR")))</f>
-        <v>EM DIA – vence em 05/02/27</v>
+        <v>EM DIA – não é necessário renovar</v>
       </c>
       <c r="Y10" s="12" t="str">
         <f>IF(Tabela1[[#This Row],[FILIAL]]=1,"SINOP",IF(Tabela1[[#This Row],[FILIAL]]=2,"DOURADOS",IF(Tabela1[[#This Row],[FILIAL]]=3,"NOVA MUTUM",IF(Tabela1[[#This Row],[FILIAL]]=4,"FULLING",IF(Tabela1[[#This Row],[FILIAL]]=5,"SÃO PAULO",IF(Tabela1[[#This Row],[FILIAL]]=6,"SIDROLÂNDIA",IF(Tabela1[[#This Row],[FILIAL]]=8,"BALSAS",IF(Tabela1[[#This Row],[FILIAL]]=10,"LUIS EDUARDO MAGALHÃES",""))))))))</f>
-        <v>SIDROLÂNDIA</v>
+        <v>NOVA MUTUM</v>
       </c>
       <c r="Z10" s="13" t="str">
         <f>VLOOKUP(N10,RENOVAÇÃO!A:D,4,0)</f>
@@ -3034,18 +3025,18 @@
       <c r="AA10" t="str">
         <f ca="1">CONCATENATE("• ",
     Tabela1[[#This Row],[DESCRICAO]], " - ",Tabela1[[#This Row],[STATUS_GERAL]])</f>
-        <v>• NR 20 - SEG. E TRAB. INFLAMÁVEIS E COMBUSTIVEIS CLASSE III - INTERMEDIÁRIO - EM DIA – vence em 05/02/27</v>
+        <v>• DIREÇÃO DEFENSIVA - TEÓRICO - EM DIA – não é necessário renovar</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A11" s="19">
-        <v>3</v>
+      <c r="A11" s="10">
+        <v>33</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C11" s="8">
-        <v>43683</v>
+        <v>43570</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>110</v>
@@ -3063,22 +3054,22 @@
         <v>125</v>
       </c>
       <c r="I11" s="6">
-        <v>134</v>
+        <v>172</v>
       </c>
       <c r="J11" s="6">
-        <v>5076</v>
+        <v>5058</v>
       </c>
       <c r="K11" s="7" t="s">
         <v>126</v>
       </c>
       <c r="L11" s="6">
-        <v>319</v>
+        <v>129</v>
       </c>
       <c r="M11" s="7" t="s">
         <v>99</v>
       </c>
       <c r="N11" s="9" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="O11" s="9"/>
       <c r="P11" s="9" t="s">
@@ -3088,21 +3079,23 @@
         <v>1</v>
       </c>
       <c r="R11" s="10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S11" s="10">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="T11" s="9" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="U11" s="11">
-        <v>45489</v>
+        <v>45945</v>
       </c>
       <c r="V11" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="W11" s="10"/>
+        <v>44</v>
+      </c>
+      <c r="W11" s="10">
+        <v>-1086</v>
+      </c>
       <c r="X11" s="12" t="str">
         <f ca="1">IF(Tabela1[[#This Row],[DATA_CURSO]]="",
 "PENDENTE",
@@ -3113,11 +3106,11 @@
 "VENCIDO – "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa"),
 "EM DIA – vence em "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa")),
 "NÃO É NECESSÁRIO RENOVAR")))</f>
-        <v>EM DIA – não é necessário renovar</v>
+        <v>EM DIA – vence em 14/10/28</v>
       </c>
       <c r="Y11" s="12" t="str">
         <f>IF(Tabela1[[#This Row],[FILIAL]]=1,"SINOP",IF(Tabela1[[#This Row],[FILIAL]]=2,"DOURADOS",IF(Tabela1[[#This Row],[FILIAL]]=3,"NOVA MUTUM",IF(Tabela1[[#This Row],[FILIAL]]=4,"FULLING",IF(Tabela1[[#This Row],[FILIAL]]=5,"SÃO PAULO",IF(Tabela1[[#This Row],[FILIAL]]=6,"SIDROLÂNDIA",IF(Tabela1[[#This Row],[FILIAL]]=8,"BALSAS",IF(Tabela1[[#This Row],[FILIAL]]=10,"LUIS EDUARDO MAGALHÃES",""))))))))</f>
-        <v>NOVA MUTUM</v>
+        <v>SINOP</v>
       </c>
       <c r="Z11" s="13" t="str">
         <f>VLOOKUP(N11,RENOVAÇÃO!A:D,4,0)</f>
@@ -3126,18 +3119,18 @@
       <c r="AA11" t="str">
         <f ca="1">CONCATENATE("• ",
     Tabela1[[#This Row],[DESCRICAO]], " - ",Tabela1[[#This Row],[STATUS_GERAL]])</f>
-        <v>• NR 26 - SINALIZAÇÃO DE SEGURANÇA - EM DIA – não é necessário renovar</v>
-      </c>
-    </row>
-    <row r="12" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A12" s="19">
-        <v>3</v>
+        <v>• NR 20 - SEG. E TRAB. INFLAMÁVEIS E COMBUSTIVEIS CLASSE III - BASICO - EM DIA – vence em 14/10/28</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A12" s="10">
+        <v>37</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C12" s="8">
-        <v>43683</v>
+        <v>43570</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>110</v>
@@ -3155,22 +3148,22 @@
         <v>125</v>
       </c>
       <c r="I12" s="6">
-        <v>134</v>
+        <v>172</v>
       </c>
       <c r="J12" s="6">
-        <v>5076</v>
+        <v>5058</v>
       </c>
       <c r="K12" s="7" t="s">
         <v>126</v>
       </c>
       <c r="L12" s="6">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="M12" s="7" t="s">
         <v>99</v>
       </c>
       <c r="N12" s="9" t="s">
-        <v>109</v>
+        <v>46</v>
       </c>
       <c r="O12" s="9"/>
       <c r="P12" s="9" t="s">
@@ -3180,7 +3173,7 @@
         <v>1</v>
       </c>
       <c r="R12" s="10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S12" s="10">
         <v>102</v>
@@ -3189,7 +3182,7 @@
         <v>106</v>
       </c>
       <c r="U12" s="11">
-        <v>44878</v>
+        <v>45489</v>
       </c>
       <c r="V12" s="9" t="s">
         <v>5</v>
@@ -3209,7 +3202,7 @@
       </c>
       <c r="Y12" s="12" t="str">
         <f>IF(Tabela1[[#This Row],[FILIAL]]=1,"SINOP",IF(Tabela1[[#This Row],[FILIAL]]=2,"DOURADOS",IF(Tabela1[[#This Row],[FILIAL]]=3,"NOVA MUTUM",IF(Tabela1[[#This Row],[FILIAL]]=4,"FULLING",IF(Tabela1[[#This Row],[FILIAL]]=5,"SÃO PAULO",IF(Tabela1[[#This Row],[FILIAL]]=6,"SIDROLÂNDIA",IF(Tabela1[[#This Row],[FILIAL]]=8,"BALSAS",IF(Tabela1[[#This Row],[FILIAL]]=10,"LUIS EDUARDO MAGALHÃES",""))))))))</f>
-        <v>NOVA MUTUM</v>
+        <v>SINOP</v>
       </c>
       <c r="Z12" s="13" t="str">
         <f>VLOOKUP(N12,RENOVAÇÃO!A:D,4,0)</f>
@@ -3218,18 +3211,18 @@
       <c r="AA12" t="str">
         <f ca="1">CONCATENATE("• ",
     Tabela1[[#This Row],[DESCRICAO]], " - ",Tabela1[[#This Row],[STATUS_GERAL]])</f>
-        <v>• BLOQUEIO E SINALIZAÇÃO DE ENERGIAS PERIGOSAS - LOCKOUT/TAGOUT - NR10 E NR12 - EM DIA – não é necessário renovar</v>
-      </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A13" s="19">
-        <v>3</v>
+        <v>• NR 26 - SINALIZAÇÃO DE SEGURANÇA - EM DIA – não é necessário renovar</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A13" s="10">
+        <v>37</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C13" s="8">
-        <v>43683</v>
+        <v>43570</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>110</v>
@@ -3247,22 +3240,22 @@
         <v>125</v>
       </c>
       <c r="I13" s="6">
-        <v>134</v>
+        <v>172</v>
       </c>
       <c r="J13" s="6">
-        <v>5076</v>
+        <v>5058</v>
       </c>
       <c r="K13" s="7" t="s">
         <v>126</v>
       </c>
       <c r="L13" s="6">
-        <v>300</v>
+        <v>82</v>
       </c>
       <c r="M13" s="7" t="s">
         <v>99</v>
       </c>
       <c r="N13" s="9" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="O13" s="9"/>
       <c r="P13" s="9" t="s">
@@ -3272,7 +3265,7 @@
         <v>1</v>
       </c>
       <c r="R13" s="10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S13" s="10">
         <v>102</v>
@@ -3281,13 +3274,13 @@
         <v>106</v>
       </c>
       <c r="U13" s="11">
-        <v>45371</v>
+        <v>45602</v>
       </c>
       <c r="V13" s="9" t="s">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="W13" s="10">
-        <v>-147</v>
+        <v>-13</v>
       </c>
       <c r="X13" s="12" t="str">
         <f ca="1">IF(Tabela1[[#This Row],[DATA_CURSO]]="",
@@ -3299,11 +3292,11 @@
 "VENCIDO – "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa"),
 "EM DIA – vence em "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa")),
 "NÃO É NECESSÁRIO RENOVAR")))</f>
-        <v>EM DIA – vence em 20/03/26</v>
+        <v>EM DIA – vence em 06/11/25</v>
       </c>
       <c r="Y13" s="12" t="str">
         <f>IF(Tabela1[[#This Row],[FILIAL]]=1,"SINOP",IF(Tabela1[[#This Row],[FILIAL]]=2,"DOURADOS",IF(Tabela1[[#This Row],[FILIAL]]=3,"NOVA MUTUM",IF(Tabela1[[#This Row],[FILIAL]]=4,"FULLING",IF(Tabela1[[#This Row],[FILIAL]]=5,"SÃO PAULO",IF(Tabela1[[#This Row],[FILIAL]]=6,"SIDROLÂNDIA",IF(Tabela1[[#This Row],[FILIAL]]=8,"BALSAS",IF(Tabela1[[#This Row],[FILIAL]]=10,"LUIS EDUARDO MAGALHÃES",""))))))))</f>
-        <v>NOVA MUTUM</v>
+        <v>SINOP</v>
       </c>
       <c r="Z13" s="13" t="str">
         <f>VLOOKUP(N13,RENOVAÇÃO!A:D,4,0)</f>
@@ -3312,18 +3305,18 @@
       <c r="AA13" t="str">
         <f ca="1">CONCATENATE("• ",
     Tabela1[[#This Row],[DESCRICAO]], " - ",Tabela1[[#This Row],[STATUS_GERAL]])</f>
-        <v>• NR 35 - TRABALHO EM ALTURA - EM DIA – vence em 20/03/26</v>
-      </c>
-    </row>
-    <row r="14" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A14" s="19">
-        <v>3</v>
+        <v>• NR 20 - SEG. E TRAB. INFLAMÁVEIS E COMBUSTIVEIS CLASSE III - AVANÇADO - EM DIA – vence em 06/11/25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A14" s="10">
+        <v>37</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C14" s="8">
-        <v>43683</v>
+        <v>43570</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>110</v>
@@ -3341,22 +3334,22 @@
         <v>125</v>
       </c>
       <c r="I14" s="6">
-        <v>134</v>
+        <v>172</v>
       </c>
       <c r="J14" s="6">
-        <v>5076</v>
+        <v>5058</v>
       </c>
       <c r="K14" s="7" t="s">
         <v>126</v>
       </c>
       <c r="L14" s="6">
-        <v>295</v>
+        <v>2</v>
       </c>
       <c r="M14" s="7" t="s">
         <v>99</v>
       </c>
       <c r="N14" s="9" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="O14" s="9"/>
       <c r="P14" s="9" t="s">
@@ -3366,22 +3359,22 @@
         <v>1</v>
       </c>
       <c r="R14" s="10">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="S14" s="10">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="T14" s="9" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="U14" s="11">
-        <v>45390</v>
+        <v>45349</v>
       </c>
       <c r="V14" s="9" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="W14" s="10">
-        <v>199</v>
+        <v>-125</v>
       </c>
       <c r="X14" s="12" t="str">
         <f ca="1">IF(Tabela1[[#This Row],[DATA_CURSO]]="",
@@ -3393,11 +3386,11 @@
 "VENCIDO – "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa"),
 "EM DIA – vence em "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa")),
 "NÃO É NECESSÁRIO RENOVAR")))</f>
-        <v>VENCIDO – 08/04/25</v>
+        <v>EM DIA – vence em 26/02/26</v>
       </c>
       <c r="Y14" s="12" t="str">
         <f>IF(Tabela1[[#This Row],[FILIAL]]=1,"SINOP",IF(Tabela1[[#This Row],[FILIAL]]=2,"DOURADOS",IF(Tabela1[[#This Row],[FILIAL]]=3,"NOVA MUTUM",IF(Tabela1[[#This Row],[FILIAL]]=4,"FULLING",IF(Tabela1[[#This Row],[FILIAL]]=5,"SÃO PAULO",IF(Tabela1[[#This Row],[FILIAL]]=6,"SIDROLÂNDIA",IF(Tabela1[[#This Row],[FILIAL]]=8,"BALSAS",IF(Tabela1[[#This Row],[FILIAL]]=10,"LUIS EDUARDO MAGALHÃES",""))))))))</f>
-        <v>LUIS EDUARDO MAGALHÃES</v>
+        <v>SINOP</v>
       </c>
       <c r="Z14" s="13" t="str">
         <f>VLOOKUP(N14,RENOVAÇÃO!A:D,4,0)</f>
@@ -3406,18 +3399,18 @@
       <c r="AA14" t="str">
         <f ca="1">CONCATENATE("• ",
     Tabela1[[#This Row],[DESCRICAO]], " - ",Tabela1[[#This Row],[STATUS_GERAL]])</f>
-        <v>• NR 20 - SEG. E TRAB. INFLAMÁVEIS E COMBUSTIVEIS CLASSE III - AVANÇADO - VENCIDO – 08/04/25</v>
-      </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A15" s="19">
-        <v>3</v>
+        <v>• NR 35 - TRABALHO EM ALTURA - EM DIA – vence em 26/02/26</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A15" s="10">
+        <v>37</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C15" s="8">
-        <v>43683</v>
+        <v>43570</v>
       </c>
       <c r="D15" s="7" t="s">
         <v>110</v>
@@ -3435,22 +3428,22 @@
         <v>125</v>
       </c>
       <c r="I15" s="6">
-        <v>134</v>
+        <v>172</v>
       </c>
       <c r="J15" s="6">
-        <v>5076</v>
+        <v>5058</v>
       </c>
       <c r="K15" s="7" t="s">
         <v>126</v>
       </c>
       <c r="L15" s="6">
-        <v>235</v>
+        <v>322</v>
       </c>
       <c r="M15" s="7" t="s">
         <v>99</v>
       </c>
       <c r="N15" s="9" t="s">
-        <v>49</v>
+        <v>109</v>
       </c>
       <c r="O15" s="9"/>
       <c r="P15" s="9" t="s">
@@ -3460,23 +3453,21 @@
         <v>1</v>
       </c>
       <c r="R15" s="10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S15" s="10">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="T15" s="9" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="U15" s="11">
-        <v>45827</v>
+        <v>44865</v>
       </c>
       <c r="V15" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="W15" s="10">
-        <v>-603</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="W15" s="10"/>
       <c r="X15" s="12" t="str">
         <f ca="1">IF(Tabela1[[#This Row],[DATA_CURSO]]="",
 "PENDENTE",
@@ -3487,11 +3478,11 @@
 "VENCIDO – "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa"),
 "EM DIA – vence em "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa")),
 "NÃO É NECESSÁRIO RENOVAR")))</f>
-        <v>EM DIA – vence em 19/06/27</v>
+        <v>EM DIA – não é necessário renovar</v>
       </c>
       <c r="Y15" s="12" t="str">
         <f>IF(Tabela1[[#This Row],[FILIAL]]=1,"SINOP",IF(Tabela1[[#This Row],[FILIAL]]=2,"DOURADOS",IF(Tabela1[[#This Row],[FILIAL]]=3,"NOVA MUTUM",IF(Tabela1[[#This Row],[FILIAL]]=4,"FULLING",IF(Tabela1[[#This Row],[FILIAL]]=5,"SÃO PAULO",IF(Tabela1[[#This Row],[FILIAL]]=6,"SIDROLÂNDIA",IF(Tabela1[[#This Row],[FILIAL]]=8,"BALSAS",IF(Tabela1[[#This Row],[FILIAL]]=10,"LUIS EDUARDO MAGALHÃES",""))))))))</f>
-        <v>SINOP</v>
+        <v>NOVA MUTUM</v>
       </c>
       <c r="Z15" s="13" t="str">
         <f>VLOOKUP(N15,RENOVAÇÃO!A:D,4,0)</f>
@@ -3500,18 +3491,18 @@
       <c r="AA15" t="str">
         <f ca="1">CONCATENATE("• ",
     Tabela1[[#This Row],[DESCRICAO]], " - ",Tabela1[[#This Row],[STATUS_GERAL]])</f>
-        <v>• NR 35 - TRABALHO EM ALTURA - EM DIA – vence em 19/06/27</v>
+        <v>• BLOQUEIO E SINALIZAÇÃO DE ENERGIAS PERIGOSAS - LOCKOUT/TAGOUT - NR10 E NR12 - EM DIA – não é necessário renovar</v>
       </c>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A16" s="19">
-        <v>3</v>
+      <c r="A16" s="10">
+        <v>45</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C16" s="8">
-        <v>43683</v>
+        <v>43570</v>
       </c>
       <c r="D16" s="7" t="s">
         <v>110</v>
@@ -3529,22 +3520,22 @@
         <v>125</v>
       </c>
       <c r="I16" s="6">
-        <v>134</v>
+        <v>172</v>
       </c>
       <c r="J16" s="6">
-        <v>5076</v>
+        <v>5058</v>
       </c>
       <c r="K16" s="7" t="s">
         <v>126</v>
       </c>
       <c r="L16" s="6">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="M16" s="7" t="s">
         <v>99</v>
       </c>
       <c r="N16" s="9" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="O16" s="9"/>
       <c r="P16" s="9" t="s">
@@ -3563,12 +3554,14 @@
         <v>106</v>
       </c>
       <c r="U16" s="11">
-        <v>45489</v>
+        <v>45834</v>
       </c>
       <c r="V16" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="W16" s="10"/>
+        <v>36</v>
+      </c>
+      <c r="W16" s="10">
+        <v>-610</v>
+      </c>
       <c r="X16" s="12" t="str">
         <f ca="1">IF(Tabela1[[#This Row],[DATA_CURSO]]="",
 "PENDENTE",
@@ -3579,7 +3572,7 @@
 "VENCIDO – "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa"),
 "EM DIA – vence em "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa")),
 "NÃO É NECESSÁRIO RENOVAR")))</f>
-        <v>EM DIA – não é necessário renovar</v>
+        <v>EM DIA – vence em 26/06/27</v>
       </c>
       <c r="Y16" s="12" t="str">
         <f>IF(Tabela1[[#This Row],[FILIAL]]=1,"SINOP",IF(Tabela1[[#This Row],[FILIAL]]=2,"DOURADOS",IF(Tabela1[[#This Row],[FILIAL]]=3,"NOVA MUTUM",IF(Tabela1[[#This Row],[FILIAL]]=4,"FULLING",IF(Tabela1[[#This Row],[FILIAL]]=5,"SÃO PAULO",IF(Tabela1[[#This Row],[FILIAL]]=6,"SIDROLÂNDIA",IF(Tabela1[[#This Row],[FILIAL]]=8,"BALSAS",IF(Tabela1[[#This Row],[FILIAL]]=10,"LUIS EDUARDO MAGALHÃES",""))))))))</f>
@@ -3592,18 +3585,18 @@
       <c r="AA16" t="str">
         <f ca="1">CONCATENATE("• ",
     Tabela1[[#This Row],[DESCRICAO]], " - ",Tabela1[[#This Row],[STATUS_GERAL]])</f>
-        <v>• NR 26 - SINALIZAÇÃO DE SEGURANÇA - EM DIA – não é necessário renovar</v>
-      </c>
-    </row>
-    <row r="17" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A17" s="19">
-        <v>3</v>
+        <v>• NR 35 - TRABALHO EM ALTURA - EM DIA – vence em 26/06/27</v>
+      </c>
+    </row>
+    <row r="17" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A17" s="10">
+        <v>45</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C17" s="8">
-        <v>43683</v>
+        <v>43570</v>
       </c>
       <c r="D17" s="7" t="s">
         <v>110</v>
@@ -3621,22 +3614,22 @@
         <v>125</v>
       </c>
       <c r="I17" s="6">
-        <v>134</v>
+        <v>172</v>
       </c>
       <c r="J17" s="6">
-        <v>5076</v>
+        <v>5058</v>
       </c>
       <c r="K17" s="7" t="s">
         <v>126</v>
       </c>
       <c r="L17" s="6">
-        <v>200</v>
+        <v>308</v>
       </c>
       <c r="M17" s="7" t="s">
         <v>99</v>
       </c>
       <c r="N17" s="9" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="O17" s="9"/>
       <c r="P17" s="9" t="s">
@@ -3646,22 +3639,22 @@
         <v>1</v>
       </c>
       <c r="R17" s="10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S17" s="10">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="T17" s="9" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="U17" s="11">
-        <v>45911</v>
+        <v>44889</v>
       </c>
       <c r="V17" s="9" t="s">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="W17" s="10">
-        <v>-322</v>
+        <v>-30</v>
       </c>
       <c r="X17" s="12" t="str">
         <f ca="1">IF(Tabela1[[#This Row],[DATA_CURSO]]="",
@@ -3673,11 +3666,11 @@
 "VENCIDO – "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa"),
 "EM DIA – vence em "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa")),
 "NÃO É NECESSÁRIO RENOVAR")))</f>
-        <v>EM DIA – vence em 11/09/26</v>
+        <v>EM DIA – vence em 23/11/25</v>
       </c>
       <c r="Y17" s="12" t="str">
         <f>IF(Tabela1[[#This Row],[FILIAL]]=1,"SINOP",IF(Tabela1[[#This Row],[FILIAL]]=2,"DOURADOS",IF(Tabela1[[#This Row],[FILIAL]]=3,"NOVA MUTUM",IF(Tabela1[[#This Row],[FILIAL]]=4,"FULLING",IF(Tabela1[[#This Row],[FILIAL]]=5,"SÃO PAULO",IF(Tabela1[[#This Row],[FILIAL]]=6,"SIDROLÂNDIA",IF(Tabela1[[#This Row],[FILIAL]]=8,"BALSAS",IF(Tabela1[[#This Row],[FILIAL]]=10,"LUIS EDUARDO MAGALHÃES",""))))))))</f>
-        <v>NOVA MUTUM</v>
+        <v>SINOP</v>
       </c>
       <c r="Z17" s="13" t="str">
         <f>VLOOKUP(N17,RENOVAÇÃO!A:D,4,0)</f>
@@ -3686,18 +3679,18 @@
       <c r="AA17" t="str">
         <f ca="1">CONCATENATE("• ",
     Tabela1[[#This Row],[DESCRICAO]], " - ",Tabela1[[#This Row],[STATUS_GERAL]])</f>
-        <v>• NR 33 - SEGURANÇA E SAUDE NOS TRABALHOS EM ESPAÇOS CONFINADOS - VIGIA E TRABALHADOR - EM DIA – vence em 11/09/26</v>
+        <v>• NR 20 - SEG. E TRAB. INFLAMÁVEIS E COMBUSTIVEIS CLASSE III - BASICO - EM DIA – vence em 23/11/25</v>
       </c>
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A18" s="19">
-        <v>3</v>
+      <c r="A18" s="10">
+        <v>45</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C18" s="8">
-        <v>43683</v>
+        <v>43570</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>110</v>
@@ -3715,22 +3708,22 @@
         <v>125</v>
       </c>
       <c r="I18" s="6">
-        <v>134</v>
+        <v>172</v>
       </c>
       <c r="J18" s="6">
-        <v>5076</v>
+        <v>5058</v>
       </c>
       <c r="K18" s="7" t="s">
         <v>126</v>
       </c>
       <c r="L18" s="6">
-        <v>320</v>
+        <v>295</v>
       </c>
       <c r="M18" s="7" t="s">
         <v>99</v>
       </c>
       <c r="N18" s="9" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="O18" s="9"/>
       <c r="P18" s="9" t="s">
@@ -3740,22 +3733,22 @@
         <v>1</v>
       </c>
       <c r="R18" s="10">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="S18" s="10">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="T18" s="9" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="U18" s="11">
-        <v>44887</v>
+        <v>45404</v>
       </c>
       <c r="V18" s="9" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="W18" s="10">
-        <v>337</v>
+        <v>-545</v>
       </c>
       <c r="X18" s="12" t="str">
         <f ca="1">IF(Tabela1[[#This Row],[DATA_CURSO]]="",
@@ -3767,11 +3760,11 @@
 "VENCIDO – "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa"),
 "EM DIA – vence em "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa")),
 "NÃO É NECESSÁRIO RENOVAR")))</f>
-        <v>VENCIDO – 21/11/24</v>
+        <v>EM DIA – vence em 22/04/27</v>
       </c>
       <c r="Y18" s="12" t="str">
         <f>IF(Tabela1[[#This Row],[FILIAL]]=1,"SINOP",IF(Tabela1[[#This Row],[FILIAL]]=2,"DOURADOS",IF(Tabela1[[#This Row],[FILIAL]]=3,"NOVA MUTUM",IF(Tabela1[[#This Row],[FILIAL]]=4,"FULLING",IF(Tabela1[[#This Row],[FILIAL]]=5,"SÃO PAULO",IF(Tabela1[[#This Row],[FILIAL]]=6,"SIDROLÂNDIA",IF(Tabela1[[#This Row],[FILIAL]]=8,"BALSAS",IF(Tabela1[[#This Row],[FILIAL]]=10,"LUIS EDUARDO MAGALHÃES",""))))))))</f>
-        <v>SINOP</v>
+        <v>BALSAS</v>
       </c>
       <c r="Z18" s="13" t="str">
         <f>VLOOKUP(N18,RENOVAÇÃO!A:D,4,0)</f>
@@ -3780,18 +3773,18 @@
       <c r="AA18" t="str">
         <f ca="1">CONCATENATE("• ",
     Tabela1[[#This Row],[DESCRICAO]], " - ",Tabela1[[#This Row],[STATUS_GERAL]])</f>
-        <v>• NR 11 - OPERAÇÃO DE TALHAS E PONTE ROLANTE - VENCIDO – 21/11/24</v>
-      </c>
-    </row>
-    <row r="19" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A19" s="19">
-        <v>3</v>
+        <v>• NR 20 - SEG. E TRAB. INFLAMÁVEIS E COMBUSTIVEIS CLASSE III - BASICO - EM DIA – vence em 22/04/27</v>
+      </c>
+    </row>
+    <row r="19" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A19" s="10">
+        <v>59</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C19" s="8">
-        <v>43683</v>
+        <v>43570</v>
       </c>
       <c r="D19" s="7" t="s">
         <v>110</v>
@@ -3809,22 +3802,22 @@
         <v>125</v>
       </c>
       <c r="I19" s="6">
-        <v>134</v>
+        <v>172</v>
       </c>
       <c r="J19" s="6">
-        <v>5076</v>
+        <v>5058</v>
       </c>
       <c r="K19" s="7" t="s">
         <v>126</v>
       </c>
       <c r="L19" s="6">
-        <v>129</v>
+        <v>302</v>
       </c>
       <c r="M19" s="7" t="s">
         <v>99</v>
       </c>
       <c r="N19" s="9" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="O19" s="9"/>
       <c r="P19" s="9" t="s">
@@ -3843,12 +3836,14 @@
         <v>106</v>
       </c>
       <c r="U19" s="11">
-        <v>44608</v>
+        <v>45607</v>
       </c>
       <c r="V19" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="W19" s="10"/>
+        <v>13</v>
+      </c>
+      <c r="W19" s="10">
+        <v>-18</v>
+      </c>
       <c r="X19" s="12" t="str">
         <f ca="1">IF(Tabela1[[#This Row],[DATA_CURSO]]="",
 "PENDENTE",
@@ -3859,7 +3854,7 @@
 "VENCIDO – "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa"),
 "EM DIA – vence em "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa")),
 "NÃO É NECESSÁRIO RENOVAR")))</f>
-        <v>EM DIA – não é necessário renovar</v>
+        <v>EM DIA – vence em 11/11/25</v>
       </c>
       <c r="Y19" s="12" t="str">
         <f>IF(Tabela1[[#This Row],[FILIAL]]=1,"SINOP",IF(Tabela1[[#This Row],[FILIAL]]=2,"DOURADOS",IF(Tabela1[[#This Row],[FILIAL]]=3,"NOVA MUTUM",IF(Tabela1[[#This Row],[FILIAL]]=4,"FULLING",IF(Tabela1[[#This Row],[FILIAL]]=5,"SÃO PAULO",IF(Tabela1[[#This Row],[FILIAL]]=6,"SIDROLÂNDIA",IF(Tabela1[[#This Row],[FILIAL]]=8,"BALSAS",IF(Tabela1[[#This Row],[FILIAL]]=10,"LUIS EDUARDO MAGALHÃES",""))))))))</f>
@@ -3872,18 +3867,18 @@
       <c r="AA19" t="str">
         <f ca="1">CONCATENATE("• ",
     Tabela1[[#This Row],[DESCRICAO]], " - ",Tabela1[[#This Row],[STATUS_GERAL]])</f>
-        <v>• NR 13 - SEGURANÇA NA OPERAÇÃO VASOS DE PRESSÃO - EM DIA – não é necessário renovar</v>
-      </c>
-    </row>
-    <row r="20" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A20" s="19">
-        <v>3</v>
+        <v>• NR 20 - SEG. E TRAB. INFLAMÁVEIS E COMBUSTIVEIS CLASSE III - AVANÇADO - EM DIA – vence em 11/11/25</v>
+      </c>
+    </row>
+    <row r="20" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A20" s="10">
+        <v>59</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C20" s="8">
-        <v>43683</v>
+        <v>43570</v>
       </c>
       <c r="D20" s="7" t="s">
         <v>110</v>
@@ -3901,22 +3896,22 @@
         <v>125</v>
       </c>
       <c r="I20" s="6">
-        <v>134</v>
+        <v>172</v>
       </c>
       <c r="J20" s="6">
-        <v>5076</v>
+        <v>5058</v>
       </c>
       <c r="K20" s="7" t="s">
         <v>126</v>
       </c>
       <c r="L20" s="6">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="M20" s="7" t="s">
         <v>99</v>
       </c>
       <c r="N20" s="9" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="O20" s="9"/>
       <c r="P20" s="9" t="s">
@@ -3935,12 +3930,14 @@
         <v>106</v>
       </c>
       <c r="U20" s="11">
-        <v>45489</v>
+        <v>45707</v>
       </c>
       <c r="V20" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="W20" s="10"/>
+        <v>13</v>
+      </c>
+      <c r="W20" s="10">
+        <v>-118</v>
+      </c>
       <c r="X20" s="12" t="str">
         <f ca="1">IF(Tabela1[[#This Row],[DATA_CURSO]]="",
 "PENDENTE",
@@ -3951,7 +3948,7 @@
 "VENCIDO – "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa"),
 "EM DIA – vence em "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa")),
 "NÃO É NECESSÁRIO RENOVAR")))</f>
-        <v>EM DIA – não é necessário renovar</v>
+        <v>EM DIA – vence em 19/02/26</v>
       </c>
       <c r="Y20" s="12" t="str">
         <f>IF(Tabela1[[#This Row],[FILIAL]]=1,"SINOP",IF(Tabela1[[#This Row],[FILIAL]]=2,"DOURADOS",IF(Tabela1[[#This Row],[FILIAL]]=3,"NOVA MUTUM",IF(Tabela1[[#This Row],[FILIAL]]=4,"FULLING",IF(Tabela1[[#This Row],[FILIAL]]=5,"SÃO PAULO",IF(Tabela1[[#This Row],[FILIAL]]=6,"SIDROLÂNDIA",IF(Tabela1[[#This Row],[FILIAL]]=8,"BALSAS",IF(Tabela1[[#This Row],[FILIAL]]=10,"LUIS EDUARDO MAGALHÃES",""))))))))</f>
@@ -3964,18 +3961,18 @@
       <c r="AA20" t="str">
         <f ca="1">CONCATENATE("• ",
     Tabela1[[#This Row],[DESCRICAO]], " - ",Tabela1[[#This Row],[STATUS_GERAL]])</f>
-        <v>• NR 26 - SINALIZAÇÃO DE SEGURANÇA - EM DIA – não é necessário renovar</v>
+        <v>• NR 33 - SEGURANÇA E SAUDE NOS TRABALHOS EM ESPAÇOS CONFINADOS - VIGIA E TRABALHADOR - EM DIA – vence em 19/02/26</v>
       </c>
     </row>
     <row r="21" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A21" s="19">
-        <v>3</v>
+      <c r="A21" s="10">
+        <v>59</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C21" s="8">
-        <v>43683</v>
+        <v>43570</v>
       </c>
       <c r="D21" s="7" t="s">
         <v>110</v>
@@ -3993,22 +3990,22 @@
         <v>125</v>
       </c>
       <c r="I21" s="6">
-        <v>134</v>
+        <v>172</v>
       </c>
       <c r="J21" s="6">
-        <v>5076</v>
+        <v>5058</v>
       </c>
       <c r="K21" s="7" t="s">
         <v>126</v>
       </c>
       <c r="L21" s="6">
-        <v>271</v>
+        <v>319</v>
       </c>
       <c r="M21" s="7" t="s">
         <v>99</v>
       </c>
       <c r="N21" s="9" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="O21" s="9"/>
       <c r="P21" s="9" t="s">
@@ -4018,7 +4015,7 @@
         <v>1</v>
       </c>
       <c r="R21" s="10">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="S21" s="10">
         <v>102</v>
@@ -4027,14 +4024,12 @@
         <v>106</v>
       </c>
       <c r="U21" s="11">
-        <v>45502</v>
+        <v>45489</v>
       </c>
       <c r="V21" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="W21" s="10">
-        <v>-643</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="W21" s="10"/>
       <c r="X21" s="12" t="str">
         <f ca="1">IF(Tabela1[[#This Row],[DATA_CURSO]]="",
 "PENDENTE",
@@ -4045,11 +4040,11 @@
 "VENCIDO – "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa"),
 "EM DIA – vence em "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa")),
 "NÃO É NECESSÁRIO RENOVAR")))</f>
-        <v>EM DIA – vence em 29/07/27</v>
+        <v>EM DIA – não é necessário renovar</v>
       </c>
       <c r="Y21" s="12" t="str">
         <f>IF(Tabela1[[#This Row],[FILIAL]]=1,"SINOP",IF(Tabela1[[#This Row],[FILIAL]]=2,"DOURADOS",IF(Tabela1[[#This Row],[FILIAL]]=3,"NOVA MUTUM",IF(Tabela1[[#This Row],[FILIAL]]=4,"FULLING",IF(Tabela1[[#This Row],[FILIAL]]=5,"SÃO PAULO",IF(Tabela1[[#This Row],[FILIAL]]=6,"SIDROLÂNDIA",IF(Tabela1[[#This Row],[FILIAL]]=8,"BALSAS",IF(Tabela1[[#This Row],[FILIAL]]=10,"LUIS EDUARDO MAGALHÃES",""))))))))</f>
-        <v>NOVA MUTUM</v>
+        <v>BALSAS</v>
       </c>
       <c r="Z21" s="13" t="str">
         <f>VLOOKUP(N21,RENOVAÇÃO!A:D,4,0)</f>
@@ -4058,18 +4053,18 @@
       <c r="AA21" t="str">
         <f ca="1">CONCATENATE("• ",
     Tabela1[[#This Row],[DESCRICAO]], " - ",Tabela1[[#This Row],[STATUS_GERAL]])</f>
-        <v>• NR 20 - SEG. E TRAB. INFLAMÁVEIS E COMBUSTIVEIS CLASSE III - BASICO - EM DIA – vence em 29/07/27</v>
+        <v>• NR 26 - SINALIZAÇÃO DE SEGURANÇA - EM DIA – não é necessário renovar</v>
       </c>
     </row>
     <row r="22" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A22" s="19">
-        <v>3</v>
+      <c r="A22" s="10">
+        <v>59</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C22" s="8">
-        <v>43683</v>
+        <v>43570</v>
       </c>
       <c r="D22" s="7" t="s">
         <v>110</v>
@@ -4087,22 +4082,22 @@
         <v>125</v>
       </c>
       <c r="I22" s="6">
-        <v>134</v>
+        <v>172</v>
       </c>
       <c r="J22" s="6">
-        <v>5076</v>
+        <v>5058</v>
       </c>
       <c r="K22" s="7" t="s">
         <v>126</v>
       </c>
       <c r="L22" s="6">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="M22" s="7" t="s">
         <v>99</v>
       </c>
       <c r="N22" s="9" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="O22" s="9"/>
       <c r="P22" s="9" t="s">
@@ -4112,23 +4107,21 @@
         <v>1</v>
       </c>
       <c r="R22" s="10">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="S22" s="10">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="T22" s="9" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="U22" s="11">
-        <v>45870</v>
+        <v>44851</v>
       </c>
       <c r="V22" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="W22" s="10">
-        <v>-646</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="W22" s="10"/>
       <c r="X22" s="12" t="str">
         <f ca="1">IF(Tabela1[[#This Row],[DATA_CURSO]]="",
 "PENDENTE",
@@ -4139,11 +4132,11 @@
 "VENCIDO – "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa"),
 "EM DIA – vence em "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa")),
 "NÃO É NECESSÁRIO RENOVAR")))</f>
-        <v>EM DIA – vence em 01/08/27</v>
+        <v>EM DIA – não é necessário renovar</v>
       </c>
       <c r="Y22" s="12" t="str">
         <f>IF(Tabela1[[#This Row],[FILIAL]]=1,"SINOP",IF(Tabela1[[#This Row],[FILIAL]]=2,"DOURADOS",IF(Tabela1[[#This Row],[FILIAL]]=3,"NOVA MUTUM",IF(Tabela1[[#This Row],[FILIAL]]=4,"FULLING",IF(Tabela1[[#This Row],[FILIAL]]=5,"SÃO PAULO",IF(Tabela1[[#This Row],[FILIAL]]=6,"SIDROLÂNDIA",IF(Tabela1[[#This Row],[FILIAL]]=8,"BALSAS",IF(Tabela1[[#This Row],[FILIAL]]=10,"LUIS EDUARDO MAGALHÃES",""))))))))</f>
-        <v>SIDROLÂNDIA</v>
+        <v>NOVA MUTUM</v>
       </c>
       <c r="Z22" s="13" t="str">
         <f>VLOOKUP(N22,RENOVAÇÃO!A:D,4,0)</f>
@@ -4152,18 +4145,18 @@
       <c r="AA22" t="str">
         <f ca="1">CONCATENATE("• ",
     Tabela1[[#This Row],[DESCRICAO]], " - ",Tabela1[[#This Row],[STATUS_GERAL]])</f>
-        <v>• NR 10 - SEGURANÇA EM INSTALAÇÕES E SERVIÇOS EM ELETRICIDADE ( BASÍCO) - EM DIA – vence em 01/08/27</v>
-      </c>
-    </row>
-    <row r="23" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A23" s="19">
-        <v>3</v>
+        <v>• BLOQUEIO E SINALIZAÇÃO DE ENERGIAS PERIGOSAS - LOCKOUT/TAGOUT - NR10 E NR12 - EM DIA – não é necessário renovar</v>
+      </c>
+    </row>
+    <row r="23" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A23" s="10">
+        <v>59</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C23" s="8">
-        <v>43683</v>
+        <v>43570</v>
       </c>
       <c r="D23" s="7" t="s">
         <v>110</v>
@@ -4181,22 +4174,22 @@
         <v>125</v>
       </c>
       <c r="I23" s="6">
-        <v>134</v>
+        <v>172</v>
       </c>
       <c r="J23" s="6">
-        <v>5076</v>
+        <v>5058</v>
       </c>
       <c r="K23" s="7" t="s">
         <v>126</v>
       </c>
       <c r="L23" s="6">
-        <v>104</v>
+        <v>123</v>
       </c>
       <c r="M23" s="7" t="s">
         <v>99</v>
       </c>
       <c r="N23" s="9" t="s">
-        <v>109</v>
+        <v>49</v>
       </c>
       <c r="O23" s="9"/>
       <c r="P23" s="9" t="s">
@@ -4215,12 +4208,14 @@
         <v>101</v>
       </c>
       <c r="U23" s="11">
-        <v>44582</v>
+        <v>45827</v>
       </c>
       <c r="V23" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="W23" s="10"/>
+        <v>36</v>
+      </c>
+      <c r="W23" s="10">
+        <v>-603</v>
+      </c>
       <c r="X23" s="12" t="str">
         <f ca="1">IF(Tabela1[[#This Row],[DATA_CURSO]]="",
 "PENDENTE",
@@ -4231,7 +4226,7 @@
 "VENCIDO – "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa"),
 "EM DIA – vence em "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa")),
 "NÃO É NECESSÁRIO RENOVAR")))</f>
-        <v>EM DIA – não é necessário renovar</v>
+        <v>EM DIA – vence em 19/06/27</v>
       </c>
       <c r="Y23" s="12" t="str">
         <f>IF(Tabela1[[#This Row],[FILIAL]]=1,"SINOP",IF(Tabela1[[#This Row],[FILIAL]]=2,"DOURADOS",IF(Tabela1[[#This Row],[FILIAL]]=3,"NOVA MUTUM",IF(Tabela1[[#This Row],[FILIAL]]=4,"FULLING",IF(Tabela1[[#This Row],[FILIAL]]=5,"SÃO PAULO",IF(Tabela1[[#This Row],[FILIAL]]=6,"SIDROLÂNDIA",IF(Tabela1[[#This Row],[FILIAL]]=8,"BALSAS",IF(Tabela1[[#This Row],[FILIAL]]=10,"LUIS EDUARDO MAGALHÃES",""))))))))</f>
@@ -4244,18 +4239,18 @@
       <c r="AA23" t="str">
         <f ca="1">CONCATENATE("• ",
     Tabela1[[#This Row],[DESCRICAO]], " - ",Tabela1[[#This Row],[STATUS_GERAL]])</f>
-        <v>• BLOQUEIO E SINALIZAÇÃO DE ENERGIAS PERIGOSAS - LOCKOUT/TAGOUT - NR10 E NR12 - EM DIA – não é necessário renovar</v>
-      </c>
-    </row>
-    <row r="24" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A24" s="19">
-        <v>3</v>
+        <v>• NR 35 - TRABALHO EM ALTURA - EM DIA – vence em 19/06/27</v>
+      </c>
+    </row>
+    <row r="24" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A24" s="10">
+        <v>68</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C24" s="8">
-        <v>43683</v>
+        <v>43570</v>
       </c>
       <c r="D24" s="7" t="s">
         <v>110</v>
@@ -4273,22 +4268,22 @@
         <v>125</v>
       </c>
       <c r="I24" s="6">
-        <v>134</v>
+        <v>172</v>
       </c>
       <c r="J24" s="6">
-        <v>5076</v>
+        <v>5058</v>
       </c>
       <c r="K24" s="7" t="s">
         <v>126</v>
       </c>
       <c r="L24" s="6">
-        <v>2</v>
+        <v>235</v>
       </c>
       <c r="M24" s="7" t="s">
         <v>99</v>
       </c>
       <c r="N24" s="9" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="O24" s="9"/>
       <c r="P24" s="9" t="s">
@@ -4298,22 +4293,22 @@
         <v>1</v>
       </c>
       <c r="R24" s="10">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="S24" s="10">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="T24" s="9" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="U24" s="11">
-        <v>45374</v>
+        <v>45889</v>
       </c>
       <c r="V24" s="9" t="s">
         <v>36</v>
       </c>
       <c r="W24" s="10">
-        <v>-150</v>
+        <v>-665</v>
       </c>
       <c r="X24" s="12" t="str">
         <f ca="1">IF(Tabela1[[#This Row],[DATA_CURSO]]="",
@@ -4325,11 +4320,11 @@
 "VENCIDO – "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa"),
 "EM DIA – vence em "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa")),
 "NÃO É NECESSÁRIO RENOVAR")))</f>
-        <v>EM DIA – vence em 23/03/26</v>
+        <v>EM DIA – vence em 20/08/27</v>
       </c>
       <c r="Y24" s="12" t="str">
         <f>IF(Tabela1[[#This Row],[FILIAL]]=1,"SINOP",IF(Tabela1[[#This Row],[FILIAL]]=2,"DOURADOS",IF(Tabela1[[#This Row],[FILIAL]]=3,"NOVA MUTUM",IF(Tabela1[[#This Row],[FILIAL]]=4,"FULLING",IF(Tabela1[[#This Row],[FILIAL]]=5,"SÃO PAULO",IF(Tabela1[[#This Row],[FILIAL]]=6,"SIDROLÂNDIA",IF(Tabela1[[#This Row],[FILIAL]]=8,"BALSAS",IF(Tabela1[[#This Row],[FILIAL]]=10,"LUIS EDUARDO MAGALHÃES",""))))))))</f>
-        <v>SINOP</v>
+        <v>BALSAS</v>
       </c>
       <c r="Z24" s="13" t="str">
         <f>VLOOKUP(N24,RENOVAÇÃO!A:D,4,0)</f>
@@ -4338,12 +4333,12 @@
       <c r="AA24" t="str">
         <f ca="1">CONCATENATE("• ",
     Tabela1[[#This Row],[DESCRICAO]], " - ",Tabela1[[#This Row],[STATUS_GERAL]])</f>
-        <v>• NR 35 - TRABALHO EM ALTURA - EM DIA – vence em 23/03/26</v>
+        <v>• NR 20 - SEG. E TRAB. INFLAMÁVEIS E COMBUSTIVEIS CLASSE III - INTERMEDIÁRIO - EM DIA – vence em 20/08/27</v>
       </c>
     </row>
     <row r="25" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A25" s="19">
-        <v>1</v>
+      <c r="A25" s="10">
+        <v>70</v>
       </c>
       <c r="B25" s="7" t="s">
         <v>121</v>
@@ -4376,39 +4371,33 @@
         <v>126</v>
       </c>
       <c r="L25" s="6">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="M25" s="7" t="s">
         <v>99</v>
       </c>
       <c r="N25" s="9" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="O25" s="9"/>
-      <c r="P25" s="9" t="s">
-        <v>100</v>
-      </c>
+      <c r="P25" s="9"/>
       <c r="Q25" s="10">
         <v>1</v>
       </c>
       <c r="R25" s="10">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="S25" s="10">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="T25" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="U25" s="11">
-        <v>45405</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="U25" s="9"/>
       <c r="V25" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="W25" s="10">
-        <v>-181</v>
-      </c>
+      <c r="W25" s="10"/>
       <c r="X25" s="12" t="str">
         <f ca="1">IF(Tabela1[[#This Row],[DATA_CURSO]]="",
 "PENDENTE",
@@ -4419,11 +4408,11 @@
 "VENCIDO – "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa"),
 "EM DIA – vence em "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa")),
 "NÃO É NECESSÁRIO RENOVAR")))</f>
-        <v>EM DIA – vence em 23/04/26</v>
+        <v>PENDENTE</v>
       </c>
       <c r="Y25" s="12" t="str">
         <f>IF(Tabela1[[#This Row],[FILIAL]]=1,"SINOP",IF(Tabela1[[#This Row],[FILIAL]]=2,"DOURADOS",IF(Tabela1[[#This Row],[FILIAL]]=3,"NOVA MUTUM",IF(Tabela1[[#This Row],[FILIAL]]=4,"FULLING",IF(Tabela1[[#This Row],[FILIAL]]=5,"SÃO PAULO",IF(Tabela1[[#This Row],[FILIAL]]=6,"SIDROLÂNDIA",IF(Tabela1[[#This Row],[FILIAL]]=8,"BALSAS",IF(Tabela1[[#This Row],[FILIAL]]=10,"LUIS EDUARDO MAGALHÃES",""))))))))</f>
-        <v>SINOP</v>
+        <v>BALSAS</v>
       </c>
       <c r="Z25" s="13" t="str">
         <f>VLOOKUP(N25,RENOVAÇÃO!A:D,4,0)</f>
@@ -4432,12 +4421,12 @@
       <c r="AA25" t="str">
         <f ca="1">CONCATENATE("• ",
     Tabela1[[#This Row],[DESCRICAO]], " - ",Tabela1[[#This Row],[STATUS_GERAL]])</f>
-        <v>• NR 35 - TRABALHO EM ALTURA - EM DIA – vence em 23/04/26</v>
-      </c>
-    </row>
-    <row r="26" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A26" s="19">
-        <v>1</v>
+        <v>• NR 11 - OPERAÇÃO DE TALHAS E PONTE ROLANTE - PENDENTE</v>
+      </c>
+    </row>
+    <row r="26" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A26" s="10">
+        <v>70</v>
       </c>
       <c r="B26" s="7" t="s">
         <v>121</v>
@@ -4470,13 +4459,13 @@
         <v>126</v>
       </c>
       <c r="L26" s="6">
-        <v>271</v>
+        <v>323</v>
       </c>
       <c r="M26" s="7" t="s">
         <v>99</v>
       </c>
       <c r="N26" s="9" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="O26" s="9"/>
       <c r="P26" s="9" t="s">
@@ -4489,19 +4478,19 @@
         <v>1</v>
       </c>
       <c r="S26" s="10">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="T26" s="9" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="U26" s="11">
-        <v>45875</v>
+        <v>45709</v>
       </c>
       <c r="V26" s="9" t="s">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="W26" s="10">
-        <v>-1016</v>
+        <v>-120</v>
       </c>
       <c r="X26" s="12" t="str">
         <f ca="1">IF(Tabela1[[#This Row],[DATA_CURSO]]="",
@@ -4513,7 +4502,7 @@
 "VENCIDO – "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa"),
 "EM DIA – vence em "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa")),
 "NÃO É NECESSÁRIO RENOVAR")))</f>
-        <v>EM DIA – vence em 05/08/28</v>
+        <v>EM DIA – vence em 21/02/26</v>
       </c>
       <c r="Y26" s="12" t="str">
         <f>IF(Tabela1[[#This Row],[FILIAL]]=1,"SINOP",IF(Tabela1[[#This Row],[FILIAL]]=2,"DOURADOS",IF(Tabela1[[#This Row],[FILIAL]]=3,"NOVA MUTUM",IF(Tabela1[[#This Row],[FILIAL]]=4,"FULLING",IF(Tabela1[[#This Row],[FILIAL]]=5,"SÃO PAULO",IF(Tabela1[[#This Row],[FILIAL]]=6,"SIDROLÂNDIA",IF(Tabela1[[#This Row],[FILIAL]]=8,"BALSAS",IF(Tabela1[[#This Row],[FILIAL]]=10,"LUIS EDUARDO MAGALHÃES",""))))))))</f>
@@ -4526,18 +4515,18 @@
       <c r="AA26" t="str">
         <f ca="1">CONCATENATE("• ",
     Tabela1[[#This Row],[DESCRICAO]], " - ",Tabela1[[#This Row],[STATUS_GERAL]])</f>
-        <v>• NR 20 - SEG. E TRAB. INFLAMÁVEIS E COMBUSTIVEIS CLASSE III - BASICO - EM DIA – vence em 05/08/28</v>
+        <v>• NR 33 - SEGURANÇA E SAUDE NOS TRABALHOS EM ESPAÇOS CONFINADOS - VIGIA E TRABALHADOR - EM DIA – vence em 21/02/26</v>
       </c>
     </row>
     <row r="27" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A27" s="19">
-        <v>1</v>
+      <c r="A27" s="10">
+        <v>70</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C27" s="8">
-        <v>43570</v>
+        <v>43587</v>
       </c>
       <c r="D27" s="7" t="s">
         <v>110</v>
@@ -4555,22 +4544,22 @@
         <v>125</v>
       </c>
       <c r="I27" s="6">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="J27" s="6">
-        <v>5058</v>
+        <v>5060</v>
       </c>
       <c r="K27" s="7" t="s">
         <v>126</v>
       </c>
       <c r="L27" s="6">
-        <v>200</v>
+        <v>123</v>
       </c>
       <c r="M27" s="7" t="s">
         <v>99</v>
       </c>
       <c r="N27" s="9" t="s">
-        <v>109</v>
+        <v>42</v>
       </c>
       <c r="O27" s="9"/>
       <c r="P27" s="9" t="s">
@@ -4589,12 +4578,14 @@
         <v>106</v>
       </c>
       <c r="U27" s="11">
-        <v>44883</v>
+        <v>45601</v>
       </c>
       <c r="V27" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="W27" s="10"/>
+        <v>13</v>
+      </c>
+      <c r="W27" s="10">
+        <v>-12</v>
+      </c>
       <c r="X27" s="12" t="str">
         <f ca="1">IF(Tabela1[[#This Row],[DATA_CURSO]]="",
 "PENDENTE",
@@ -4605,7 +4596,7 @@
 "VENCIDO – "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa"),
 "EM DIA – vence em "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa")),
 "NÃO É NECESSÁRIO RENOVAR")))</f>
-        <v>EM DIA – não é necessário renovar</v>
+        <v>EM DIA – vence em 05/11/25</v>
       </c>
       <c r="Y27" s="12" t="str">
         <f>IF(Tabela1[[#This Row],[FILIAL]]=1,"SINOP",IF(Tabela1[[#This Row],[FILIAL]]=2,"DOURADOS",IF(Tabela1[[#This Row],[FILIAL]]=3,"NOVA MUTUM",IF(Tabela1[[#This Row],[FILIAL]]=4,"FULLING",IF(Tabela1[[#This Row],[FILIAL]]=5,"SÃO PAULO",IF(Tabela1[[#This Row],[FILIAL]]=6,"SIDROLÂNDIA",IF(Tabela1[[#This Row],[FILIAL]]=8,"BALSAS",IF(Tabela1[[#This Row],[FILIAL]]=10,"LUIS EDUARDO MAGALHÃES",""))))))))</f>
@@ -4618,18 +4609,18 @@
       <c r="AA27" t="str">
         <f ca="1">CONCATENATE("• ",
     Tabela1[[#This Row],[DESCRICAO]], " - ",Tabela1[[#This Row],[STATUS_GERAL]])</f>
-        <v>• BLOQUEIO E SINALIZAÇÃO DE ENERGIAS PERIGOSAS - LOCKOUT/TAGOUT - NR10 E NR12 - EM DIA – não é necessário renovar</v>
+        <v>• NR 20 - SEG. E TRAB. INFLAMÁVEIS E COMBUSTIVEIS CLASSE III - AVANÇADO - EM DIA – vence em 05/11/25</v>
       </c>
     </row>
     <row r="28" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A28" s="19">
-        <v>1</v>
+      <c r="A28" s="10">
+        <v>70</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C28" s="8">
-        <v>43570</v>
+        <v>43587</v>
       </c>
       <c r="D28" s="7" t="s">
         <v>110</v>
@@ -4647,22 +4638,22 @@
         <v>125</v>
       </c>
       <c r="I28" s="6">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="J28" s="6">
-        <v>5058</v>
+        <v>5060</v>
       </c>
       <c r="K28" s="7" t="s">
         <v>126</v>
       </c>
       <c r="L28" s="6">
-        <v>1</v>
+        <v>295</v>
       </c>
       <c r="M28" s="7" t="s">
         <v>99</v>
       </c>
       <c r="N28" s="9" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="O28" s="9"/>
       <c r="P28" s="9" t="s">
@@ -4675,20 +4666,18 @@
         <v>1</v>
       </c>
       <c r="S28" s="10">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="T28" s="9" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="U28" s="11">
-        <v>45349</v>
+        <v>45489</v>
       </c>
       <c r="V28" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="W28" s="10">
-        <v>-125</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="W28" s="10"/>
       <c r="X28" s="12" t="str">
         <f ca="1">IF(Tabela1[[#This Row],[DATA_CURSO]]="",
 "PENDENTE",
@@ -4699,7 +4688,7 @@
 "VENCIDO – "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa"),
 "EM DIA – vence em "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa")),
 "NÃO É NECESSÁRIO RENOVAR")))</f>
-        <v>EM DIA – vence em 26/02/26</v>
+        <v>EM DIA – não é necessário renovar</v>
       </c>
       <c r="Y28" s="12" t="str">
         <f>IF(Tabela1[[#This Row],[FILIAL]]=1,"SINOP",IF(Tabela1[[#This Row],[FILIAL]]=2,"DOURADOS",IF(Tabela1[[#This Row],[FILIAL]]=3,"NOVA MUTUM",IF(Tabela1[[#This Row],[FILIAL]]=4,"FULLING",IF(Tabela1[[#This Row],[FILIAL]]=5,"SÃO PAULO",IF(Tabela1[[#This Row],[FILIAL]]=6,"SIDROLÂNDIA",IF(Tabela1[[#This Row],[FILIAL]]=8,"BALSAS",IF(Tabela1[[#This Row],[FILIAL]]=10,"LUIS EDUARDO MAGALHÃES",""))))))))</f>
@@ -4712,18 +4701,18 @@
       <c r="AA28" t="str">
         <f ca="1">CONCATENATE("• ",
     Tabela1[[#This Row],[DESCRICAO]], " - ",Tabela1[[#This Row],[STATUS_GERAL]])</f>
-        <v>• NR 35 - TRABALHO EM ALTURA - EM DIA – vence em 26/02/26</v>
+        <v>• NR 26 - SINALIZAÇÃO DE SEGURANÇA - EM DIA – não é necessário renovar</v>
       </c>
     </row>
     <row r="29" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A29" s="19">
-        <v>1</v>
+      <c r="A29" s="10">
+        <v>74</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C29" s="8">
-        <v>43570</v>
+        <v>43587</v>
       </c>
       <c r="D29" s="7" t="s">
         <v>110</v>
@@ -4741,16 +4730,16 @@
         <v>125</v>
       </c>
       <c r="I29" s="6">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="J29" s="6">
-        <v>5058</v>
+        <v>5060</v>
       </c>
       <c r="K29" s="7" t="s">
         <v>126</v>
       </c>
       <c r="L29" s="6">
-        <v>262</v>
+        <v>235</v>
       </c>
       <c r="M29" s="7" t="s">
         <v>99</v>
@@ -4769,19 +4758,19 @@
         <v>1</v>
       </c>
       <c r="S29" s="10">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="T29" s="9" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="U29" s="11">
-        <v>45349</v>
+        <v>45544</v>
       </c>
       <c r="V29" s="9" t="s">
         <v>36</v>
       </c>
       <c r="W29" s="10">
-        <v>-125</v>
+        <v>-320</v>
       </c>
       <c r="X29" s="12" t="str">
         <f ca="1">IF(Tabela1[[#This Row],[DATA_CURSO]]="",
@@ -4793,7 +4782,7 @@
 "VENCIDO – "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa"),
 "EM DIA – vence em "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa")),
 "NÃO É NECESSÁRIO RENOVAR")))</f>
-        <v>EM DIA – vence em 26/02/26</v>
+        <v>EM DIA – vence em 09/09/26</v>
       </c>
       <c r="Y29" s="12" t="str">
         <f>IF(Tabela1[[#This Row],[FILIAL]]=1,"SINOP",IF(Tabela1[[#This Row],[FILIAL]]=2,"DOURADOS",IF(Tabela1[[#This Row],[FILIAL]]=3,"NOVA MUTUM",IF(Tabela1[[#This Row],[FILIAL]]=4,"FULLING",IF(Tabela1[[#This Row],[FILIAL]]=5,"SÃO PAULO",IF(Tabela1[[#This Row],[FILIAL]]=6,"SIDROLÂNDIA",IF(Tabela1[[#This Row],[FILIAL]]=8,"BALSAS",IF(Tabela1[[#This Row],[FILIAL]]=10,"LUIS EDUARDO MAGALHÃES",""))))))))</f>
@@ -4806,18 +4795,18 @@
       <c r="AA29" t="str">
         <f ca="1">CONCATENATE("• ",
     Tabela1[[#This Row],[DESCRICAO]], " - ",Tabela1[[#This Row],[STATUS_GERAL]])</f>
-        <v>• NR 35 - TRABALHO EM ALTURA - EM DIA – vence em 26/02/26</v>
-      </c>
-    </row>
-    <row r="30" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A30" s="19">
-        <v>1</v>
+        <v>• NR 35 - TRABALHO EM ALTURA - EM DIA – vence em 09/09/26</v>
+      </c>
+    </row>
+    <row r="30" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A30" s="10">
+        <v>74</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C30" s="8">
-        <v>43570</v>
+        <v>43587</v>
       </c>
       <c r="D30" s="7" t="s">
         <v>110</v>
@@ -4835,22 +4824,22 @@
         <v>125</v>
       </c>
       <c r="I30" s="6">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="J30" s="6">
-        <v>5058</v>
+        <v>5060</v>
       </c>
       <c r="K30" s="7" t="s">
         <v>126</v>
       </c>
       <c r="L30" s="6">
-        <v>28</v>
+        <v>262</v>
       </c>
       <c r="M30" s="7" t="s">
         <v>99</v>
       </c>
       <c r="N30" s="9" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="O30" s="9"/>
       <c r="P30" s="9" t="s">
@@ -4860,21 +4849,23 @@
         <v>1</v>
       </c>
       <c r="R30" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S30" s="10">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="T30" s="9" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="U30" s="11">
-        <v>45042</v>
+        <v>45757</v>
       </c>
       <c r="V30" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="W30" s="10"/>
+        <v>13</v>
+      </c>
+      <c r="W30" s="10">
+        <v>-168</v>
+      </c>
       <c r="X30" s="12" t="str">
         <f ca="1">IF(Tabela1[[#This Row],[DATA_CURSO]]="",
 "PENDENTE",
@@ -4885,11 +4876,11 @@
 "VENCIDO – "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa"),
 "EM DIA – vence em "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa")),
 "NÃO É NECESSÁRIO RENOVAR")))</f>
-        <v>EM DIA – não é necessário renovar</v>
+        <v>EM DIA – vence em 10/04/26</v>
       </c>
       <c r="Y30" s="12" t="str">
         <f>IF(Tabela1[[#This Row],[FILIAL]]=1,"SINOP",IF(Tabela1[[#This Row],[FILIAL]]=2,"DOURADOS",IF(Tabela1[[#This Row],[FILIAL]]=3,"NOVA MUTUM",IF(Tabela1[[#This Row],[FILIAL]]=4,"FULLING",IF(Tabela1[[#This Row],[FILIAL]]=5,"SÃO PAULO",IF(Tabela1[[#This Row],[FILIAL]]=6,"SIDROLÂNDIA",IF(Tabela1[[#This Row],[FILIAL]]=8,"BALSAS",IF(Tabela1[[#This Row],[FILIAL]]=10,"LUIS EDUARDO MAGALHÃES",""))))))))</f>
-        <v>SINOP</v>
+        <v>DOURADOS</v>
       </c>
       <c r="Z30" s="13" t="str">
         <f>VLOOKUP(N30,RENOVAÇÃO!A:D,4,0)</f>
@@ -4898,18 +4889,18 @@
       <c r="AA30" t="str">
         <f ca="1">CONCATENATE("• ",
     Tabela1[[#This Row],[DESCRICAO]], " - ",Tabela1[[#This Row],[STATUS_GERAL]])</f>
-        <v>• NR 13 - SEGURANÇA NA OPERAÇÃO DE CALDEIRAS - EM DIA – não é necessário renovar</v>
+        <v>• NR 33 - SEGURANÇA E SAUDE NOS TRABALHOS EM ESPAÇOS CONFINADOS - VIGIA E TRABALHADOR - EM DIA – vence em 10/04/26</v>
       </c>
     </row>
     <row r="31" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A31" s="19">
-        <v>1</v>
+      <c r="A31" s="10">
+        <v>74</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C31" s="8">
-        <v>43570</v>
+        <v>43587</v>
       </c>
       <c r="D31" s="7" t="s">
         <v>110</v>
@@ -4927,22 +4918,22 @@
         <v>125</v>
       </c>
       <c r="I31" s="6">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="J31" s="6">
-        <v>5058</v>
+        <v>5060</v>
       </c>
       <c r="K31" s="7" t="s">
         <v>126</v>
       </c>
       <c r="L31" s="6">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="M31" s="7" t="s">
         <v>99</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>109</v>
+        <v>48</v>
       </c>
       <c r="O31" s="9"/>
       <c r="P31" s="9" t="s">
@@ -4955,18 +4946,20 @@
         <v>1</v>
       </c>
       <c r="S31" s="10">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="T31" s="9" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="U31" s="11">
-        <v>45125</v>
+        <v>45918</v>
       </c>
       <c r="V31" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="W31" s="10"/>
+        <v>13</v>
+      </c>
+      <c r="W31" s="10">
+        <v>-329</v>
+      </c>
       <c r="X31" s="12" t="str">
         <f ca="1">IF(Tabela1[[#This Row],[DATA_CURSO]]="",
 "PENDENTE",
@@ -4977,7 +4970,7 @@
 "VENCIDO – "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa"),
 "EM DIA – vence em "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa")),
 "NÃO É NECESSÁRIO RENOVAR")))</f>
-        <v>EM DIA – não é necessário renovar</v>
+        <v>EM DIA – vence em 18/09/26</v>
       </c>
       <c r="Y31" s="12" t="str">
         <f>IF(Tabela1[[#This Row],[FILIAL]]=1,"SINOP",IF(Tabela1[[#This Row],[FILIAL]]=2,"DOURADOS",IF(Tabela1[[#This Row],[FILIAL]]=3,"NOVA MUTUM",IF(Tabela1[[#This Row],[FILIAL]]=4,"FULLING",IF(Tabela1[[#This Row],[FILIAL]]=5,"SÃO PAULO",IF(Tabela1[[#This Row],[FILIAL]]=6,"SIDROLÂNDIA",IF(Tabela1[[#This Row],[FILIAL]]=8,"BALSAS",IF(Tabela1[[#This Row],[FILIAL]]=10,"LUIS EDUARDO MAGALHÃES",""))))))))</f>
@@ -4990,18 +4983,18 @@
       <c r="AA31" t="str">
         <f ca="1">CONCATENATE("• ",
     Tabela1[[#This Row],[DESCRICAO]], " - ",Tabela1[[#This Row],[STATUS_GERAL]])</f>
-        <v>• BLOQUEIO E SINALIZAÇÃO DE ENERGIAS PERIGOSAS - LOCKOUT/TAGOUT - NR10 E NR12 - EM DIA – não é necessário renovar</v>
-      </c>
-    </row>
-    <row r="32" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A32" s="19">
-        <v>1</v>
+        <v>• NR 33 - SEGURANÇA E SAUDE NOS TRABALHOS EM ESPAÇOS CONFINADOS - VIGIA E TRABALHADOR - EM DIA – vence em 18/09/26</v>
+      </c>
+    </row>
+    <row r="32" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A32" s="10">
+        <v>74</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C32" s="8">
-        <v>43570</v>
+        <v>43587</v>
       </c>
       <c r="D32" s="7" t="s">
         <v>110</v>
@@ -5019,22 +5012,22 @@
         <v>125</v>
       </c>
       <c r="I32" s="6">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="J32" s="6">
-        <v>5058</v>
+        <v>5060</v>
       </c>
       <c r="K32" s="7" t="s">
         <v>126</v>
       </c>
       <c r="L32" s="6">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="M32" s="7" t="s">
         <v>99</v>
       </c>
       <c r="N32" s="9" t="s">
-        <v>111</v>
+        <v>43</v>
       </c>
       <c r="O32" s="9"/>
       <c r="P32" s="9" t="s">
@@ -5044,22 +5037,22 @@
         <v>1</v>
       </c>
       <c r="R32" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S32" s="10">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="T32" s="9" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="U32" s="11">
-        <v>45401</v>
+        <v>45735</v>
       </c>
       <c r="V32" s="9" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="W32" s="10">
-        <v>-177</v>
+        <v>-876</v>
       </c>
       <c r="X32" s="12" t="str">
         <f ca="1">IF(Tabela1[[#This Row],[DATA_CURSO]]="",
@@ -5071,11 +5064,11 @@
 "VENCIDO – "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa"),
 "EM DIA – vence em "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa")),
 "NÃO É NECESSÁRIO RENOVAR")))</f>
-        <v>EM DIA – vence em 19/04/26</v>
+        <v>EM DIA – vence em 18/03/28</v>
       </c>
       <c r="Y32" s="12" t="str">
         <f>IF(Tabela1[[#This Row],[FILIAL]]=1,"SINOP",IF(Tabela1[[#This Row],[FILIAL]]=2,"DOURADOS",IF(Tabela1[[#This Row],[FILIAL]]=3,"NOVA MUTUM",IF(Tabela1[[#This Row],[FILIAL]]=4,"FULLING",IF(Tabela1[[#This Row],[FILIAL]]=5,"SÃO PAULO",IF(Tabela1[[#This Row],[FILIAL]]=6,"SIDROLÂNDIA",IF(Tabela1[[#This Row],[FILIAL]]=8,"BALSAS",IF(Tabela1[[#This Row],[FILIAL]]=10,"LUIS EDUARDO MAGALHÃES",""))))))))</f>
-        <v>DOURADOS</v>
+        <v>SINOP</v>
       </c>
       <c r="Z32" s="13" t="str">
         <f>VLOOKUP(N32,RENOVAÇÃO!A:D,4,0)</f>
@@ -5084,18 +5077,18 @@
       <c r="AA32" t="str">
         <f ca="1">CONCATENATE("• ",
     Tabela1[[#This Row],[DESCRICAO]], " - ",Tabela1[[#This Row],[STATUS_GERAL]])</f>
-        <v>• NR 10 - SEGURANÇA EM INSTALAÇÕES E SERVIÇOS EM ELETRICIDADE ( BASÍCO) - EM DIA – vence em 19/04/26</v>
+        <v>• NR 20 - SEG. E TRAB. INFLAMÁVEIS E COMBUSTIVEIS CLASSE III - BASICO - EM DIA – vence em 18/03/28</v>
       </c>
     </row>
     <row r="33" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A33" s="19">
-        <v>1</v>
+      <c r="A33" s="10">
+        <v>74</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C33" s="8">
-        <v>43570</v>
+        <v>43587</v>
       </c>
       <c r="D33" s="7" t="s">
         <v>110</v>
@@ -5113,22 +5106,22 @@
         <v>125</v>
       </c>
       <c r="I33" s="6">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="J33" s="6">
-        <v>5058</v>
+        <v>5060</v>
       </c>
       <c r="K33" s="7" t="s">
         <v>126</v>
       </c>
       <c r="L33" s="6">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="M33" s="7" t="s">
         <v>99</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="O33" s="9"/>
       <c r="P33" s="9" t="s">
@@ -5138,21 +5131,23 @@
         <v>1</v>
       </c>
       <c r="R33" s="10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S33" s="10">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="T33" s="9" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="U33" s="11">
-        <v>44568</v>
+        <v>45602</v>
       </c>
       <c r="V33" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="W33" s="10"/>
+        <v>44</v>
+      </c>
+      <c r="W33" s="10">
+        <v>-743</v>
+      </c>
       <c r="X33" s="12" t="str">
         <f ca="1">IF(Tabela1[[#This Row],[DATA_CURSO]]="",
 "PENDENTE",
@@ -5163,11 +5158,11 @@
 "VENCIDO – "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa"),
 "EM DIA – vence em "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa")),
 "NÃO É NECESSÁRIO RENOVAR")))</f>
-        <v>EM DIA – não é necessário renovar</v>
+        <v>EM DIA – vence em 06/11/27</v>
       </c>
       <c r="Y33" s="12" t="str">
         <f>IF(Tabela1[[#This Row],[FILIAL]]=1,"SINOP",IF(Tabela1[[#This Row],[FILIAL]]=2,"DOURADOS",IF(Tabela1[[#This Row],[FILIAL]]=3,"NOVA MUTUM",IF(Tabela1[[#This Row],[FILIAL]]=4,"FULLING",IF(Tabela1[[#This Row],[FILIAL]]=5,"SÃO PAULO",IF(Tabela1[[#This Row],[FILIAL]]=6,"SIDROLÂNDIA",IF(Tabela1[[#This Row],[FILIAL]]=8,"BALSAS",IF(Tabela1[[#This Row],[FILIAL]]=10,"LUIS EDUARDO MAGALHÃES",""))))))))</f>
-        <v>NOVA MUTUM</v>
+        <v>SINOP</v>
       </c>
       <c r="Z33" s="13" t="str">
         <f>VLOOKUP(N33,RENOVAÇÃO!A:D,4,0)</f>
@@ -5176,18 +5171,18 @@
       <c r="AA33" t="str">
         <f ca="1">CONCATENATE("• ",
     Tabela1[[#This Row],[DESCRICAO]], " - ",Tabela1[[#This Row],[STATUS_GERAL]])</f>
-        <v>• DIREÇÃO DEFENSIVA - TEÓRICO - EM DIA – não é necessário renovar</v>
+        <v>• NR 20 - SEG. E TRAB. INFLAMÁVEIS E COMBUSTIVEIS CLASSE III - BASICO - EM DIA – vence em 06/11/27</v>
       </c>
     </row>
     <row r="34" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A34" s="19">
-        <v>1</v>
+      <c r="A34" s="10">
+        <v>74</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C34" s="8">
-        <v>43570</v>
+        <v>43587</v>
       </c>
       <c r="D34" s="7" t="s">
         <v>110</v>
@@ -5205,22 +5200,22 @@
         <v>125</v>
       </c>
       <c r="I34" s="6">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="J34" s="6">
-        <v>5058</v>
+        <v>5060</v>
       </c>
       <c r="K34" s="7" t="s">
         <v>126</v>
       </c>
       <c r="L34" s="6">
-        <v>129</v>
+        <v>11</v>
       </c>
       <c r="M34" s="7" t="s">
         <v>99</v>
       </c>
       <c r="N34" s="9" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="O34" s="9"/>
       <c r="P34" s="9" t="s">
@@ -5233,19 +5228,19 @@
         <v>1</v>
       </c>
       <c r="S34" s="10">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="T34" s="9" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="U34" s="11">
-        <v>45945</v>
+        <v>45404</v>
       </c>
       <c r="V34" s="9" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="W34" s="10">
-        <v>-1086</v>
+        <v>-180</v>
       </c>
       <c r="X34" s="12" t="str">
         <f ca="1">IF(Tabela1[[#This Row],[DATA_CURSO]]="",
@@ -5257,7 +5252,7 @@
 "VENCIDO – "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa"),
 "EM DIA – vence em "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa")),
 "NÃO É NECESSÁRIO RENOVAR")))</f>
-        <v>EM DIA – vence em 14/10/28</v>
+        <v>EM DIA – vence em 22/04/26</v>
       </c>
       <c r="Y34" s="12" t="str">
         <f>IF(Tabela1[[#This Row],[FILIAL]]=1,"SINOP",IF(Tabela1[[#This Row],[FILIAL]]=2,"DOURADOS",IF(Tabela1[[#This Row],[FILIAL]]=3,"NOVA MUTUM",IF(Tabela1[[#This Row],[FILIAL]]=4,"FULLING",IF(Tabela1[[#This Row],[FILIAL]]=5,"SÃO PAULO",IF(Tabela1[[#This Row],[FILIAL]]=6,"SIDROLÂNDIA",IF(Tabela1[[#This Row],[FILIAL]]=8,"BALSAS",IF(Tabela1[[#This Row],[FILIAL]]=10,"LUIS EDUARDO MAGALHÃES",""))))))))</f>
@@ -5270,18 +5265,18 @@
       <c r="AA34" t="str">
         <f ca="1">CONCATENATE("• ",
     Tabela1[[#This Row],[DESCRICAO]], " - ",Tabela1[[#This Row],[STATUS_GERAL]])</f>
-        <v>• NR 20 - SEG. E TRAB. INFLAMÁVEIS E COMBUSTIVEIS CLASSE III - BASICO - EM DIA – vence em 14/10/28</v>
-      </c>
-    </row>
-    <row r="35" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A35" s="19">
-        <v>1</v>
+        <v>• NR 35 - TRABALHO EM ALTURA - EM DIA – vence em 22/04/26</v>
+      </c>
+    </row>
+    <row r="35" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A35" s="10">
+        <v>96</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C35" s="8">
-        <v>43570</v>
+        <v>43587</v>
       </c>
       <c r="D35" s="7" t="s">
         <v>110</v>
@@ -5299,22 +5294,22 @@
         <v>125</v>
       </c>
       <c r="I35" s="6">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="J35" s="6">
-        <v>5058</v>
+        <v>5060</v>
       </c>
       <c r="K35" s="7" t="s">
         <v>126</v>
       </c>
       <c r="L35" s="6">
-        <v>300</v>
+        <v>26</v>
       </c>
       <c r="M35" s="7" t="s">
         <v>99</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>46</v>
+        <v>109</v>
       </c>
       <c r="O35" s="9"/>
       <c r="P35" s="9" t="s">
@@ -5324,16 +5319,16 @@
         <v>1</v>
       </c>
       <c r="R35" s="10">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="S35" s="10">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="T35" s="9" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="U35" s="11">
-        <v>45489</v>
+        <v>44698</v>
       </c>
       <c r="V35" s="9" t="s">
         <v>5</v>
@@ -5353,7 +5348,7 @@
       </c>
       <c r="Y35" s="12" t="str">
         <f>IF(Tabela1[[#This Row],[FILIAL]]=1,"SINOP",IF(Tabela1[[#This Row],[FILIAL]]=2,"DOURADOS",IF(Tabela1[[#This Row],[FILIAL]]=3,"NOVA MUTUM",IF(Tabela1[[#This Row],[FILIAL]]=4,"FULLING",IF(Tabela1[[#This Row],[FILIAL]]=5,"SÃO PAULO",IF(Tabela1[[#This Row],[FILIAL]]=6,"SIDROLÂNDIA",IF(Tabela1[[#This Row],[FILIAL]]=8,"BALSAS",IF(Tabela1[[#This Row],[FILIAL]]=10,"LUIS EDUARDO MAGALHÃES",""))))))))</f>
-        <v>SINOP</v>
+        <v>BALSAS</v>
       </c>
       <c r="Z35" s="13" t="str">
         <f>VLOOKUP(N35,RENOVAÇÃO!A:D,4,0)</f>
@@ -5362,18 +5357,18 @@
       <c r="AA35" t="str">
         <f ca="1">CONCATENATE("• ",
     Tabela1[[#This Row],[DESCRICAO]], " - ",Tabela1[[#This Row],[STATUS_GERAL]])</f>
-        <v>• NR 26 - SINALIZAÇÃO DE SEGURANÇA - EM DIA – não é necessário renovar</v>
+        <v>• BLOQUEIO E SINALIZAÇÃO DE ENERGIAS PERIGOSAS - LOCKOUT/TAGOUT - NR10 E NR12 - EM DIA – não é necessário renovar</v>
       </c>
     </row>
     <row r="36" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A36" s="19">
-        <v>1</v>
+      <c r="A36" s="10">
+        <v>104</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C36" s="8">
-        <v>43570</v>
+        <v>43587</v>
       </c>
       <c r="D36" s="7" t="s">
         <v>110</v>
@@ -5391,22 +5386,22 @@
         <v>125</v>
       </c>
       <c r="I36" s="6">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="J36" s="6">
-        <v>5058</v>
+        <v>5060</v>
       </c>
       <c r="K36" s="7" t="s">
         <v>126</v>
       </c>
       <c r="L36" s="6">
-        <v>82</v>
+        <v>2</v>
       </c>
       <c r="M36" s="7" t="s">
         <v>99</v>
       </c>
       <c r="N36" s="9" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="O36" s="9"/>
       <c r="P36" s="9" t="s">
@@ -5416,22 +5411,22 @@
         <v>1</v>
       </c>
       <c r="R36" s="10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S36" s="10">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="T36" s="9" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="U36" s="11">
-        <v>45602</v>
+        <v>45826</v>
       </c>
       <c r="V36" s="9" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="W36" s="10">
-        <v>-13</v>
+        <v>-602</v>
       </c>
       <c r="X36" s="12" t="str">
         <f ca="1">IF(Tabela1[[#This Row],[DATA_CURSO]]="",
@@ -5443,11 +5438,11 @@
 "VENCIDO – "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa"),
 "EM DIA – vence em "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa")),
 "NÃO É NECESSÁRIO RENOVAR")))</f>
-        <v>EM DIA – vence em 06/11/25</v>
+        <v>EM DIA – vence em 18/06/27</v>
       </c>
       <c r="Y36" s="12" t="str">
         <f>IF(Tabela1[[#This Row],[FILIAL]]=1,"SINOP",IF(Tabela1[[#This Row],[FILIAL]]=2,"DOURADOS",IF(Tabela1[[#This Row],[FILIAL]]=3,"NOVA MUTUM",IF(Tabela1[[#This Row],[FILIAL]]=4,"FULLING",IF(Tabela1[[#This Row],[FILIAL]]=5,"SÃO PAULO",IF(Tabela1[[#This Row],[FILIAL]]=6,"SIDROLÂNDIA",IF(Tabela1[[#This Row],[FILIAL]]=8,"BALSAS",IF(Tabela1[[#This Row],[FILIAL]]=10,"LUIS EDUARDO MAGALHÃES",""))))))))</f>
-        <v>SINOP</v>
+        <v>NOVA MUTUM</v>
       </c>
       <c r="Z36" s="13" t="str">
         <f>VLOOKUP(N36,RENOVAÇÃO!A:D,4,0)</f>
@@ -5456,18 +5451,18 @@
       <c r="AA36" t="str">
         <f ca="1">CONCATENATE("• ",
     Tabela1[[#This Row],[DESCRICAO]], " - ",Tabela1[[#This Row],[STATUS_GERAL]])</f>
-        <v>• NR 20 - SEG. E TRAB. INFLAMÁVEIS E COMBUSTIVEIS CLASSE III - AVANÇADO - EM DIA – vence em 06/11/25</v>
-      </c>
-    </row>
-    <row r="37" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A37" s="19">
-        <v>1</v>
+        <v>• NR 20 - SEG. E TRAB. INFLAMÁVEIS E COMBUSTIVEIS CLASSE III - INTERMEDIÁRIO - EM DIA – vence em 18/06/27</v>
+      </c>
+    </row>
+    <row r="37" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A37" s="10">
+        <v>104</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C37" s="8">
-        <v>43570</v>
+        <v>43587</v>
       </c>
       <c r="D37" s="7" t="s">
         <v>110</v>
@@ -5485,22 +5480,22 @@
         <v>125</v>
       </c>
       <c r="I37" s="6">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="J37" s="6">
-        <v>5058</v>
+        <v>5060</v>
       </c>
       <c r="K37" s="7" t="s">
         <v>126</v>
       </c>
       <c r="L37" s="6">
-        <v>2</v>
+        <v>323</v>
       </c>
       <c r="M37" s="7" t="s">
         <v>99</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O37" s="9"/>
       <c r="P37" s="9" t="s">
@@ -5510,7 +5505,7 @@
         <v>1</v>
       </c>
       <c r="R37" s="10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S37" s="10">
         <v>80</v>
@@ -5519,13 +5514,13 @@
         <v>104</v>
       </c>
       <c r="U37" s="11">
-        <v>45349</v>
+        <v>45827</v>
       </c>
       <c r="V37" s="9" t="s">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="W37" s="10">
-        <v>-125</v>
+        <v>-238</v>
       </c>
       <c r="X37" s="12" t="str">
         <f ca="1">IF(Tabela1[[#This Row],[DATA_CURSO]]="",
@@ -5537,11 +5532,11 @@
 "VENCIDO – "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa"),
 "EM DIA – vence em "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa")),
 "NÃO É NECESSÁRIO RENOVAR")))</f>
-        <v>EM DIA – vence em 26/02/26</v>
+        <v>EM DIA – vence em 19/06/26</v>
       </c>
       <c r="Y37" s="12" t="str">
         <f>IF(Tabela1[[#This Row],[FILIAL]]=1,"SINOP",IF(Tabela1[[#This Row],[FILIAL]]=2,"DOURADOS",IF(Tabela1[[#This Row],[FILIAL]]=3,"NOVA MUTUM",IF(Tabela1[[#This Row],[FILIAL]]=4,"FULLING",IF(Tabela1[[#This Row],[FILIAL]]=5,"SÃO PAULO",IF(Tabela1[[#This Row],[FILIAL]]=6,"SIDROLÂNDIA",IF(Tabela1[[#This Row],[FILIAL]]=8,"BALSAS",IF(Tabela1[[#This Row],[FILIAL]]=10,"LUIS EDUARDO MAGALHÃES",""))))))))</f>
-        <v>SINOP</v>
+        <v>NOVA MUTUM</v>
       </c>
       <c r="Z37" s="13" t="str">
         <f>VLOOKUP(N37,RENOVAÇÃO!A:D,4,0)</f>
@@ -5550,18 +5545,18 @@
       <c r="AA37" t="str">
         <f ca="1">CONCATENATE("• ",
     Tabela1[[#This Row],[DESCRICAO]], " - ",Tabela1[[#This Row],[STATUS_GERAL]])</f>
-        <v>• NR 35 - TRABALHO EM ALTURA - EM DIA – vence em 26/02/26</v>
+        <v>• NR 33 - SEGURANÇA E SAUDE NOS TRABALHOS EM ESPAÇOS CONFINADOS - VIGIA E TRABALHADOR - EM DIA – vence em 19/06/26</v>
       </c>
     </row>
     <row r="38" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A38" s="19">
-        <v>1</v>
+      <c r="A38" s="10">
+        <v>127</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C38" s="8">
-        <v>43570</v>
+        <v>43587</v>
       </c>
       <c r="D38" s="7" t="s">
         <v>110</v>
@@ -5579,22 +5574,22 @@
         <v>125</v>
       </c>
       <c r="I38" s="6">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="J38" s="6">
-        <v>5058</v>
+        <v>5060</v>
       </c>
       <c r="K38" s="7" t="s">
         <v>126</v>
       </c>
       <c r="L38" s="6">
-        <v>322</v>
+        <v>104</v>
       </c>
       <c r="M38" s="7" t="s">
         <v>99</v>
       </c>
       <c r="N38" s="9" t="s">
-        <v>109</v>
+        <v>48</v>
       </c>
       <c r="O38" s="9"/>
       <c r="P38" s="9" t="s">
@@ -5604,21 +5599,23 @@
         <v>1</v>
       </c>
       <c r="R38" s="10">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="S38" s="10">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="T38" s="9" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="U38" s="11">
-        <v>44865</v>
+        <v>45717</v>
       </c>
       <c r="V38" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="W38" s="10"/>
+        <v>13</v>
+      </c>
+      <c r="W38" s="10">
+        <v>-128</v>
+      </c>
       <c r="X38" s="12" t="str">
         <f ca="1">IF(Tabela1[[#This Row],[DATA_CURSO]]="",
 "PENDENTE",
@@ -5629,11 +5626,11 @@
 "VENCIDO – "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa"),
 "EM DIA – vence em "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa")),
 "NÃO É NECESSÁRIO RENOVAR")))</f>
-        <v>EM DIA – não é necessário renovar</v>
+        <v>EM DIA – vence em 01/03/26</v>
       </c>
       <c r="Y38" s="12" t="str">
         <f>IF(Tabela1[[#This Row],[FILIAL]]=1,"SINOP",IF(Tabela1[[#This Row],[FILIAL]]=2,"DOURADOS",IF(Tabela1[[#This Row],[FILIAL]]=3,"NOVA MUTUM",IF(Tabela1[[#This Row],[FILIAL]]=4,"FULLING",IF(Tabela1[[#This Row],[FILIAL]]=5,"SÃO PAULO",IF(Tabela1[[#This Row],[FILIAL]]=6,"SIDROLÂNDIA",IF(Tabela1[[#This Row],[FILIAL]]=8,"BALSAS",IF(Tabela1[[#This Row],[FILIAL]]=10,"LUIS EDUARDO MAGALHÃES",""))))))))</f>
-        <v>NOVA MUTUM</v>
+        <v>BALSAS</v>
       </c>
       <c r="Z38" s="13" t="str">
         <f>VLOOKUP(N38,RENOVAÇÃO!A:D,4,0)</f>
@@ -5642,18 +5639,18 @@
       <c r="AA38" t="str">
         <f ca="1">CONCATENATE("• ",
     Tabela1[[#This Row],[DESCRICAO]], " - ",Tabela1[[#This Row],[STATUS_GERAL]])</f>
-        <v>• BLOQUEIO E SINALIZAÇÃO DE ENERGIAS PERIGOSAS - LOCKOUT/TAGOUT - NR10 E NR12 - EM DIA – não é necessário renovar</v>
+        <v>• NR 33 - SEGURANÇA E SAUDE NOS TRABALHOS EM ESPAÇOS CONFINADOS - VIGIA E TRABALHADOR - EM DIA – vence em 01/03/26</v>
       </c>
     </row>
     <row r="39" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A39" s="19">
-        <v>1</v>
+      <c r="A39" s="10">
+        <v>127</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C39" s="8">
-        <v>43570</v>
+        <v>43587</v>
       </c>
       <c r="D39" s="7" t="s">
         <v>110</v>
@@ -5671,16 +5668,16 @@
         <v>125</v>
       </c>
       <c r="I39" s="6">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="J39" s="6">
-        <v>5058</v>
+        <v>5060</v>
       </c>
       <c r="K39" s="7" t="s">
         <v>126</v>
       </c>
       <c r="L39" s="6">
-        <v>320</v>
+        <v>302</v>
       </c>
       <c r="M39" s="7" t="s">
         <v>99</v>
@@ -5696,22 +5693,22 @@
         <v>1</v>
       </c>
       <c r="R39" s="10">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="S39" s="10">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="T39" s="9" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="U39" s="11">
-        <v>45834</v>
+        <v>45569</v>
       </c>
       <c r="V39" s="9" t="s">
         <v>36</v>
       </c>
       <c r="W39" s="10">
-        <v>-610</v>
+        <v>-345</v>
       </c>
       <c r="X39" s="12" t="str">
         <f ca="1">IF(Tabela1[[#This Row],[DATA_CURSO]]="",
@@ -5723,11 +5720,11 @@
 "VENCIDO – "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa"),
 "EM DIA – vence em "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa")),
 "NÃO É NECESSÁRIO RENOVAR")))</f>
-        <v>EM DIA – vence em 26/06/27</v>
+        <v>EM DIA – vence em 04/10/26</v>
       </c>
       <c r="Y39" s="12" t="str">
         <f>IF(Tabela1[[#This Row],[FILIAL]]=1,"SINOP",IF(Tabela1[[#This Row],[FILIAL]]=2,"DOURADOS",IF(Tabela1[[#This Row],[FILIAL]]=3,"NOVA MUTUM",IF(Tabela1[[#This Row],[FILIAL]]=4,"FULLING",IF(Tabela1[[#This Row],[FILIAL]]=5,"SÃO PAULO",IF(Tabela1[[#This Row],[FILIAL]]=6,"SIDROLÂNDIA",IF(Tabela1[[#This Row],[FILIAL]]=8,"BALSAS",IF(Tabela1[[#This Row],[FILIAL]]=10,"LUIS EDUARDO MAGALHÃES",""))))))))</f>
-        <v>SINOP</v>
+        <v>BALSAS</v>
       </c>
       <c r="Z39" s="13" t="str">
         <f>VLOOKUP(N39,RENOVAÇÃO!A:D,4,0)</f>
@@ -5736,18 +5733,18 @@
       <c r="AA39" t="str">
         <f ca="1">CONCATENATE("• ",
     Tabela1[[#This Row],[DESCRICAO]], " - ",Tabela1[[#This Row],[STATUS_GERAL]])</f>
-        <v>• NR 35 - TRABALHO EM ALTURA - EM DIA – vence em 26/06/27</v>
+        <v>• NR 35 - TRABALHO EM ALTURA - EM DIA – vence em 04/10/26</v>
       </c>
     </row>
     <row r="40" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A40" s="19">
-        <v>1</v>
+      <c r="A40" s="10">
+        <v>136</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C40" s="8">
-        <v>43570</v>
+        <v>43587</v>
       </c>
       <c r="D40" s="7" t="s">
         <v>110</v>
@@ -5765,10 +5762,10 @@
         <v>125</v>
       </c>
       <c r="I40" s="6">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="J40" s="6">
-        <v>5058</v>
+        <v>5060</v>
       </c>
       <c r="K40" s="7" t="s">
         <v>126</v>
@@ -5780,7 +5777,7 @@
         <v>99</v>
       </c>
       <c r="N40" s="9" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="O40" s="9"/>
       <c r="P40" s="9" t="s">
@@ -5793,20 +5790,18 @@
         <v>1</v>
       </c>
       <c r="S40" s="10">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="T40" s="9" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="U40" s="11">
-        <v>44889</v>
+        <v>44510</v>
       </c>
       <c r="V40" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="W40" s="10">
-        <v>-30</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="W40" s="10"/>
       <c r="X40" s="12" t="str">
         <f ca="1">IF(Tabela1[[#This Row],[DATA_CURSO]]="",
 "PENDENTE",
@@ -5817,7 +5812,7 @@
 "VENCIDO – "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa"),
 "EM DIA – vence em "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa")),
 "NÃO É NECESSÁRIO RENOVAR")))</f>
-        <v>EM DIA – vence em 23/11/25</v>
+        <v>EM DIA – não é necessário renovar</v>
       </c>
       <c r="Y40" s="12" t="str">
         <f>IF(Tabela1[[#This Row],[FILIAL]]=1,"SINOP",IF(Tabela1[[#This Row],[FILIAL]]=2,"DOURADOS",IF(Tabela1[[#This Row],[FILIAL]]=3,"NOVA MUTUM",IF(Tabela1[[#This Row],[FILIAL]]=4,"FULLING",IF(Tabela1[[#This Row],[FILIAL]]=5,"SÃO PAULO",IF(Tabela1[[#This Row],[FILIAL]]=6,"SIDROLÂNDIA",IF(Tabela1[[#This Row],[FILIAL]]=8,"BALSAS",IF(Tabela1[[#This Row],[FILIAL]]=10,"LUIS EDUARDO MAGALHÃES",""))))))))</f>
@@ -5830,18 +5825,18 @@
       <c r="AA40" t="str">
         <f ca="1">CONCATENATE("• ",
     Tabela1[[#This Row],[DESCRICAO]], " - ",Tabela1[[#This Row],[STATUS_GERAL]])</f>
-        <v>• NR 20 - SEG. E TRAB. INFLAMÁVEIS E COMBUSTIVEIS CLASSE III - BASICO - EM DIA – vence em 23/11/25</v>
+        <v>• DIREÇÃO DEFENSIVA - TEÓRICO - EM DIA – não é necessário renovar</v>
       </c>
     </row>
     <row r="41" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A41" s="19">
-        <v>1</v>
+      <c r="A41" s="10">
+        <v>136</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C41" s="8">
-        <v>43570</v>
+        <v>43587</v>
       </c>
       <c r="D41" s="7" t="s">
         <v>110</v>
@@ -5859,22 +5854,22 @@
         <v>125</v>
       </c>
       <c r="I41" s="6">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="J41" s="6">
-        <v>5058</v>
+        <v>5060</v>
       </c>
       <c r="K41" s="7" t="s">
         <v>126</v>
       </c>
       <c r="L41" s="6">
-        <v>295</v>
+        <v>322</v>
       </c>
       <c r="M41" s="7" t="s">
         <v>99</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="O41" s="9"/>
       <c r="P41" s="9" t="s">
@@ -5884,23 +5879,21 @@
         <v>1</v>
       </c>
       <c r="R41" s="10">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="S41" s="10">
-        <v>78</v>
+        <v>102</v>
       </c>
       <c r="T41" s="9" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="U41" s="11">
-        <v>45404</v>
+        <v>44771</v>
       </c>
       <c r="V41" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="W41" s="10">
-        <v>-545</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="W41" s="10"/>
       <c r="X41" s="12" t="str">
         <f ca="1">IF(Tabela1[[#This Row],[DATA_CURSO]]="",
 "PENDENTE",
@@ -5911,11 +5904,11 @@
 "VENCIDO – "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa"),
 "EM DIA – vence em "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa")),
 "NÃO É NECESSÁRIO RENOVAR")))</f>
-        <v>EM DIA – vence em 22/04/27</v>
+        <v>EM DIA – não é necessário renovar</v>
       </c>
       <c r="Y41" s="12" t="str">
         <f>IF(Tabela1[[#This Row],[FILIAL]]=1,"SINOP",IF(Tabela1[[#This Row],[FILIAL]]=2,"DOURADOS",IF(Tabela1[[#This Row],[FILIAL]]=3,"NOVA MUTUM",IF(Tabela1[[#This Row],[FILIAL]]=4,"FULLING",IF(Tabela1[[#This Row],[FILIAL]]=5,"SÃO PAULO",IF(Tabela1[[#This Row],[FILIAL]]=6,"SIDROLÂNDIA",IF(Tabela1[[#This Row],[FILIAL]]=8,"BALSAS",IF(Tabela1[[#This Row],[FILIAL]]=10,"LUIS EDUARDO MAGALHÃES",""))))))))</f>
-        <v>BALSAS</v>
+        <v>NOVA MUTUM</v>
       </c>
       <c r="Z41" s="13" t="str">
         <f>VLOOKUP(N41,RENOVAÇÃO!A:D,4,0)</f>
@@ -5924,18 +5917,18 @@
       <c r="AA41" t="str">
         <f ca="1">CONCATENATE("• ",
     Tabela1[[#This Row],[DESCRICAO]], " - ",Tabela1[[#This Row],[STATUS_GERAL]])</f>
-        <v>• NR 20 - SEG. E TRAB. INFLAMÁVEIS E COMBUSTIVEIS CLASSE III - BASICO - EM DIA – vence em 22/04/27</v>
-      </c>
-    </row>
-    <row r="42" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A42" s="19">
-        <v>1</v>
+        <v>• NR 13 - SEGURANÇA NA OPERAÇÃO VASOS DE PRESSÃO - EM DIA – não é necessário renovar</v>
+      </c>
+    </row>
+    <row r="42" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A42" s="10">
+        <v>136</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C42" s="8">
-        <v>43570</v>
+        <v>43587</v>
       </c>
       <c r="D42" s="7" t="s">
         <v>110</v>
@@ -5953,22 +5946,22 @@
         <v>125</v>
       </c>
       <c r="I42" s="6">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="J42" s="6">
-        <v>5058</v>
+        <v>5060</v>
       </c>
       <c r="K42" s="7" t="s">
         <v>126</v>
       </c>
       <c r="L42" s="6">
-        <v>302</v>
+        <v>320</v>
       </c>
       <c r="M42" s="7" t="s">
         <v>99</v>
       </c>
       <c r="N42" s="9" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="O42" s="9"/>
       <c r="P42" s="9" t="s">
@@ -5981,19 +5974,19 @@
         <v>1</v>
       </c>
       <c r="S42" s="10">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="T42" s="9" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="U42" s="11">
-        <v>45607</v>
+        <v>45181</v>
       </c>
       <c r="V42" s="9" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="W42" s="10">
-        <v>-18</v>
+        <v>43</v>
       </c>
       <c r="X42" s="12" t="str">
         <f ca="1">IF(Tabela1[[#This Row],[DATA_CURSO]]="",
@@ -6005,7 +5998,7 @@
 "VENCIDO – "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa"),
 "EM DIA – vence em "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa")),
 "NÃO É NECESSÁRIO RENOVAR")))</f>
-        <v>EM DIA – vence em 11/11/25</v>
+        <v>VENCIDO – 11/09/25</v>
       </c>
       <c r="Y42" s="12" t="str">
         <f>IF(Tabela1[[#This Row],[FILIAL]]=1,"SINOP",IF(Tabela1[[#This Row],[FILIAL]]=2,"DOURADOS",IF(Tabela1[[#This Row],[FILIAL]]=3,"NOVA MUTUM",IF(Tabela1[[#This Row],[FILIAL]]=4,"FULLING",IF(Tabela1[[#This Row],[FILIAL]]=5,"SÃO PAULO",IF(Tabela1[[#This Row],[FILIAL]]=6,"SIDROLÂNDIA",IF(Tabela1[[#This Row],[FILIAL]]=8,"BALSAS",IF(Tabela1[[#This Row],[FILIAL]]=10,"LUIS EDUARDO MAGALHÃES",""))))))))</f>
@@ -6018,18 +6011,18 @@
       <c r="AA42" t="str">
         <f ca="1">CONCATENATE("• ",
     Tabela1[[#This Row],[DESCRICAO]], " - ",Tabela1[[#This Row],[STATUS_GERAL]])</f>
-        <v>• NR 20 - SEG. E TRAB. INFLAMÁVEIS E COMBUSTIVEIS CLASSE III - AVANÇADO - EM DIA – vence em 11/11/25</v>
-      </c>
-    </row>
-    <row r="43" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A43" s="19">
-        <v>1</v>
+        <v>• NR 11 - OPERAÇÃO DE TALHAS E PONTE ROLANTE - VENCIDO – 11/09/25</v>
+      </c>
+    </row>
+    <row r="43" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A43" s="10">
+        <v>136</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C43" s="8">
-        <v>43570</v>
+        <v>43587</v>
       </c>
       <c r="D43" s="7" t="s">
         <v>110</v>
@@ -6047,22 +6040,22 @@
         <v>125</v>
       </c>
       <c r="I43" s="6">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="J43" s="6">
-        <v>5058</v>
+        <v>5060</v>
       </c>
       <c r="K43" s="7" t="s">
         <v>126</v>
       </c>
       <c r="L43" s="6">
-        <v>318</v>
+        <v>129</v>
       </c>
       <c r="M43" s="7" t="s">
         <v>99</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="O43" s="9"/>
       <c r="P43" s="9" t="s">
@@ -6072,7 +6065,7 @@
         <v>1</v>
       </c>
       <c r="R43" s="10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S43" s="10">
         <v>102</v>
@@ -6081,13 +6074,13 @@
         <v>106</v>
       </c>
       <c r="U43" s="11">
-        <v>45707</v>
+        <v>45349</v>
       </c>
       <c r="V43" s="9" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="W43" s="10">
-        <v>-118</v>
+        <v>-125</v>
       </c>
       <c r="X43" s="12" t="str">
         <f ca="1">IF(Tabela1[[#This Row],[DATA_CURSO]]="",
@@ -6099,11 +6092,11 @@
 "VENCIDO – "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa"),
 "EM DIA – vence em "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa")),
 "NÃO É NECESSÁRIO RENOVAR")))</f>
-        <v>EM DIA – vence em 19/02/26</v>
+        <v>EM DIA – vence em 26/02/26</v>
       </c>
       <c r="Y43" s="12" t="str">
         <f>IF(Tabela1[[#This Row],[FILIAL]]=1,"SINOP",IF(Tabela1[[#This Row],[FILIAL]]=2,"DOURADOS",IF(Tabela1[[#This Row],[FILIAL]]=3,"NOVA MUTUM",IF(Tabela1[[#This Row],[FILIAL]]=4,"FULLING",IF(Tabela1[[#This Row],[FILIAL]]=5,"SÃO PAULO",IF(Tabela1[[#This Row],[FILIAL]]=6,"SIDROLÂNDIA",IF(Tabela1[[#This Row],[FILIAL]]=8,"BALSAS",IF(Tabela1[[#This Row],[FILIAL]]=10,"LUIS EDUARDO MAGALHÃES",""))))))))</f>
-        <v>SINOP</v>
+        <v>NOVA MUTUM</v>
       </c>
       <c r="Z43" s="13" t="str">
         <f>VLOOKUP(N43,RENOVAÇÃO!A:D,4,0)</f>
@@ -6112,18 +6105,18 @@
       <c r="AA43" t="str">
         <f ca="1">CONCATENATE("• ",
     Tabela1[[#This Row],[DESCRICAO]], " - ",Tabela1[[#This Row],[STATUS_GERAL]])</f>
-        <v>• NR 33 - SEGURANÇA E SAUDE NOS TRABALHOS EM ESPAÇOS CONFINADOS - VIGIA E TRABALHADOR - EM DIA – vence em 19/02/26</v>
+        <v>• NR 35 - TRABALHO EM ALTURA - EM DIA – vence em 26/02/26</v>
       </c>
     </row>
     <row r="44" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A44" s="19">
-        <v>1</v>
+      <c r="A44" s="10">
+        <v>141</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C44" s="8">
-        <v>43570</v>
+        <v>43587</v>
       </c>
       <c r="D44" s="7" t="s">
         <v>110</v>
@@ -6141,22 +6134,22 @@
         <v>125</v>
       </c>
       <c r="I44" s="6">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="J44" s="6">
-        <v>5058</v>
+        <v>5060</v>
       </c>
       <c r="K44" s="7" t="s">
         <v>126</v>
       </c>
       <c r="L44" s="6">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="M44" s="7" t="s">
         <v>99</v>
       </c>
       <c r="N44" s="9" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="O44" s="9"/>
       <c r="P44" s="9" t="s">
@@ -6166,21 +6159,23 @@
         <v>1</v>
       </c>
       <c r="R44" s="10">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="S44" s="10">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="T44" s="9" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="U44" s="11">
-        <v>45489</v>
+        <v>45735</v>
       </c>
       <c r="V44" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="W44" s="10"/>
+        <v>44</v>
+      </c>
+      <c r="W44" s="10">
+        <v>-876</v>
+      </c>
       <c r="X44" s="12" t="str">
         <f ca="1">IF(Tabela1[[#This Row],[DATA_CURSO]]="",
 "PENDENTE",
@@ -6191,11 +6186,11 @@
 "VENCIDO – "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa"),
 "EM DIA – vence em "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa")),
 "NÃO É NECESSÁRIO RENOVAR")))</f>
-        <v>EM DIA – não é necessário renovar</v>
+        <v>EM DIA – vence em 18/03/28</v>
       </c>
       <c r="Y44" s="12" t="str">
         <f>IF(Tabela1[[#This Row],[FILIAL]]=1,"SINOP",IF(Tabela1[[#This Row],[FILIAL]]=2,"DOURADOS",IF(Tabela1[[#This Row],[FILIAL]]=3,"NOVA MUTUM",IF(Tabela1[[#This Row],[FILIAL]]=4,"FULLING",IF(Tabela1[[#This Row],[FILIAL]]=5,"SÃO PAULO",IF(Tabela1[[#This Row],[FILIAL]]=6,"SIDROLÂNDIA",IF(Tabela1[[#This Row],[FILIAL]]=8,"BALSAS",IF(Tabela1[[#This Row],[FILIAL]]=10,"LUIS EDUARDO MAGALHÃES",""))))))))</f>
-        <v>BALSAS</v>
+        <v>SINOP</v>
       </c>
       <c r="Z44" s="13" t="str">
         <f>VLOOKUP(N44,RENOVAÇÃO!A:D,4,0)</f>
@@ -6204,18 +6199,18 @@
       <c r="AA44" t="str">
         <f ca="1">CONCATENATE("• ",
     Tabela1[[#This Row],[DESCRICAO]], " - ",Tabela1[[#This Row],[STATUS_GERAL]])</f>
-        <v>• NR 26 - SINALIZAÇÃO DE SEGURANÇA - EM DIA – não é necessário renovar</v>
-      </c>
-    </row>
-    <row r="45" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A45" s="19">
-        <v>1</v>
+        <v>• NR 20 - SEG. E TRAB. INFLAMÁVEIS E COMBUSTIVEIS CLASSE III - BASICO - EM DIA – vence em 18/03/28</v>
+      </c>
+    </row>
+    <row r="45" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A45" s="10">
+        <v>143</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C45" s="8">
-        <v>43570</v>
+        <v>43587</v>
       </c>
       <c r="D45" s="7" t="s">
         <v>110</v>
@@ -6233,22 +6228,22 @@
         <v>125</v>
       </c>
       <c r="I45" s="6">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="J45" s="6">
-        <v>5058</v>
+        <v>5060</v>
       </c>
       <c r="K45" s="7" t="s">
         <v>126</v>
       </c>
       <c r="L45" s="6">
-        <v>104</v>
+        <v>318</v>
       </c>
       <c r="M45" s="7" t="s">
         <v>99</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>109</v>
+        <v>43</v>
       </c>
       <c r="O45" s="9"/>
       <c r="P45" s="9" t="s">
@@ -6258,21 +6253,23 @@
         <v>1</v>
       </c>
       <c r="R45" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S45" s="10">
+        <v>78</v>
+      </c>
+      <c r="T45" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="T45" s="9" t="s">
-        <v>106</v>
-      </c>
       <c r="U45" s="11">
-        <v>44851</v>
+        <v>45876</v>
       </c>
       <c r="V45" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="W45" s="10"/>
+        <v>44</v>
+      </c>
+      <c r="W45" s="10">
+        <v>-1017</v>
+      </c>
       <c r="X45" s="12" t="str">
         <f ca="1">IF(Tabela1[[#This Row],[DATA_CURSO]]="",
 "PENDENTE",
@@ -6283,11 +6280,11 @@
 "VENCIDO – "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa"),
 "EM DIA – vence em "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa")),
 "NÃO É NECESSÁRIO RENOVAR")))</f>
-        <v>EM DIA – não é necessário renovar</v>
+        <v>EM DIA – vence em 06/08/28</v>
       </c>
       <c r="Y45" s="12" t="str">
         <f>IF(Tabela1[[#This Row],[FILIAL]]=1,"SINOP",IF(Tabela1[[#This Row],[FILIAL]]=2,"DOURADOS",IF(Tabela1[[#This Row],[FILIAL]]=3,"NOVA MUTUM",IF(Tabela1[[#This Row],[FILIAL]]=4,"FULLING",IF(Tabela1[[#This Row],[FILIAL]]=5,"SÃO PAULO",IF(Tabela1[[#This Row],[FILIAL]]=6,"SIDROLÂNDIA",IF(Tabela1[[#This Row],[FILIAL]]=8,"BALSAS",IF(Tabela1[[#This Row],[FILIAL]]=10,"LUIS EDUARDO MAGALHÃES",""))))))))</f>
-        <v>NOVA MUTUM</v>
+        <v>DOURADOS</v>
       </c>
       <c r="Z45" s="13" t="str">
         <f>VLOOKUP(N45,RENOVAÇÃO!A:D,4,0)</f>
@@ -6296,18 +6293,18 @@
       <c r="AA45" t="str">
         <f ca="1">CONCATENATE("• ",
     Tabela1[[#This Row],[DESCRICAO]], " - ",Tabela1[[#This Row],[STATUS_GERAL]])</f>
-        <v>• BLOQUEIO E SINALIZAÇÃO DE ENERGIAS PERIGOSAS - LOCKOUT/TAGOUT - NR10 E NR12 - EM DIA – não é necessário renovar</v>
+        <v>• NR 20 - SEG. E TRAB. INFLAMÁVEIS E COMBUSTIVEIS CLASSE III - BASICO - EM DIA – vence em 06/08/28</v>
       </c>
     </row>
     <row r="46" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A46" s="19">
-        <v>1</v>
+      <c r="A46" s="10">
+        <v>143</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C46" s="8">
-        <v>43570</v>
+        <v>43587</v>
       </c>
       <c r="D46" s="7" t="s">
         <v>110</v>
@@ -6325,16 +6322,16 @@
         <v>125</v>
       </c>
       <c r="I46" s="6">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="J46" s="6">
-        <v>5058</v>
+        <v>5060</v>
       </c>
       <c r="K46" s="7" t="s">
         <v>126</v>
       </c>
       <c r="L46" s="6">
-        <v>123</v>
+        <v>200</v>
       </c>
       <c r="M46" s="7" t="s">
         <v>99</v>
@@ -6350,22 +6347,22 @@
         <v>1</v>
       </c>
       <c r="R46" s="10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S46" s="10">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="T46" s="9" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="U46" s="11">
-        <v>45827</v>
+        <v>45365</v>
       </c>
       <c r="V46" s="9" t="s">
         <v>36</v>
       </c>
       <c r="W46" s="10">
-        <v>-603</v>
+        <v>-141</v>
       </c>
       <c r="X46" s="12" t="str">
         <f ca="1">IF(Tabela1[[#This Row],[DATA_CURSO]]="",
@@ -6377,11 +6374,11 @@
 "VENCIDO – "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa"),
 "EM DIA – vence em "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa")),
 "NÃO É NECESSÁRIO RENOVAR")))</f>
-        <v>EM DIA – vence em 19/06/27</v>
+        <v>EM DIA – vence em 14/03/26</v>
       </c>
       <c r="Y46" s="12" t="str">
         <f>IF(Tabela1[[#This Row],[FILIAL]]=1,"SINOP",IF(Tabela1[[#This Row],[FILIAL]]=2,"DOURADOS",IF(Tabela1[[#This Row],[FILIAL]]=3,"NOVA MUTUM",IF(Tabela1[[#This Row],[FILIAL]]=4,"FULLING",IF(Tabela1[[#This Row],[FILIAL]]=5,"SÃO PAULO",IF(Tabela1[[#This Row],[FILIAL]]=6,"SIDROLÂNDIA",IF(Tabela1[[#This Row],[FILIAL]]=8,"BALSAS",IF(Tabela1[[#This Row],[FILIAL]]=10,"LUIS EDUARDO MAGALHÃES",""))))))))</f>
-        <v>SINOP</v>
+        <v>NOVA MUTUM</v>
       </c>
       <c r="Z46" s="13" t="str">
         <f>VLOOKUP(N46,RENOVAÇÃO!A:D,4,0)</f>
@@ -6390,18 +6387,18 @@
       <c r="AA46" t="str">
         <f ca="1">CONCATENATE("• ",
     Tabela1[[#This Row],[DESCRICAO]], " - ",Tabela1[[#This Row],[STATUS_GERAL]])</f>
-        <v>• NR 35 - TRABALHO EM ALTURA - EM DIA – vence em 19/06/27</v>
+        <v>• NR 35 - TRABALHO EM ALTURA - EM DIA – vence em 14/03/26</v>
       </c>
     </row>
     <row r="47" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A47" s="19">
-        <v>1</v>
+      <c r="A47" s="10">
+        <v>143</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C47" s="8">
-        <v>43570</v>
+        <v>43587</v>
       </c>
       <c r="D47" s="7" t="s">
         <v>110</v>
@@ -6419,22 +6416,22 @@
         <v>125</v>
       </c>
       <c r="I47" s="6">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="J47" s="6">
-        <v>5058</v>
+        <v>5060</v>
       </c>
       <c r="K47" s="7" t="s">
         <v>126</v>
       </c>
       <c r="L47" s="6">
-        <v>235</v>
+        <v>271</v>
       </c>
       <c r="M47" s="7" t="s">
         <v>99</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="O47" s="9"/>
       <c r="P47" s="9" t="s">
@@ -6444,22 +6441,22 @@
         <v>1</v>
       </c>
       <c r="R47" s="10">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="S47" s="10">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="T47" s="9" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="U47" s="11">
-        <v>45889</v>
+        <v>45807</v>
       </c>
       <c r="V47" s="9" t="s">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="W47" s="10">
-        <v>-665</v>
+        <v>-218</v>
       </c>
       <c r="X47" s="12" t="str">
         <f ca="1">IF(Tabela1[[#This Row],[DATA_CURSO]]="",
@@ -6471,11 +6468,11 @@
 "VENCIDO – "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa"),
 "EM DIA – vence em "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa")),
 "NÃO É NECESSÁRIO RENOVAR")))</f>
-        <v>EM DIA – vence em 20/08/27</v>
+        <v>EM DIA – vence em 30/05/26</v>
       </c>
       <c r="Y47" s="12" t="str">
         <f>IF(Tabela1[[#This Row],[FILIAL]]=1,"SINOP",IF(Tabela1[[#This Row],[FILIAL]]=2,"DOURADOS",IF(Tabela1[[#This Row],[FILIAL]]=3,"NOVA MUTUM",IF(Tabela1[[#This Row],[FILIAL]]=4,"FULLING",IF(Tabela1[[#This Row],[FILIAL]]=5,"SÃO PAULO",IF(Tabela1[[#This Row],[FILIAL]]=6,"SIDROLÂNDIA",IF(Tabela1[[#This Row],[FILIAL]]=8,"BALSAS",IF(Tabela1[[#This Row],[FILIAL]]=10,"LUIS EDUARDO MAGALHÃES",""))))))))</f>
-        <v>BALSAS</v>
+        <v>NOVA MUTUM</v>
       </c>
       <c r="Z47" s="13" t="str">
         <f>VLOOKUP(N47,RENOVAÇÃO!A:D,4,0)</f>
@@ -6484,18 +6481,18 @@
       <c r="AA47" t="str">
         <f ca="1">CONCATENATE("• ",
     Tabela1[[#This Row],[DESCRICAO]], " - ",Tabela1[[#This Row],[STATUS_GERAL]])</f>
-        <v>• NR 20 - SEG. E TRAB. INFLAMÁVEIS E COMBUSTIVEIS CLASSE III - INTERMEDIÁRIO - EM DIA – vence em 20/08/27</v>
+        <v>• NR 20 - SEG. E TRAB. INFLAMÁVEIS E COMBUSTIVEIS CLASSE III - AVANÇADO - EM DIA – vence em 30/05/26</v>
       </c>
     </row>
     <row r="48" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A48" s="19">
-        <v>1</v>
+      <c r="A48" s="10">
+        <v>145</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C48" s="8">
-        <v>43570</v>
+        <v>43587</v>
       </c>
       <c r="D48" s="7" t="s">
         <v>110</v>
@@ -6513,10 +6510,10 @@
         <v>125</v>
       </c>
       <c r="I48" s="6">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="J48" s="6">
-        <v>5058</v>
+        <v>5060</v>
       </c>
       <c r="K48" s="7" t="s">
         <v>126</v>
@@ -6528,25 +6525,29 @@
         <v>99</v>
       </c>
       <c r="N48" s="9" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="O48" s="9"/>
-      <c r="P48" s="9"/>
+      <c r="P48" s="9" t="s">
+        <v>100</v>
+      </c>
       <c r="Q48" s="10">
         <v>1</v>
       </c>
       <c r="R48" s="10">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="S48" s="10">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="T48" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="U48" s="9"/>
+        <v>106</v>
+      </c>
+      <c r="U48" s="11">
+        <v>44359</v>
+      </c>
       <c r="V48" s="9" t="s">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="W48" s="10"/>
       <c r="X48" s="12" t="str">
@@ -6559,11 +6560,11 @@
 "VENCIDO – "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa"),
 "EM DIA – vence em "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa")),
 "NÃO É NECESSÁRIO RENOVAR")))</f>
-        <v>PENDENTE</v>
+        <v>EM DIA – não é necessário renovar</v>
       </c>
       <c r="Y48" s="12" t="str">
         <f>IF(Tabela1[[#This Row],[FILIAL]]=1,"SINOP",IF(Tabela1[[#This Row],[FILIAL]]=2,"DOURADOS",IF(Tabela1[[#This Row],[FILIAL]]=3,"NOVA MUTUM",IF(Tabela1[[#This Row],[FILIAL]]=4,"FULLING",IF(Tabela1[[#This Row],[FILIAL]]=5,"SÃO PAULO",IF(Tabela1[[#This Row],[FILIAL]]=6,"SIDROLÂNDIA",IF(Tabela1[[#This Row],[FILIAL]]=8,"BALSAS",IF(Tabela1[[#This Row],[FILIAL]]=10,"LUIS EDUARDO MAGALHÃES",""))))))))</f>
-        <v>BALSAS</v>
+        <v>NOVA MUTUM</v>
       </c>
       <c r="Z48" s="13" t="str">
         <f>VLOOKUP(N48,RENOVAÇÃO!A:D,4,0)</f>
@@ -6572,18 +6573,18 @@
       <c r="AA48" t="str">
         <f ca="1">CONCATENATE("• ",
     Tabela1[[#This Row],[DESCRICAO]], " - ",Tabela1[[#This Row],[STATUS_GERAL]])</f>
-        <v>• NR 11 - OPERAÇÃO DE TALHAS E PONTE ROLANTE - PENDENTE</v>
-      </c>
-    </row>
-    <row r="49" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A49" s="19">
-        <v>1</v>
+        <v>• NR 13 - SEGURANÇA NA OPERAÇÃO VASOS DE PRESSÃO - EM DIA – não é necessário renovar</v>
+      </c>
+    </row>
+    <row r="49" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A49" s="10">
+        <v>145</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C49" s="8">
-        <v>43570</v>
+        <v>43683</v>
       </c>
       <c r="D49" s="7" t="s">
         <v>110</v>
@@ -6601,22 +6602,22 @@
         <v>125</v>
       </c>
       <c r="I49" s="6">
-        <v>172</v>
+        <v>134</v>
       </c>
       <c r="J49" s="6">
-        <v>5058</v>
+        <v>5076</v>
       </c>
       <c r="K49" s="7" t="s">
         <v>126</v>
       </c>
       <c r="L49" s="6">
-        <v>323</v>
+        <v>123</v>
       </c>
       <c r="M49" s="7" t="s">
         <v>99</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="O49" s="9"/>
       <c r="P49" s="9" t="s">
@@ -6629,19 +6630,19 @@
         <v>1</v>
       </c>
       <c r="S49" s="10">
+        <v>78</v>
+      </c>
+      <c r="T49" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="T49" s="9" t="s">
-        <v>106</v>
-      </c>
       <c r="U49" s="11">
-        <v>45709</v>
+        <v>45243</v>
       </c>
       <c r="V49" s="9" t="s">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="W49" s="10">
-        <v>-120</v>
+        <v>-384</v>
       </c>
       <c r="X49" s="12" t="str">
         <f ca="1">IF(Tabela1[[#This Row],[DATA_CURSO]]="",
@@ -6653,7 +6654,7 @@
 "VENCIDO – "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa"),
 "EM DIA – vence em "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa")),
 "NÃO É NECESSÁRIO RENOVAR")))</f>
-        <v>EM DIA – vence em 21/02/26</v>
+        <v>EM DIA – vence em 12/11/26</v>
       </c>
       <c r="Y49" s="12" t="str">
         <f>IF(Tabela1[[#This Row],[FILIAL]]=1,"SINOP",IF(Tabela1[[#This Row],[FILIAL]]=2,"DOURADOS",IF(Tabela1[[#This Row],[FILIAL]]=3,"NOVA MUTUM",IF(Tabela1[[#This Row],[FILIAL]]=4,"FULLING",IF(Tabela1[[#This Row],[FILIAL]]=5,"SÃO PAULO",IF(Tabela1[[#This Row],[FILIAL]]=6,"SIDROLÂNDIA",IF(Tabela1[[#This Row],[FILIAL]]=8,"BALSAS",IF(Tabela1[[#This Row],[FILIAL]]=10,"LUIS EDUARDO MAGALHÃES",""))))))))</f>
@@ -6666,18 +6667,18 @@
       <c r="AA49" t="str">
         <f ca="1">CONCATENATE("• ",
     Tabela1[[#This Row],[DESCRICAO]], " - ",Tabela1[[#This Row],[STATUS_GERAL]])</f>
-        <v>• NR 33 - SEGURANÇA E SAUDE NOS TRABALHOS EM ESPAÇOS CONFINADOS - VIGIA E TRABALHADOR - EM DIA – vence em 21/02/26</v>
+        <v>• NR 20 - SEG. E TRAB. INFLAMÁVEIS E COMBUSTIVEIS CLASSE III - BASICO - EM DIA – vence em 12/11/26</v>
       </c>
     </row>
     <row r="50" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A50" s="19">
-        <v>2</v>
+      <c r="A50" s="10">
+        <v>145</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C50" s="8">
-        <v>43587</v>
+        <v>43683</v>
       </c>
       <c r="D50" s="7" t="s">
         <v>110</v>
@@ -6695,22 +6696,22 @@
         <v>125</v>
       </c>
       <c r="I50" s="6">
-        <v>168</v>
+        <v>134</v>
       </c>
       <c r="J50" s="6">
-        <v>5060</v>
+        <v>5076</v>
       </c>
       <c r="K50" s="7" t="s">
         <v>126</v>
       </c>
       <c r="L50" s="6">
-        <v>123</v>
+        <v>266</v>
       </c>
       <c r="M50" s="7" t="s">
         <v>99</v>
       </c>
       <c r="N50" s="9" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="O50" s="9"/>
       <c r="P50" s="9" t="s">
@@ -6723,19 +6724,19 @@
         <v>1</v>
       </c>
       <c r="S50" s="10">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="T50" s="9" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="U50" s="11">
-        <v>45601</v>
+        <v>45812</v>
       </c>
       <c r="V50" s="9" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="W50" s="10">
-        <v>-12</v>
+        <v>-588</v>
       </c>
       <c r="X50" s="12" t="str">
         <f ca="1">IF(Tabela1[[#This Row],[DATA_CURSO]]="",
@@ -6747,7 +6748,7 @@
 "VENCIDO – "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa"),
 "EM DIA – vence em "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa")),
 "NÃO É NECESSÁRIO RENOVAR")))</f>
-        <v>EM DIA – vence em 05/11/25</v>
+        <v>EM DIA – vence em 04/06/27</v>
       </c>
       <c r="Y50" s="12" t="str">
         <f>IF(Tabela1[[#This Row],[FILIAL]]=1,"SINOP",IF(Tabela1[[#This Row],[FILIAL]]=2,"DOURADOS",IF(Tabela1[[#This Row],[FILIAL]]=3,"NOVA MUTUM",IF(Tabela1[[#This Row],[FILIAL]]=4,"FULLING",IF(Tabela1[[#This Row],[FILIAL]]=5,"SÃO PAULO",IF(Tabela1[[#This Row],[FILIAL]]=6,"SIDROLÂNDIA",IF(Tabela1[[#This Row],[FILIAL]]=8,"BALSAS",IF(Tabela1[[#This Row],[FILIAL]]=10,"LUIS EDUARDO MAGALHÃES",""))))))))</f>
@@ -6760,18 +6761,18 @@
       <c r="AA50" t="str">
         <f ca="1">CONCATENATE("• ",
     Tabela1[[#This Row],[DESCRICAO]], " - ",Tabela1[[#This Row],[STATUS_GERAL]])</f>
-        <v>• NR 20 - SEG. E TRAB. INFLAMÁVEIS E COMBUSTIVEIS CLASSE III - AVANÇADO - EM DIA – vence em 05/11/25</v>
+        <v>• NR 20 - SEG. E TRAB. INFLAMÁVEIS E COMBUSTIVEIS CLASSE III - INTERMEDIÁRIO - EM DIA – vence em 04/06/27</v>
       </c>
     </row>
     <row r="51" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A51" s="19">
-        <v>2</v>
+      <c r="A51" s="10">
+        <v>145</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C51" s="8">
-        <v>43587</v>
+        <v>43683</v>
       </c>
       <c r="D51" s="7" t="s">
         <v>110</v>
@@ -6789,22 +6790,22 @@
         <v>125</v>
       </c>
       <c r="I51" s="6">
-        <v>168</v>
+        <v>134</v>
       </c>
       <c r="J51" s="6">
-        <v>5060</v>
+        <v>5076</v>
       </c>
       <c r="K51" s="7" t="s">
         <v>126</v>
       </c>
       <c r="L51" s="6">
-        <v>295</v>
+        <v>28</v>
       </c>
       <c r="M51" s="7" t="s">
         <v>99</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="O51" s="9"/>
       <c r="P51" s="9" t="s">
@@ -6817,18 +6818,20 @@
         <v>1</v>
       </c>
       <c r="S51" s="10">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="T51" s="9" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="U51" s="11">
-        <v>45489</v>
+        <v>45349</v>
       </c>
       <c r="V51" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="W51" s="10"/>
+        <v>36</v>
+      </c>
+      <c r="W51" s="10">
+        <v>-125</v>
+      </c>
       <c r="X51" s="12" t="str">
         <f ca="1">IF(Tabela1[[#This Row],[DATA_CURSO]]="",
 "PENDENTE",
@@ -6839,7 +6842,7 @@
 "VENCIDO – "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa"),
 "EM DIA – vence em "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa")),
 "NÃO É NECESSÁRIO RENOVAR")))</f>
-        <v>EM DIA – não é necessário renovar</v>
+        <v>EM DIA – vence em 26/02/26</v>
       </c>
       <c r="Y51" s="12" t="str">
         <f>IF(Tabela1[[#This Row],[FILIAL]]=1,"SINOP",IF(Tabela1[[#This Row],[FILIAL]]=2,"DOURADOS",IF(Tabela1[[#This Row],[FILIAL]]=3,"NOVA MUTUM",IF(Tabela1[[#This Row],[FILIAL]]=4,"FULLING",IF(Tabela1[[#This Row],[FILIAL]]=5,"SÃO PAULO",IF(Tabela1[[#This Row],[FILIAL]]=6,"SIDROLÂNDIA",IF(Tabela1[[#This Row],[FILIAL]]=8,"BALSAS",IF(Tabela1[[#This Row],[FILIAL]]=10,"LUIS EDUARDO MAGALHÃES",""))))))))</f>
@@ -6852,18 +6855,18 @@
       <c r="AA51" t="str">
         <f ca="1">CONCATENATE("• ",
     Tabela1[[#This Row],[DESCRICAO]], " - ",Tabela1[[#This Row],[STATUS_GERAL]])</f>
-        <v>• NR 26 - SINALIZAÇÃO DE SEGURANÇA - EM DIA – não é necessário renovar</v>
-      </c>
-    </row>
-    <row r="52" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A52" s="19">
-        <v>2</v>
+        <v>• NR 35 - TRABALHO EM ALTURA - EM DIA – vence em 26/02/26</v>
+      </c>
+    </row>
+    <row r="52" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A52" s="10">
+        <v>159</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C52" s="8">
-        <v>43587</v>
+        <v>43683</v>
       </c>
       <c r="D52" s="7" t="s">
         <v>110</v>
@@ -6881,22 +6884,22 @@
         <v>125</v>
       </c>
       <c r="I52" s="6">
-        <v>168</v>
+        <v>134</v>
       </c>
       <c r="J52" s="6">
-        <v>5060</v>
+        <v>5076</v>
       </c>
       <c r="K52" s="7" t="s">
         <v>126</v>
       </c>
       <c r="L52" s="6">
-        <v>235</v>
+        <v>10</v>
       </c>
       <c r="M52" s="7" t="s">
         <v>99</v>
       </c>
       <c r="N52" s="9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O52" s="9"/>
       <c r="P52" s="9" t="s">
@@ -6909,19 +6912,19 @@
         <v>1</v>
       </c>
       <c r="S52" s="10">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="T52" s="9" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="U52" s="11">
-        <v>45544</v>
+        <v>44333</v>
       </c>
       <c r="V52" s="9" t="s">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="W52" s="10">
-        <v>-320</v>
+        <v>1256</v>
       </c>
       <c r="X52" s="12" t="str">
         <f ca="1">IF(Tabela1[[#This Row],[DATA_CURSO]]="",
@@ -6933,7 +6936,7 @@
 "VENCIDO – "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa"),
 "EM DIA – vence em "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa")),
 "NÃO É NECESSÁRIO RENOVAR")))</f>
-        <v>EM DIA – vence em 09/09/26</v>
+        <v>VENCIDO – 17/05/22</v>
       </c>
       <c r="Y52" s="12" t="str">
         <f>IF(Tabela1[[#This Row],[FILIAL]]=1,"SINOP",IF(Tabela1[[#This Row],[FILIAL]]=2,"DOURADOS",IF(Tabela1[[#This Row],[FILIAL]]=3,"NOVA MUTUM",IF(Tabela1[[#This Row],[FILIAL]]=4,"FULLING",IF(Tabela1[[#This Row],[FILIAL]]=5,"SÃO PAULO",IF(Tabela1[[#This Row],[FILIAL]]=6,"SIDROLÂNDIA",IF(Tabela1[[#This Row],[FILIAL]]=8,"BALSAS",IF(Tabela1[[#This Row],[FILIAL]]=10,"LUIS EDUARDO MAGALHÃES",""))))))))</f>
@@ -6946,18 +6949,18 @@
       <c r="AA52" t="str">
         <f ca="1">CONCATENATE("• ",
     Tabela1[[#This Row],[DESCRICAO]], " - ",Tabela1[[#This Row],[STATUS_GERAL]])</f>
-        <v>• NR 35 - TRABALHO EM ALTURA - EM DIA – vence em 09/09/26</v>
-      </c>
-    </row>
-    <row r="53" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A53" s="19">
-        <v>2</v>
+        <v>• NR 33 - SEGURANÇA E SAUDE NOS TRABALHOS EM ESPAÇOS CONFINADOS - VIGIA E TRABALHADOR - VENCIDO – 17/05/22</v>
+      </c>
+    </row>
+    <row r="53" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A53" s="10">
+        <v>159</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C53" s="8">
-        <v>43587</v>
+        <v>43683</v>
       </c>
       <c r="D53" s="7" t="s">
         <v>110</v>
@@ -6975,10 +6978,10 @@
         <v>125</v>
       </c>
       <c r="I53" s="6">
-        <v>168</v>
+        <v>134</v>
       </c>
       <c r="J53" s="6">
-        <v>5060</v>
+        <v>5076</v>
       </c>
       <c r="K53" s="7" t="s">
         <v>126</v>
@@ -6990,7 +6993,7 @@
         <v>99</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="O53" s="9"/>
       <c r="P53" s="9" t="s">
@@ -7000,7 +7003,7 @@
         <v>1</v>
       </c>
       <c r="R53" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S53" s="10">
         <v>114</v>
@@ -7009,13 +7012,13 @@
         <v>101</v>
       </c>
       <c r="U53" s="11">
-        <v>45757</v>
+        <v>45871</v>
       </c>
       <c r="V53" s="9" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="W53" s="10">
-        <v>-168</v>
+        <v>-647</v>
       </c>
       <c r="X53" s="12" t="str">
         <f ca="1">IF(Tabela1[[#This Row],[DATA_CURSO]]="",
@@ -7027,11 +7030,11 @@
 "VENCIDO – "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa"),
 "EM DIA – vence em "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa")),
 "NÃO É NECESSÁRIO RENOVAR")))</f>
-        <v>EM DIA – vence em 10/04/26</v>
+        <v>EM DIA – vence em 02/08/27</v>
       </c>
       <c r="Y53" s="12" t="str">
         <f>IF(Tabela1[[#This Row],[FILIAL]]=1,"SINOP",IF(Tabela1[[#This Row],[FILIAL]]=2,"DOURADOS",IF(Tabela1[[#This Row],[FILIAL]]=3,"NOVA MUTUM",IF(Tabela1[[#This Row],[FILIAL]]=4,"FULLING",IF(Tabela1[[#This Row],[FILIAL]]=5,"SÃO PAULO",IF(Tabela1[[#This Row],[FILIAL]]=6,"SIDROLÂNDIA",IF(Tabela1[[#This Row],[FILIAL]]=8,"BALSAS",IF(Tabela1[[#This Row],[FILIAL]]=10,"LUIS EDUARDO MAGALHÃES",""))))))))</f>
-        <v>DOURADOS</v>
+        <v>SINOP</v>
       </c>
       <c r="Z53" s="13" t="str">
         <f>VLOOKUP(N53,RENOVAÇÃO!A:D,4,0)</f>
@@ -7040,18 +7043,18 @@
       <c r="AA53" t="str">
         <f ca="1">CONCATENATE("• ",
     Tabela1[[#This Row],[DESCRICAO]], " - ",Tabela1[[#This Row],[STATUS_GERAL]])</f>
-        <v>• NR 33 - SEGURANÇA E SAUDE NOS TRABALHOS EM ESPAÇOS CONFINADOS - VIGIA E TRABALHADOR - EM DIA – vence em 10/04/26</v>
-      </c>
-    </row>
-    <row r="54" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A54" s="19">
-        <v>2</v>
+        <v>• NR 11 - OPERADOR PA CARREGADEIRA - EM DIA – vence em 02/08/27</v>
+      </c>
+    </row>
+    <row r="54" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A54" s="10">
+        <v>171</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C54" s="8">
-        <v>43587</v>
+        <v>43683</v>
       </c>
       <c r="D54" s="7" t="s">
         <v>110</v>
@@ -7069,22 +7072,22 @@
         <v>125</v>
       </c>
       <c r="I54" s="6">
-        <v>168</v>
+        <v>134</v>
       </c>
       <c r="J54" s="6">
-        <v>5060</v>
+        <v>5076</v>
       </c>
       <c r="K54" s="7" t="s">
         <v>126</v>
       </c>
       <c r="L54" s="6">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="M54" s="7" t="s">
         <v>99</v>
       </c>
       <c r="N54" s="9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="O54" s="9"/>
       <c r="P54" s="9" t="s">
@@ -7094,22 +7097,22 @@
         <v>1</v>
       </c>
       <c r="R54" s="10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S54" s="10">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="T54" s="9" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="U54" s="11">
-        <v>45918</v>
+        <v>45581</v>
       </c>
       <c r="V54" s="9" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="W54" s="10">
-        <v>-329</v>
+        <v>-357</v>
       </c>
       <c r="X54" s="12" t="str">
         <f ca="1">IF(Tabela1[[#This Row],[DATA_CURSO]]="",
@@ -7121,11 +7124,11 @@
 "VENCIDO – "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa"),
 "EM DIA – vence em "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa")),
 "NÃO É NECESSÁRIO RENOVAR")))</f>
-        <v>EM DIA – vence em 18/09/26</v>
+        <v>EM DIA – vence em 16/10/26</v>
       </c>
       <c r="Y54" s="12" t="str">
         <f>IF(Tabela1[[#This Row],[FILIAL]]=1,"SINOP",IF(Tabela1[[#This Row],[FILIAL]]=2,"DOURADOS",IF(Tabela1[[#This Row],[FILIAL]]=3,"NOVA MUTUM",IF(Tabela1[[#This Row],[FILIAL]]=4,"FULLING",IF(Tabela1[[#This Row],[FILIAL]]=5,"SÃO PAULO",IF(Tabela1[[#This Row],[FILIAL]]=6,"SIDROLÂNDIA",IF(Tabela1[[#This Row],[FILIAL]]=8,"BALSAS",IF(Tabela1[[#This Row],[FILIAL]]=10,"LUIS EDUARDO MAGALHÃES",""))))))))</f>
-        <v>SINOP</v>
+        <v>NOVA MUTUM</v>
       </c>
       <c r="Z54" s="13" t="str">
         <f>VLOOKUP(N54,RENOVAÇÃO!A:D,4,0)</f>
@@ -7134,18 +7137,18 @@
       <c r="AA54" t="str">
         <f ca="1">CONCATENATE("• ",
     Tabela1[[#This Row],[DESCRICAO]], " - ",Tabela1[[#This Row],[STATUS_GERAL]])</f>
-        <v>• NR 33 - SEGURANÇA E SAUDE NOS TRABALHOS EM ESPAÇOS CONFINADOS - VIGIA E TRABALHADOR - EM DIA – vence em 18/09/26</v>
-      </c>
-    </row>
-    <row r="55" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A55" s="19">
-        <v>2</v>
+        <v>• NR 35 - TRABALHO EM ALTURA - EM DIA – vence em 16/10/26</v>
+      </c>
+    </row>
+    <row r="55" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A55" s="10">
+        <v>171</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C55" s="8">
-        <v>43587</v>
+        <v>43683</v>
       </c>
       <c r="D55" s="7" t="s">
         <v>110</v>
@@ -7163,22 +7166,22 @@
         <v>125</v>
       </c>
       <c r="I55" s="6">
-        <v>168</v>
+        <v>134</v>
       </c>
       <c r="J55" s="6">
-        <v>5060</v>
+        <v>5076</v>
       </c>
       <c r="K55" s="7" t="s">
         <v>126</v>
       </c>
       <c r="L55" s="6">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="M55" s="7" t="s">
         <v>99</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>43</v>
+        <v>109</v>
       </c>
       <c r="O55" s="9"/>
       <c r="P55" s="9" t="s">
@@ -7188,23 +7191,21 @@
         <v>1</v>
       </c>
       <c r="R55" s="10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S55" s="10">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="T55" s="9" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="U55" s="11">
-        <v>45735</v>
+        <v>44820</v>
       </c>
       <c r="V55" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="W55" s="10">
-        <v>-876</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="W55" s="10"/>
       <c r="X55" s="12" t="str">
         <f ca="1">IF(Tabela1[[#This Row],[DATA_CURSO]]="",
 "PENDENTE",
@@ -7215,11 +7216,11 @@
 "VENCIDO – "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa"),
 "EM DIA – vence em "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa")),
 "NÃO É NECESSÁRIO RENOVAR")))</f>
-        <v>EM DIA – vence em 18/03/28</v>
+        <v>EM DIA – não é necessário renovar</v>
       </c>
       <c r="Y55" s="12" t="str">
         <f>IF(Tabela1[[#This Row],[FILIAL]]=1,"SINOP",IF(Tabela1[[#This Row],[FILIAL]]=2,"DOURADOS",IF(Tabela1[[#This Row],[FILIAL]]=3,"NOVA MUTUM",IF(Tabela1[[#This Row],[FILIAL]]=4,"FULLING",IF(Tabela1[[#This Row],[FILIAL]]=5,"SÃO PAULO",IF(Tabela1[[#This Row],[FILIAL]]=6,"SIDROLÂNDIA",IF(Tabela1[[#This Row],[FILIAL]]=8,"BALSAS",IF(Tabela1[[#This Row],[FILIAL]]=10,"LUIS EDUARDO MAGALHÃES",""))))))))</f>
-        <v>SINOP</v>
+        <v>NOVA MUTUM</v>
       </c>
       <c r="Z55" s="13" t="str">
         <f>VLOOKUP(N55,RENOVAÇÃO!A:D,4,0)</f>
@@ -7228,18 +7229,18 @@
       <c r="AA55" t="str">
         <f ca="1">CONCATENATE("• ",
     Tabela1[[#This Row],[DESCRICAO]], " - ",Tabela1[[#This Row],[STATUS_GERAL]])</f>
-        <v>• NR 20 - SEG. E TRAB. INFLAMÁVEIS E COMBUSTIVEIS CLASSE III - BASICO - EM DIA – vence em 18/03/28</v>
+        <v>• BLOQUEIO E SINALIZAÇÃO DE ENERGIAS PERIGOSAS - LOCKOUT/TAGOUT - NR10 E NR12 - EM DIA – não é necessário renovar</v>
       </c>
     </row>
     <row r="56" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A56" s="19">
-        <v>2</v>
+      <c r="A56" s="10">
+        <v>183</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C56" s="8">
-        <v>43587</v>
+        <v>43683</v>
       </c>
       <c r="D56" s="7" t="s">
         <v>110</v>
@@ -7257,22 +7258,22 @@
         <v>125</v>
       </c>
       <c r="I56" s="6">
-        <v>168</v>
+        <v>134</v>
       </c>
       <c r="J56" s="6">
-        <v>5060</v>
+        <v>5076</v>
       </c>
       <c r="K56" s="7" t="s">
         <v>126</v>
       </c>
       <c r="L56" s="6">
-        <v>28</v>
+        <v>308</v>
       </c>
       <c r="M56" s="7" t="s">
         <v>99</v>
       </c>
       <c r="N56" s="9" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="O56" s="9"/>
       <c r="P56" s="9" t="s">
@@ -7285,19 +7286,19 @@
         <v>1</v>
       </c>
       <c r="S56" s="10">
-        <v>78</v>
+        <v>102</v>
       </c>
       <c r="T56" s="9" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="U56" s="11">
-        <v>45602</v>
+        <v>45350</v>
       </c>
       <c r="V56" s="9" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="W56" s="10">
-        <v>-743</v>
+        <v>-126</v>
       </c>
       <c r="X56" s="12" t="str">
         <f ca="1">IF(Tabela1[[#This Row],[DATA_CURSO]]="",
@@ -7309,7 +7310,7 @@
 "VENCIDO – "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa"),
 "EM DIA – vence em "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa")),
 "NÃO É NECESSÁRIO RENOVAR")))</f>
-        <v>EM DIA – vence em 06/11/27</v>
+        <v>EM DIA – vence em 27/02/26</v>
       </c>
       <c r="Y56" s="12" t="str">
         <f>IF(Tabela1[[#This Row],[FILIAL]]=1,"SINOP",IF(Tabela1[[#This Row],[FILIAL]]=2,"DOURADOS",IF(Tabela1[[#This Row],[FILIAL]]=3,"NOVA MUTUM",IF(Tabela1[[#This Row],[FILIAL]]=4,"FULLING",IF(Tabela1[[#This Row],[FILIAL]]=5,"SÃO PAULO",IF(Tabela1[[#This Row],[FILIAL]]=6,"SIDROLÂNDIA",IF(Tabela1[[#This Row],[FILIAL]]=8,"BALSAS",IF(Tabela1[[#This Row],[FILIAL]]=10,"LUIS EDUARDO MAGALHÃES",""))))))))</f>
@@ -7322,18 +7323,18 @@
       <c r="AA56" t="str">
         <f ca="1">CONCATENATE("• ",
     Tabela1[[#This Row],[DESCRICAO]], " - ",Tabela1[[#This Row],[STATUS_GERAL]])</f>
-        <v>• NR 20 - SEG. E TRAB. INFLAMÁVEIS E COMBUSTIVEIS CLASSE III - BASICO - EM DIA – vence em 06/11/27</v>
-      </c>
-    </row>
-    <row r="57" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A57" s="19">
-        <v>2</v>
+        <v>• NR 35 - TRABALHO EM ALTURA - EM DIA – vence em 27/02/26</v>
+      </c>
+    </row>
+    <row r="57" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A57" s="10">
+        <v>183</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C57" s="8">
-        <v>43587</v>
+        <v>43683</v>
       </c>
       <c r="D57" s="7" t="s">
         <v>110</v>
@@ -7351,22 +7352,22 @@
         <v>125</v>
       </c>
       <c r="I57" s="6">
-        <v>168</v>
+        <v>134</v>
       </c>
       <c r="J57" s="6">
-        <v>5060</v>
+        <v>5076</v>
       </c>
       <c r="K57" s="7" t="s">
         <v>126</v>
       </c>
       <c r="L57" s="6">
-        <v>11</v>
+        <v>321</v>
       </c>
       <c r="M57" s="7" t="s">
         <v>99</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="O57" s="9"/>
       <c r="P57" s="9" t="s">
@@ -7376,22 +7377,22 @@
         <v>1</v>
       </c>
       <c r="R57" s="10">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="S57" s="10">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="T57" s="9" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="U57" s="11">
-        <v>45404</v>
+        <v>45693</v>
       </c>
       <c r="V57" s="9" t="s">
         <v>36</v>
       </c>
       <c r="W57" s="10">
-        <v>-180</v>
+        <v>-469</v>
       </c>
       <c r="X57" s="12" t="str">
         <f ca="1">IF(Tabela1[[#This Row],[DATA_CURSO]]="",
@@ -7403,11 +7404,11 @@
 "VENCIDO – "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa"),
 "EM DIA – vence em "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa")),
 "NÃO É NECESSÁRIO RENOVAR")))</f>
-        <v>EM DIA – vence em 22/04/26</v>
+        <v>EM DIA – vence em 05/02/27</v>
       </c>
       <c r="Y57" s="12" t="str">
         <f>IF(Tabela1[[#This Row],[FILIAL]]=1,"SINOP",IF(Tabela1[[#This Row],[FILIAL]]=2,"DOURADOS",IF(Tabela1[[#This Row],[FILIAL]]=3,"NOVA MUTUM",IF(Tabela1[[#This Row],[FILIAL]]=4,"FULLING",IF(Tabela1[[#This Row],[FILIAL]]=5,"SÃO PAULO",IF(Tabela1[[#This Row],[FILIAL]]=6,"SIDROLÂNDIA",IF(Tabela1[[#This Row],[FILIAL]]=8,"BALSAS",IF(Tabela1[[#This Row],[FILIAL]]=10,"LUIS EDUARDO MAGALHÃES",""))))))))</f>
-        <v>SINOP</v>
+        <v>SIDROLÂNDIA</v>
       </c>
       <c r="Z57" s="13" t="str">
         <f>VLOOKUP(N57,RENOVAÇÃO!A:D,4,0)</f>
@@ -7416,18 +7417,18 @@
       <c r="AA57" t="str">
         <f ca="1">CONCATENATE("• ",
     Tabela1[[#This Row],[DESCRICAO]], " - ",Tabela1[[#This Row],[STATUS_GERAL]])</f>
-        <v>• NR 35 - TRABALHO EM ALTURA - EM DIA – vence em 22/04/26</v>
-      </c>
-    </row>
-    <row r="58" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A58" s="19">
-        <v>2</v>
+        <v>• NR 20 - SEG. E TRAB. INFLAMÁVEIS E COMBUSTIVEIS CLASSE III - INTERMEDIÁRIO - EM DIA – vence em 05/02/27</v>
+      </c>
+    </row>
+    <row r="58" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A58" s="10">
+        <v>183</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C58" s="8">
-        <v>43587</v>
+        <v>43683</v>
       </c>
       <c r="D58" s="7" t="s">
         <v>110</v>
@@ -7445,22 +7446,22 @@
         <v>125</v>
       </c>
       <c r="I58" s="6">
-        <v>168</v>
+        <v>134</v>
       </c>
       <c r="J58" s="6">
-        <v>5060</v>
+        <v>5076</v>
       </c>
       <c r="K58" s="7" t="s">
         <v>126</v>
       </c>
       <c r="L58" s="6">
-        <v>26</v>
+        <v>319</v>
       </c>
       <c r="M58" s="7" t="s">
         <v>99</v>
       </c>
       <c r="N58" s="9" t="s">
-        <v>109</v>
+        <v>46</v>
       </c>
       <c r="O58" s="9"/>
       <c r="P58" s="9" t="s">
@@ -7470,16 +7471,16 @@
         <v>1</v>
       </c>
       <c r="R58" s="10">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="S58" s="10">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="T58" s="9" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="U58" s="11">
-        <v>44698</v>
+        <v>45489</v>
       </c>
       <c r="V58" s="9" t="s">
         <v>5</v>
@@ -7499,7 +7500,7 @@
       </c>
       <c r="Y58" s="12" t="str">
         <f>IF(Tabela1[[#This Row],[FILIAL]]=1,"SINOP",IF(Tabela1[[#This Row],[FILIAL]]=2,"DOURADOS",IF(Tabela1[[#This Row],[FILIAL]]=3,"NOVA MUTUM",IF(Tabela1[[#This Row],[FILIAL]]=4,"FULLING",IF(Tabela1[[#This Row],[FILIAL]]=5,"SÃO PAULO",IF(Tabela1[[#This Row],[FILIAL]]=6,"SIDROLÂNDIA",IF(Tabela1[[#This Row],[FILIAL]]=8,"BALSAS",IF(Tabela1[[#This Row],[FILIAL]]=10,"LUIS EDUARDO MAGALHÃES",""))))))))</f>
-        <v>BALSAS</v>
+        <v>NOVA MUTUM</v>
       </c>
       <c r="Z58" s="13" t="str">
         <f>VLOOKUP(N58,RENOVAÇÃO!A:D,4,0)</f>
@@ -7508,18 +7509,18 @@
       <c r="AA58" t="str">
         <f ca="1">CONCATENATE("• ",
     Tabela1[[#This Row],[DESCRICAO]], " - ",Tabela1[[#This Row],[STATUS_GERAL]])</f>
-        <v>• BLOQUEIO E SINALIZAÇÃO DE ENERGIAS PERIGOSAS - LOCKOUT/TAGOUT - NR10 E NR12 - EM DIA – não é necessário renovar</v>
+        <v>• NR 26 - SINALIZAÇÃO DE SEGURANÇA - EM DIA – não é necessário renovar</v>
       </c>
     </row>
     <row r="59" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A59" s="19">
-        <v>2</v>
+      <c r="A59" s="10">
+        <v>188</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C59" s="8">
-        <v>43587</v>
+        <v>43683</v>
       </c>
       <c r="D59" s="7" t="s">
         <v>110</v>
@@ -7537,22 +7538,22 @@
         <v>125</v>
       </c>
       <c r="I59" s="6">
-        <v>168</v>
+        <v>134</v>
       </c>
       <c r="J59" s="6">
-        <v>5060</v>
+        <v>5076</v>
       </c>
       <c r="K59" s="7" t="s">
         <v>126</v>
       </c>
       <c r="L59" s="6">
-        <v>2</v>
+        <v>302</v>
       </c>
       <c r="M59" s="7" t="s">
         <v>99</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>45</v>
+        <v>109</v>
       </c>
       <c r="O59" s="9"/>
       <c r="P59" s="9" t="s">
@@ -7565,20 +7566,18 @@
         <v>3</v>
       </c>
       <c r="S59" s="10">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="T59" s="9" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="U59" s="11">
-        <v>45826</v>
+        <v>44878</v>
       </c>
       <c r="V59" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="W59" s="10">
-        <v>-602</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="W59" s="10"/>
       <c r="X59" s="12" t="str">
         <f ca="1">IF(Tabela1[[#This Row],[DATA_CURSO]]="",
 "PENDENTE",
@@ -7589,7 +7588,7 @@
 "VENCIDO – "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa"),
 "EM DIA – vence em "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa")),
 "NÃO É NECESSÁRIO RENOVAR")))</f>
-        <v>EM DIA – vence em 18/06/27</v>
+        <v>EM DIA – não é necessário renovar</v>
       </c>
       <c r="Y59" s="12" t="str">
         <f>IF(Tabela1[[#This Row],[FILIAL]]=1,"SINOP",IF(Tabela1[[#This Row],[FILIAL]]=2,"DOURADOS",IF(Tabela1[[#This Row],[FILIAL]]=3,"NOVA MUTUM",IF(Tabela1[[#This Row],[FILIAL]]=4,"FULLING",IF(Tabela1[[#This Row],[FILIAL]]=5,"SÃO PAULO",IF(Tabela1[[#This Row],[FILIAL]]=6,"SIDROLÂNDIA",IF(Tabela1[[#This Row],[FILIAL]]=8,"BALSAS",IF(Tabela1[[#This Row],[FILIAL]]=10,"LUIS EDUARDO MAGALHÃES",""))))))))</f>
@@ -7602,18 +7601,18 @@
       <c r="AA59" t="str">
         <f ca="1">CONCATENATE("• ",
     Tabela1[[#This Row],[DESCRICAO]], " - ",Tabela1[[#This Row],[STATUS_GERAL]])</f>
-        <v>• NR 20 - SEG. E TRAB. INFLAMÁVEIS E COMBUSTIVEIS CLASSE III - INTERMEDIÁRIO - EM DIA – vence em 18/06/27</v>
-      </c>
-    </row>
-    <row r="60" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A60" s="19">
-        <v>2</v>
+        <v>• BLOQUEIO E SINALIZAÇÃO DE ENERGIAS PERIGOSAS - LOCKOUT/TAGOUT - NR10 E NR12 - EM DIA – não é necessário renovar</v>
+      </c>
+    </row>
+    <row r="60" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A60" s="10">
+        <v>189</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C60" s="8">
-        <v>43587</v>
+        <v>43683</v>
       </c>
       <c r="D60" s="7" t="s">
         <v>110</v>
@@ -7631,22 +7630,22 @@
         <v>125</v>
       </c>
       <c r="I60" s="6">
-        <v>168</v>
+        <v>134</v>
       </c>
       <c r="J60" s="6">
-        <v>5060</v>
+        <v>5076</v>
       </c>
       <c r="K60" s="7" t="s">
         <v>126</v>
       </c>
       <c r="L60" s="6">
-        <v>323</v>
+        <v>300</v>
       </c>
       <c r="M60" s="7" t="s">
         <v>99</v>
       </c>
       <c r="N60" s="9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="O60" s="9"/>
       <c r="P60" s="9" t="s">
@@ -7659,19 +7658,19 @@
         <v>3</v>
       </c>
       <c r="S60" s="10">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="T60" s="9" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="U60" s="11">
-        <v>45827</v>
+        <v>45371</v>
       </c>
       <c r="V60" s="9" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="W60" s="10">
-        <v>-238</v>
+        <v>-147</v>
       </c>
       <c r="X60" s="12" t="str">
         <f ca="1">IF(Tabela1[[#This Row],[DATA_CURSO]]="",
@@ -7683,7 +7682,7 @@
 "VENCIDO – "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa"),
 "EM DIA – vence em "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa")),
 "NÃO É NECESSÁRIO RENOVAR")))</f>
-        <v>EM DIA – vence em 19/06/26</v>
+        <v>EM DIA – vence em 20/03/26</v>
       </c>
       <c r="Y60" s="12" t="str">
         <f>IF(Tabela1[[#This Row],[FILIAL]]=1,"SINOP",IF(Tabela1[[#This Row],[FILIAL]]=2,"DOURADOS",IF(Tabela1[[#This Row],[FILIAL]]=3,"NOVA MUTUM",IF(Tabela1[[#This Row],[FILIAL]]=4,"FULLING",IF(Tabela1[[#This Row],[FILIAL]]=5,"SÃO PAULO",IF(Tabela1[[#This Row],[FILIAL]]=6,"SIDROLÂNDIA",IF(Tabela1[[#This Row],[FILIAL]]=8,"BALSAS",IF(Tabela1[[#This Row],[FILIAL]]=10,"LUIS EDUARDO MAGALHÃES",""))))))))</f>
@@ -7696,18 +7695,18 @@
       <c r="AA60" t="str">
         <f ca="1">CONCATENATE("• ",
     Tabela1[[#This Row],[DESCRICAO]], " - ",Tabela1[[#This Row],[STATUS_GERAL]])</f>
-        <v>• NR 33 - SEGURANÇA E SAUDE NOS TRABALHOS EM ESPAÇOS CONFINADOS - VIGIA E TRABALHADOR - EM DIA – vence em 19/06/26</v>
+        <v>• NR 35 - TRABALHO EM ALTURA - EM DIA – vence em 20/03/26</v>
       </c>
     </row>
     <row r="61" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A61" s="19">
-        <v>2</v>
+      <c r="A61" s="10">
+        <v>192</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C61" s="8">
-        <v>43587</v>
+        <v>43683</v>
       </c>
       <c r="D61" s="7" t="s">
         <v>110</v>
@@ -7725,22 +7724,22 @@
         <v>125</v>
       </c>
       <c r="I61" s="6">
-        <v>168</v>
+        <v>134</v>
       </c>
       <c r="J61" s="6">
-        <v>5060</v>
+        <v>5076</v>
       </c>
       <c r="K61" s="7" t="s">
         <v>126</v>
       </c>
       <c r="L61" s="6">
-        <v>104</v>
+        <v>295</v>
       </c>
       <c r="M61" s="7" t="s">
         <v>99</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="O61" s="9"/>
       <c r="P61" s="9" t="s">
@@ -7750,22 +7749,22 @@
         <v>1</v>
       </c>
       <c r="R61" s="10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="S61" s="10">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="T61" s="9" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="U61" s="11">
-        <v>45717</v>
+        <v>45390</v>
       </c>
       <c r="V61" s="9" t="s">
         <v>13</v>
       </c>
       <c r="W61" s="10">
-        <v>-128</v>
+        <v>199</v>
       </c>
       <c r="X61" s="12" t="str">
         <f ca="1">IF(Tabela1[[#This Row],[DATA_CURSO]]="",
@@ -7777,11 +7776,11 @@
 "VENCIDO – "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa"),
 "EM DIA – vence em "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa")),
 "NÃO É NECESSÁRIO RENOVAR")))</f>
-        <v>EM DIA – vence em 01/03/26</v>
+        <v>VENCIDO – 08/04/25</v>
       </c>
       <c r="Y61" s="12" t="str">
         <f>IF(Tabela1[[#This Row],[FILIAL]]=1,"SINOP",IF(Tabela1[[#This Row],[FILIAL]]=2,"DOURADOS",IF(Tabela1[[#This Row],[FILIAL]]=3,"NOVA MUTUM",IF(Tabela1[[#This Row],[FILIAL]]=4,"FULLING",IF(Tabela1[[#This Row],[FILIAL]]=5,"SÃO PAULO",IF(Tabela1[[#This Row],[FILIAL]]=6,"SIDROLÂNDIA",IF(Tabela1[[#This Row],[FILIAL]]=8,"BALSAS",IF(Tabela1[[#This Row],[FILIAL]]=10,"LUIS EDUARDO MAGALHÃES",""))))))))</f>
-        <v>BALSAS</v>
+        <v>LUIS EDUARDO MAGALHÃES</v>
       </c>
       <c r="Z61" s="13" t="str">
         <f>VLOOKUP(N61,RENOVAÇÃO!A:D,4,0)</f>
@@ -7790,18 +7789,18 @@
       <c r="AA61" t="str">
         <f ca="1">CONCATENATE("• ",
     Tabela1[[#This Row],[DESCRICAO]], " - ",Tabela1[[#This Row],[STATUS_GERAL]])</f>
-        <v>• NR 33 - SEGURANÇA E SAUDE NOS TRABALHOS EM ESPAÇOS CONFINADOS - VIGIA E TRABALHADOR - EM DIA – vence em 01/03/26</v>
+        <v>• NR 20 - SEG. E TRAB. INFLAMÁVEIS E COMBUSTIVEIS CLASSE III - AVANÇADO - VENCIDO – 08/04/25</v>
       </c>
     </row>
     <row r="62" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A62" s="19">
-        <v>2</v>
+      <c r="A62" s="10">
+        <v>193</v>
       </c>
       <c r="B62" s="7" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C62" s="8">
-        <v>43587</v>
+        <v>43683</v>
       </c>
       <c r="D62" s="7" t="s">
         <v>110</v>
@@ -7819,16 +7818,16 @@
         <v>125</v>
       </c>
       <c r="I62" s="6">
-        <v>168</v>
+        <v>134</v>
       </c>
       <c r="J62" s="6">
-        <v>5060</v>
+        <v>5076</v>
       </c>
       <c r="K62" s="7" t="s">
         <v>126</v>
       </c>
       <c r="L62" s="6">
-        <v>302</v>
+        <v>235</v>
       </c>
       <c r="M62" s="7" t="s">
         <v>99</v>
@@ -7844,22 +7843,22 @@
         <v>1</v>
       </c>
       <c r="R62" s="10">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="S62" s="10">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="T62" s="9" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="U62" s="11">
-        <v>45569</v>
+        <v>45827</v>
       </c>
       <c r="V62" s="9" t="s">
         <v>36</v>
       </c>
       <c r="W62" s="10">
-        <v>-345</v>
+        <v>-603</v>
       </c>
       <c r="X62" s="12" t="str">
         <f ca="1">IF(Tabela1[[#This Row],[DATA_CURSO]]="",
@@ -7871,11 +7870,11 @@
 "VENCIDO – "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa"),
 "EM DIA – vence em "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa")),
 "NÃO É NECESSÁRIO RENOVAR")))</f>
-        <v>EM DIA – vence em 04/10/26</v>
+        <v>EM DIA – vence em 19/06/27</v>
       </c>
       <c r="Y62" s="12" t="str">
         <f>IF(Tabela1[[#This Row],[FILIAL]]=1,"SINOP",IF(Tabela1[[#This Row],[FILIAL]]=2,"DOURADOS",IF(Tabela1[[#This Row],[FILIAL]]=3,"NOVA MUTUM",IF(Tabela1[[#This Row],[FILIAL]]=4,"FULLING",IF(Tabela1[[#This Row],[FILIAL]]=5,"SÃO PAULO",IF(Tabela1[[#This Row],[FILIAL]]=6,"SIDROLÂNDIA",IF(Tabela1[[#This Row],[FILIAL]]=8,"BALSAS",IF(Tabela1[[#This Row],[FILIAL]]=10,"LUIS EDUARDO MAGALHÃES",""))))))))</f>
-        <v>BALSAS</v>
+        <v>SINOP</v>
       </c>
       <c r="Z62" s="13" t="str">
         <f>VLOOKUP(N62,RENOVAÇÃO!A:D,4,0)</f>
@@ -7884,18 +7883,18 @@
       <c r="AA62" t="str">
         <f ca="1">CONCATENATE("• ",
     Tabela1[[#This Row],[DESCRICAO]], " - ",Tabela1[[#This Row],[STATUS_GERAL]])</f>
-        <v>• NR 35 - TRABALHO EM ALTURA - EM DIA – vence em 04/10/26</v>
+        <v>• NR 35 - TRABALHO EM ALTURA - EM DIA – vence em 19/06/27</v>
       </c>
     </row>
     <row r="63" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A63" s="19">
-        <v>2</v>
+      <c r="A63" s="10">
+        <v>193</v>
       </c>
       <c r="B63" s="7" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C63" s="8">
-        <v>43587</v>
+        <v>43683</v>
       </c>
       <c r="D63" s="7" t="s">
         <v>110</v>
@@ -7913,22 +7912,22 @@
         <v>125</v>
       </c>
       <c r="I63" s="6">
-        <v>168</v>
+        <v>134</v>
       </c>
       <c r="J63" s="6">
-        <v>5060</v>
+        <v>5076</v>
       </c>
       <c r="K63" s="7" t="s">
         <v>126</v>
       </c>
       <c r="L63" s="6">
-        <v>308</v>
+        <v>323</v>
       </c>
       <c r="M63" s="7" t="s">
         <v>99</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="O63" s="9"/>
       <c r="P63" s="9" t="s">
@@ -7941,13 +7940,13 @@
         <v>1</v>
       </c>
       <c r="S63" s="10">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="T63" s="9" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="U63" s="11">
-        <v>44510</v>
+        <v>45489</v>
       </c>
       <c r="V63" s="9" t="s">
         <v>5</v>
@@ -7976,18 +7975,18 @@
       <c r="AA63" t="str">
         <f ca="1">CONCATENATE("• ",
     Tabela1[[#This Row],[DESCRICAO]], " - ",Tabela1[[#This Row],[STATUS_GERAL]])</f>
-        <v>• DIREÇÃO DEFENSIVA - TEÓRICO - EM DIA – não é necessário renovar</v>
-      </c>
-    </row>
-    <row r="64" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A64" s="19">
-        <v>2</v>
+        <v>• NR 26 - SINALIZAÇÃO DE SEGURANÇA - EM DIA – não é necessário renovar</v>
+      </c>
+    </row>
+    <row r="64" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A64" s="10">
+        <v>193</v>
       </c>
       <c r="B64" s="7" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C64" s="8">
-        <v>43587</v>
+        <v>43683</v>
       </c>
       <c r="D64" s="7" t="s">
         <v>110</v>
@@ -8005,22 +8004,22 @@
         <v>125</v>
       </c>
       <c r="I64" s="6">
-        <v>168</v>
+        <v>134</v>
       </c>
       <c r="J64" s="6">
-        <v>5060</v>
+        <v>5076</v>
       </c>
       <c r="K64" s="7" t="s">
         <v>126</v>
       </c>
       <c r="L64" s="6">
-        <v>322</v>
+        <v>200</v>
       </c>
       <c r="M64" s="7" t="s">
         <v>99</v>
       </c>
       <c r="N64" s="9" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="O64" s="9"/>
       <c r="P64" s="9" t="s">
@@ -8033,18 +8032,20 @@
         <v>3</v>
       </c>
       <c r="S64" s="10">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="T64" s="9" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="U64" s="11">
-        <v>44771</v>
+        <v>45911</v>
       </c>
       <c r="V64" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="W64" s="10"/>
+        <v>13</v>
+      </c>
+      <c r="W64" s="10">
+        <v>-322</v>
+      </c>
       <c r="X64" s="12" t="str">
         <f ca="1">IF(Tabela1[[#This Row],[DATA_CURSO]]="",
 "PENDENTE",
@@ -8055,7 +8056,7 @@
 "VENCIDO – "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa"),
 "EM DIA – vence em "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa")),
 "NÃO É NECESSÁRIO RENOVAR")))</f>
-        <v>EM DIA – não é necessário renovar</v>
+        <v>EM DIA – vence em 11/09/26</v>
       </c>
       <c r="Y64" s="12" t="str">
         <f>IF(Tabela1[[#This Row],[FILIAL]]=1,"SINOP",IF(Tabela1[[#This Row],[FILIAL]]=2,"DOURADOS",IF(Tabela1[[#This Row],[FILIAL]]=3,"NOVA MUTUM",IF(Tabela1[[#This Row],[FILIAL]]=4,"FULLING",IF(Tabela1[[#This Row],[FILIAL]]=5,"SÃO PAULO",IF(Tabela1[[#This Row],[FILIAL]]=6,"SIDROLÂNDIA",IF(Tabela1[[#This Row],[FILIAL]]=8,"BALSAS",IF(Tabela1[[#This Row],[FILIAL]]=10,"LUIS EDUARDO MAGALHÃES",""))))))))</f>
@@ -8068,18 +8069,18 @@
       <c r="AA64" t="str">
         <f ca="1">CONCATENATE("• ",
     Tabela1[[#This Row],[DESCRICAO]], " - ",Tabela1[[#This Row],[STATUS_GERAL]])</f>
-        <v>• NR 13 - SEGURANÇA NA OPERAÇÃO VASOS DE PRESSÃO - EM DIA – não é necessário renovar</v>
+        <v>• NR 33 - SEGURANÇA E SAUDE NOS TRABALHOS EM ESPAÇOS CONFINADOS - VIGIA E TRABALHADOR - EM DIA – vence em 11/09/26</v>
       </c>
     </row>
     <row r="65" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A65" s="19">
-        <v>2</v>
+      <c r="A65" s="10">
+        <v>193</v>
       </c>
       <c r="B65" s="7" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C65" s="8">
-        <v>43587</v>
+        <v>43683</v>
       </c>
       <c r="D65" s="7" t="s">
         <v>110</v>
@@ -8097,10 +8098,10 @@
         <v>125</v>
       </c>
       <c r="I65" s="6">
-        <v>168</v>
+        <v>134</v>
       </c>
       <c r="J65" s="6">
-        <v>5060</v>
+        <v>5076</v>
       </c>
       <c r="K65" s="7" t="s">
         <v>126</v>
@@ -8131,13 +8132,13 @@
         <v>104</v>
       </c>
       <c r="U65" s="11">
-        <v>45181</v>
+        <v>44887</v>
       </c>
       <c r="V65" s="9" t="s">
         <v>36</v>
       </c>
       <c r="W65" s="10">
-        <v>43</v>
+        <v>337</v>
       </c>
       <c r="X65" s="12" t="str">
         <f ca="1">IF(Tabela1[[#This Row],[DATA_CURSO]]="",
@@ -8149,7 +8150,7 @@
 "VENCIDO – "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa"),
 "EM DIA – vence em "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa")),
 "NÃO É NECESSÁRIO RENOVAR")))</f>
-        <v>VENCIDO – 11/09/25</v>
+        <v>VENCIDO – 21/11/24</v>
       </c>
       <c r="Y65" s="12" t="str">
         <f>IF(Tabela1[[#This Row],[FILIAL]]=1,"SINOP",IF(Tabela1[[#This Row],[FILIAL]]=2,"DOURADOS",IF(Tabela1[[#This Row],[FILIAL]]=3,"NOVA MUTUM",IF(Tabela1[[#This Row],[FILIAL]]=4,"FULLING",IF(Tabela1[[#This Row],[FILIAL]]=5,"SÃO PAULO",IF(Tabela1[[#This Row],[FILIAL]]=6,"SIDROLÂNDIA",IF(Tabela1[[#This Row],[FILIAL]]=8,"BALSAS",IF(Tabela1[[#This Row],[FILIAL]]=10,"LUIS EDUARDO MAGALHÃES",""))))))))</f>
@@ -8162,18 +8163,18 @@
       <c r="AA65" t="str">
         <f ca="1">CONCATENATE("• ",
     Tabela1[[#This Row],[DESCRICAO]], " - ",Tabela1[[#This Row],[STATUS_GERAL]])</f>
-        <v>• NR 11 - OPERAÇÃO DE TALHAS E PONTE ROLANTE - VENCIDO – 11/09/25</v>
+        <v>• NR 11 - OPERAÇÃO DE TALHAS E PONTE ROLANTE - VENCIDO – 21/11/24</v>
       </c>
     </row>
     <row r="66" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A66" s="19">
-        <v>2</v>
+      <c r="A66" s="10">
+        <v>199</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C66" s="8">
-        <v>43587</v>
+        <v>43683</v>
       </c>
       <c r="D66" s="7" t="s">
         <v>110</v>
@@ -8191,10 +8192,10 @@
         <v>125</v>
       </c>
       <c r="I66" s="6">
-        <v>168</v>
+        <v>134</v>
       </c>
       <c r="J66" s="6">
-        <v>5060</v>
+        <v>5076</v>
       </c>
       <c r="K66" s="7" t="s">
         <v>126</v>
@@ -8206,7 +8207,7 @@
         <v>99</v>
       </c>
       <c r="N66" s="9" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="O66" s="9"/>
       <c r="P66" s="9" t="s">
@@ -8216,7 +8217,7 @@
         <v>1</v>
       </c>
       <c r="R66" s="10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S66" s="10">
         <v>102</v>
@@ -8225,14 +8226,12 @@
         <v>106</v>
       </c>
       <c r="U66" s="11">
-        <v>45349</v>
+        <v>44608</v>
       </c>
       <c r="V66" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="W66" s="10">
-        <v>-125</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="W66" s="10"/>
       <c r="X66" s="12" t="str">
         <f ca="1">IF(Tabela1[[#This Row],[DATA_CURSO]]="",
 "PENDENTE",
@@ -8243,11 +8242,11 @@
 "VENCIDO – "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa"),
 "EM DIA – vence em "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa")),
 "NÃO É NECESSÁRIO RENOVAR")))</f>
-        <v>EM DIA – vence em 26/02/26</v>
+        <v>EM DIA – não é necessário renovar</v>
       </c>
       <c r="Y66" s="12" t="str">
         <f>IF(Tabela1[[#This Row],[FILIAL]]=1,"SINOP",IF(Tabela1[[#This Row],[FILIAL]]=2,"DOURADOS",IF(Tabela1[[#This Row],[FILIAL]]=3,"NOVA MUTUM",IF(Tabela1[[#This Row],[FILIAL]]=4,"FULLING",IF(Tabela1[[#This Row],[FILIAL]]=5,"SÃO PAULO",IF(Tabela1[[#This Row],[FILIAL]]=6,"SIDROLÂNDIA",IF(Tabela1[[#This Row],[FILIAL]]=8,"BALSAS",IF(Tabela1[[#This Row],[FILIAL]]=10,"LUIS EDUARDO MAGALHÃES",""))))))))</f>
-        <v>NOVA MUTUM</v>
+        <v>SINOP</v>
       </c>
       <c r="Z66" s="13" t="str">
         <f>VLOOKUP(N66,RENOVAÇÃO!A:D,4,0)</f>
@@ -8256,18 +8255,18 @@
       <c r="AA66" t="str">
         <f ca="1">CONCATENATE("• ",
     Tabela1[[#This Row],[DESCRICAO]], " - ",Tabela1[[#This Row],[STATUS_GERAL]])</f>
-        <v>• NR 35 - TRABALHO EM ALTURA - EM DIA – vence em 26/02/26</v>
+        <v>• NR 13 - SEGURANÇA NA OPERAÇÃO VASOS DE PRESSÃO - EM DIA – não é necessário renovar</v>
       </c>
     </row>
     <row r="67" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A67" s="19">
-        <v>2</v>
+      <c r="A67" s="10">
+        <v>201</v>
       </c>
       <c r="B67" s="7" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C67" s="8">
-        <v>43587</v>
+        <v>43683</v>
       </c>
       <c r="D67" s="7" t="s">
         <v>110</v>
@@ -8285,22 +8284,22 @@
         <v>125</v>
       </c>
       <c r="I67" s="6">
-        <v>168</v>
+        <v>134</v>
       </c>
       <c r="J67" s="6">
-        <v>5060</v>
+        <v>5076</v>
       </c>
       <c r="K67" s="7" t="s">
         <v>126</v>
       </c>
       <c r="L67" s="6">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="M67" s="7" t="s">
         <v>99</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="O67" s="9"/>
       <c r="P67" s="9" t="s">
@@ -8313,20 +8312,18 @@
         <v>1</v>
       </c>
       <c r="S67" s="10">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="T67" s="9" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="U67" s="11">
-        <v>45735</v>
+        <v>45489</v>
       </c>
       <c r="V67" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="W67" s="10">
-        <v>-876</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="W67" s="10"/>
       <c r="X67" s="12" t="str">
         <f ca="1">IF(Tabela1[[#This Row],[DATA_CURSO]]="",
 "PENDENTE",
@@ -8337,7 +8334,7 @@
 "VENCIDO – "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa"),
 "EM DIA – vence em "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa")),
 "NÃO É NECESSÁRIO RENOVAR")))</f>
-        <v>EM DIA – vence em 18/03/28</v>
+        <v>EM DIA – não é necessário renovar</v>
       </c>
       <c r="Y67" s="12" t="str">
         <f>IF(Tabela1[[#This Row],[FILIAL]]=1,"SINOP",IF(Tabela1[[#This Row],[FILIAL]]=2,"DOURADOS",IF(Tabela1[[#This Row],[FILIAL]]=3,"NOVA MUTUM",IF(Tabela1[[#This Row],[FILIAL]]=4,"FULLING",IF(Tabela1[[#This Row],[FILIAL]]=5,"SÃO PAULO",IF(Tabela1[[#This Row],[FILIAL]]=6,"SIDROLÂNDIA",IF(Tabela1[[#This Row],[FILIAL]]=8,"BALSAS",IF(Tabela1[[#This Row],[FILIAL]]=10,"LUIS EDUARDO MAGALHÃES",""))))))))</f>
@@ -8350,18 +8347,18 @@
       <c r="AA67" t="str">
         <f ca="1">CONCATENATE("• ",
     Tabela1[[#This Row],[DESCRICAO]], " - ",Tabela1[[#This Row],[STATUS_GERAL]])</f>
-        <v>• NR 20 - SEG. E TRAB. INFLAMÁVEIS E COMBUSTIVEIS CLASSE III - BASICO - EM DIA – vence em 18/03/28</v>
+        <v>• NR 26 - SINALIZAÇÃO DE SEGURANÇA - EM DIA – não é necessário renovar</v>
       </c>
     </row>
     <row r="68" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A68" s="19">
-        <v>2</v>
+      <c r="A68" s="10">
+        <v>201</v>
       </c>
       <c r="B68" s="7" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C68" s="8">
-        <v>43587</v>
+        <v>43683</v>
       </c>
       <c r="D68" s="7" t="s">
         <v>110</v>
@@ -8379,16 +8376,16 @@
         <v>125</v>
       </c>
       <c r="I68" s="6">
-        <v>168</v>
+        <v>134</v>
       </c>
       <c r="J68" s="6">
-        <v>5060</v>
+        <v>5076</v>
       </c>
       <c r="K68" s="7" t="s">
         <v>126</v>
       </c>
       <c r="L68" s="6">
-        <v>318</v>
+        <v>271</v>
       </c>
       <c r="M68" s="7" t="s">
         <v>99</v>
@@ -8404,22 +8401,22 @@
         <v>1</v>
       </c>
       <c r="R68" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S68" s="10">
-        <v>78</v>
+        <v>102</v>
       </c>
       <c r="T68" s="9" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="U68" s="11">
-        <v>45876</v>
+        <v>45502</v>
       </c>
       <c r="V68" s="9" t="s">
         <v>44</v>
       </c>
       <c r="W68" s="10">
-        <v>-1017</v>
+        <v>-643</v>
       </c>
       <c r="X68" s="12" t="str">
         <f ca="1">IF(Tabela1[[#This Row],[DATA_CURSO]]="",
@@ -8431,11 +8428,11 @@
 "VENCIDO – "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa"),
 "EM DIA – vence em "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa")),
 "NÃO É NECESSÁRIO RENOVAR")))</f>
-        <v>EM DIA – vence em 06/08/28</v>
+        <v>EM DIA – vence em 29/07/27</v>
       </c>
       <c r="Y68" s="12" t="str">
         <f>IF(Tabela1[[#This Row],[FILIAL]]=1,"SINOP",IF(Tabela1[[#This Row],[FILIAL]]=2,"DOURADOS",IF(Tabela1[[#This Row],[FILIAL]]=3,"NOVA MUTUM",IF(Tabela1[[#This Row],[FILIAL]]=4,"FULLING",IF(Tabela1[[#This Row],[FILIAL]]=5,"SÃO PAULO",IF(Tabela1[[#This Row],[FILIAL]]=6,"SIDROLÂNDIA",IF(Tabela1[[#This Row],[FILIAL]]=8,"BALSAS",IF(Tabela1[[#This Row],[FILIAL]]=10,"LUIS EDUARDO MAGALHÃES",""))))))))</f>
-        <v>DOURADOS</v>
+        <v>NOVA MUTUM</v>
       </c>
       <c r="Z68" s="13" t="str">
         <f>VLOOKUP(N68,RENOVAÇÃO!A:D,4,0)</f>
@@ -8444,18 +8441,18 @@
       <c r="AA68" t="str">
         <f ca="1">CONCATENATE("• ",
     Tabela1[[#This Row],[DESCRICAO]], " - ",Tabela1[[#This Row],[STATUS_GERAL]])</f>
-        <v>• NR 20 - SEG. E TRAB. INFLAMÁVEIS E COMBUSTIVEIS CLASSE III - BASICO - EM DIA – vence em 06/08/28</v>
-      </c>
-    </row>
-    <row r="69" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A69" s="19">
-        <v>2</v>
+        <v>• NR 20 - SEG. E TRAB. INFLAMÁVEIS E COMBUSTIVEIS CLASSE III - BASICO - EM DIA – vence em 29/07/27</v>
+      </c>
+    </row>
+    <row r="69" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A69" s="10">
+        <v>207</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C69" s="8">
-        <v>43587</v>
+        <v>43683</v>
       </c>
       <c r="D69" s="7" t="s">
         <v>110</v>
@@ -8473,22 +8470,22 @@
         <v>125</v>
       </c>
       <c r="I69" s="6">
-        <v>168</v>
+        <v>134</v>
       </c>
       <c r="J69" s="6">
-        <v>5060</v>
+        <v>5076</v>
       </c>
       <c r="K69" s="7" t="s">
         <v>126</v>
       </c>
       <c r="L69" s="6">
-        <v>200</v>
+        <v>82</v>
       </c>
       <c r="M69" s="7" t="s">
         <v>99</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>49</v>
+        <v>111</v>
       </c>
       <c r="O69" s="9"/>
       <c r="P69" s="9" t="s">
@@ -8498,22 +8495,22 @@
         <v>1</v>
       </c>
       <c r="R69" s="10">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="S69" s="10">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="T69" s="9" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="U69" s="11">
-        <v>45365</v>
+        <v>45870</v>
       </c>
       <c r="V69" s="9" t="s">
         <v>36</v>
       </c>
       <c r="W69" s="10">
-        <v>-141</v>
+        <v>-646</v>
       </c>
       <c r="X69" s="12" t="str">
         <f ca="1">IF(Tabela1[[#This Row],[DATA_CURSO]]="",
@@ -8525,11 +8522,11 @@
 "VENCIDO – "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa"),
 "EM DIA – vence em "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa")),
 "NÃO É NECESSÁRIO RENOVAR")))</f>
-        <v>EM DIA – vence em 14/03/26</v>
+        <v>EM DIA – vence em 01/08/27</v>
       </c>
       <c r="Y69" s="12" t="str">
         <f>IF(Tabela1[[#This Row],[FILIAL]]=1,"SINOP",IF(Tabela1[[#This Row],[FILIAL]]=2,"DOURADOS",IF(Tabela1[[#This Row],[FILIAL]]=3,"NOVA MUTUM",IF(Tabela1[[#This Row],[FILIAL]]=4,"FULLING",IF(Tabela1[[#This Row],[FILIAL]]=5,"SÃO PAULO",IF(Tabela1[[#This Row],[FILIAL]]=6,"SIDROLÂNDIA",IF(Tabela1[[#This Row],[FILIAL]]=8,"BALSAS",IF(Tabela1[[#This Row],[FILIAL]]=10,"LUIS EDUARDO MAGALHÃES",""))))))))</f>
-        <v>NOVA MUTUM</v>
+        <v>SIDROLÂNDIA</v>
       </c>
       <c r="Z69" s="13" t="str">
         <f>VLOOKUP(N69,RENOVAÇÃO!A:D,4,0)</f>
@@ -8538,18 +8535,18 @@
       <c r="AA69" t="str">
         <f ca="1">CONCATENATE("• ",
     Tabela1[[#This Row],[DESCRICAO]], " - ",Tabela1[[#This Row],[STATUS_GERAL]])</f>
-        <v>• NR 35 - TRABALHO EM ALTURA - EM DIA – vence em 14/03/26</v>
+        <v>• NR 10 - SEGURANÇA EM INSTALAÇÕES E SERVIÇOS EM ELETRICIDADE ( BASÍCO) - EM DIA – vence em 01/08/27</v>
       </c>
     </row>
     <row r="70" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A70" s="19">
-        <v>2</v>
+      <c r="A70" s="10">
+        <v>207</v>
       </c>
       <c r="B70" s="7" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C70" s="8">
-        <v>43587</v>
+        <v>43683</v>
       </c>
       <c r="D70" s="7" t="s">
         <v>110</v>
@@ -8567,22 +8564,22 @@
         <v>125</v>
       </c>
       <c r="I70" s="6">
-        <v>168</v>
+        <v>134</v>
       </c>
       <c r="J70" s="6">
-        <v>5060</v>
+        <v>5076</v>
       </c>
       <c r="K70" s="7" t="s">
         <v>126</v>
       </c>
       <c r="L70" s="6">
-        <v>271</v>
+        <v>104</v>
       </c>
       <c r="M70" s="7" t="s">
         <v>99</v>
       </c>
       <c r="N70" s="9" t="s">
-        <v>42</v>
+        <v>109</v>
       </c>
       <c r="O70" s="9"/>
       <c r="P70" s="9" t="s">
@@ -8592,23 +8589,21 @@
         <v>1</v>
       </c>
       <c r="R70" s="10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S70" s="10">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="T70" s="9" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="U70" s="11">
-        <v>45807</v>
+        <v>44582</v>
       </c>
       <c r="V70" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="W70" s="10">
-        <v>-218</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="W70" s="10"/>
       <c r="X70" s="12" t="str">
         <f ca="1">IF(Tabela1[[#This Row],[DATA_CURSO]]="",
 "PENDENTE",
@@ -8619,11 +8614,11 @@
 "VENCIDO – "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa"),
 "EM DIA – vence em "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa")),
 "NÃO É NECESSÁRIO RENOVAR")))</f>
-        <v>EM DIA – vence em 30/05/26</v>
+        <v>EM DIA – não é necessário renovar</v>
       </c>
       <c r="Y70" s="12" t="str">
         <f>IF(Tabela1[[#This Row],[FILIAL]]=1,"SINOP",IF(Tabela1[[#This Row],[FILIAL]]=2,"DOURADOS",IF(Tabela1[[#This Row],[FILIAL]]=3,"NOVA MUTUM",IF(Tabela1[[#This Row],[FILIAL]]=4,"FULLING",IF(Tabela1[[#This Row],[FILIAL]]=5,"SÃO PAULO",IF(Tabela1[[#This Row],[FILIAL]]=6,"SIDROLÂNDIA",IF(Tabela1[[#This Row],[FILIAL]]=8,"BALSAS",IF(Tabela1[[#This Row],[FILIAL]]=10,"LUIS EDUARDO MAGALHÃES",""))))))))</f>
-        <v>NOVA MUTUM</v>
+        <v>SINOP</v>
       </c>
       <c r="Z70" s="13" t="str">
         <f>VLOOKUP(N70,RENOVAÇÃO!A:D,4,0)</f>
@@ -8632,18 +8627,18 @@
       <c r="AA70" t="str">
         <f ca="1">CONCATENATE("• ",
     Tabela1[[#This Row],[DESCRICAO]], " - ",Tabela1[[#This Row],[STATUS_GERAL]])</f>
-        <v>• NR 20 - SEG. E TRAB. INFLAMÁVEIS E COMBUSTIVEIS CLASSE III - AVANÇADO - EM DIA – vence em 30/05/26</v>
+        <v>• BLOQUEIO E SINALIZAÇÃO DE ENERGIAS PERIGOSAS - LOCKOUT/TAGOUT - NR10 E NR12 - EM DIA – não é necessário renovar</v>
       </c>
     </row>
     <row r="71" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A71" s="19">
-        <v>2</v>
+      <c r="A71" s="10">
+        <v>207</v>
       </c>
       <c r="B71" s="7" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C71" s="8">
-        <v>43587</v>
+        <v>43683</v>
       </c>
       <c r="D71" s="7" t="s">
         <v>110</v>
@@ -8661,22 +8656,22 @@
         <v>125</v>
       </c>
       <c r="I71" s="6">
-        <v>168</v>
+        <v>134</v>
       </c>
       <c r="J71" s="6">
-        <v>5060</v>
+        <v>5076</v>
       </c>
       <c r="K71" s="7" t="s">
         <v>126</v>
       </c>
       <c r="L71" s="6">
-        <v>321</v>
+        <v>2</v>
       </c>
       <c r="M71" s="7" t="s">
         <v>99</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="O71" s="9"/>
       <c r="P71" s="9" t="s">
@@ -8686,7 +8681,7 @@
         <v>1</v>
       </c>
       <c r="R71" s="10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S71" s="10">
         <v>102</v>
@@ -8695,12 +8690,14 @@
         <v>106</v>
       </c>
       <c r="U71" s="11">
-        <v>44359</v>
+        <v>45374</v>
       </c>
       <c r="V71" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="W71" s="10"/>
+        <v>36</v>
+      </c>
+      <c r="W71" s="10">
+        <v>-150</v>
+      </c>
       <c r="X71" s="12" t="str">
         <f ca="1">IF(Tabela1[[#This Row],[DATA_CURSO]]="",
 "PENDENTE",
@@ -8711,11 +8708,11 @@
 "VENCIDO – "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa"),
 "EM DIA – vence em "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa")),
 "NÃO É NECESSÁRIO RENOVAR")))</f>
-        <v>EM DIA – não é necessário renovar</v>
+        <v>EM DIA – vence em 23/03/26</v>
       </c>
       <c r="Y71" s="12" t="str">
         <f>IF(Tabela1[[#This Row],[FILIAL]]=1,"SINOP",IF(Tabela1[[#This Row],[FILIAL]]=2,"DOURADOS",IF(Tabela1[[#This Row],[FILIAL]]=3,"NOVA MUTUM",IF(Tabela1[[#This Row],[FILIAL]]=4,"FULLING",IF(Tabela1[[#This Row],[FILIAL]]=5,"SÃO PAULO",IF(Tabela1[[#This Row],[FILIAL]]=6,"SIDROLÂNDIA",IF(Tabela1[[#This Row],[FILIAL]]=8,"BALSAS",IF(Tabela1[[#This Row],[FILIAL]]=10,"LUIS EDUARDO MAGALHÃES",""))))))))</f>
-        <v>NOVA MUTUM</v>
+        <v>SINOP</v>
       </c>
       <c r="Z71" s="13" t="str">
         <f>VLOOKUP(N71,RENOVAÇÃO!A:D,4,0)</f>
@@ -8724,12 +8721,12 @@
       <c r="AA71" t="str">
         <f ca="1">CONCATENATE("• ",
     Tabela1[[#This Row],[DESCRICAO]], " - ",Tabela1[[#This Row],[STATUS_GERAL]])</f>
-        <v>• NR 13 - SEGURANÇA NA OPERAÇÃO VASOS DE PRESSÃO - EM DIA – não é necessário renovar</v>
+        <v>• NR 35 - TRABALHO EM ALTURA - EM DIA – vence em 23/03/26</v>
       </c>
     </row>
     <row r="72" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A72" s="19">
-        <v>4</v>
+      <c r="A72" s="10">
+        <v>207</v>
       </c>
       <c r="B72" s="7" t="s">
         <v>124</v>
@@ -8822,8 +8819,8 @@
       </c>
     </row>
     <row r="73" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A73" s="19">
-        <v>4</v>
+      <c r="A73" s="10">
+        <v>208</v>
       </c>
       <c r="B73" s="7" t="s">
         <v>124</v>
@@ -8916,8 +8913,8 @@
       </c>
     </row>
     <row r="74" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A74" s="19">
-        <v>4</v>
+      <c r="A74" s="10">
+        <v>208</v>
       </c>
       <c r="B74" s="7" t="s">
         <v>124</v>
@@ -9010,8 +9007,8 @@
       </c>
     </row>
     <row r="75" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A75" s="19">
-        <v>4</v>
+      <c r="A75" s="10">
+        <v>208</v>
       </c>
       <c r="B75" s="7" t="s">
         <v>124</v>
@@ -9104,8 +9101,8 @@
       </c>
     </row>
     <row r="76" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A76" s="19">
-        <v>4</v>
+      <c r="A76" s="10">
+        <v>208</v>
       </c>
       <c r="B76" s="7" t="s">
         <v>124</v>
@@ -9198,8 +9195,8 @@
       </c>
     </row>
     <row r="77" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A77" s="19">
-        <v>4</v>
+      <c r="A77" s="10">
+        <v>208</v>
       </c>
       <c r="B77" s="7" t="s">
         <v>124</v>
@@ -9292,8 +9289,8 @@
       </c>
     </row>
     <row r="78" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A78" s="19">
-        <v>4</v>
+      <c r="A78" s="10">
+        <v>208</v>
       </c>
       <c r="B78" s="7" t="s">
         <v>124</v>
@@ -9386,8 +9383,8 @@
       </c>
     </row>
     <row r="79" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A79" s="19">
-        <v>4</v>
+      <c r="A79" s="10">
+        <v>208</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>124</v>
@@ -9480,8 +9477,8 @@
       </c>
     </row>
     <row r="80" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A80" s="19">
-        <v>4</v>
+      <c r="A80" s="10">
+        <v>212</v>
       </c>
       <c r="B80" s="7" t="s">
         <v>124</v>
@@ -9572,8 +9569,8 @@
       </c>
     </row>
     <row r="81" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A81" s="19">
-        <v>4</v>
+      <c r="A81" s="10">
+        <v>212</v>
       </c>
       <c r="B81" s="7" t="s">
         <v>124</v>
@@ -9666,8 +9663,8 @@
       </c>
     </row>
     <row r="82" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A82" s="19">
-        <v>4</v>
+      <c r="A82" s="10">
+        <v>212</v>
       </c>
       <c r="B82" s="7" t="s">
         <v>124</v>
@@ -9760,8 +9757,8 @@
       </c>
     </row>
     <row r="83" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A83" s="19">
-        <v>4</v>
+      <c r="A83" s="10">
+        <v>212</v>
       </c>
       <c r="B83" s="7" t="s">
         <v>124</v>
@@ -9852,8 +9849,8 @@
       </c>
     </row>
     <row r="84" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A84" s="19">
-        <v>4</v>
+      <c r="A84" s="10">
+        <v>225</v>
       </c>
       <c r="B84" s="7" t="s">
         <v>124</v>
@@ -9946,8 +9943,8 @@
       </c>
     </row>
     <row r="85" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A85" s="19">
-        <v>4</v>
+      <c r="A85" s="10">
+        <v>225</v>
       </c>
       <c r="B85" s="7" t="s">
         <v>124</v>
@@ -10038,8 +10035,8 @@
       </c>
     </row>
     <row r="86" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A86" s="19">
-        <v>4</v>
+      <c r="A86" s="10">
+        <v>233</v>
       </c>
       <c r="B86" s="7" t="s">
         <v>124</v>
@@ -10130,8 +10127,8 @@
       </c>
     </row>
     <row r="87" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A87" s="19">
-        <v>4</v>
+      <c r="A87" s="10">
+        <v>233</v>
       </c>
       <c r="B87" s="7" t="s">
         <v>124</v>
@@ -10222,8 +10219,8 @@
       </c>
     </row>
     <row r="88" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A88" s="19">
-        <v>4</v>
+      <c r="A88" s="10">
+        <v>233</v>
       </c>
       <c r="B88" s="7" t="s">
         <v>124</v>
@@ -10316,8 +10313,8 @@
       </c>
     </row>
     <row r="89" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A89" s="19">
-        <v>4</v>
+      <c r="A89" s="10">
+        <v>240</v>
       </c>
       <c r="B89" s="7" t="s">
         <v>124</v>
@@ -10410,8 +10407,8 @@
       </c>
     </row>
     <row r="90" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A90" s="19">
-        <v>4</v>
+      <c r="A90" s="10">
+        <v>240</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>124</v>
@@ -10504,8 +10501,8 @@
       </c>
     </row>
     <row r="91" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A91" s="19">
-        <v>4</v>
+      <c r="A91" s="10">
+        <v>243</v>
       </c>
       <c r="B91" s="7" t="s">
         <v>124</v>
@@ -10596,8 +10593,8 @@
       </c>
     </row>
     <row r="92" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A92" s="19">
-        <v>4</v>
+      <c r="A92" s="10">
+        <v>243</v>
       </c>
       <c r="B92" s="7" t="s">
         <v>124</v>
@@ -10688,8 +10685,8 @@
       </c>
     </row>
     <row r="93" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A93" s="19">
-        <v>4</v>
+      <c r="A93" s="10">
+        <v>243</v>
       </c>
       <c r="B93" s="7" t="s">
         <v>124</v>
@@ -10782,7 +10779,9 @@
       </c>
     </row>
     <row r="94" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A94" s="6"/>
+      <c r="A94" s="10">
+        <v>243</v>
+      </c>
       <c r="B94" s="7"/>
       <c r="C94" s="8"/>
       <c r="D94" s="7"/>

--- a/Treinamentos Normativos.xlsx
+++ b/Treinamentos Normativos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://inpasabr-my.sharepoint.com/personal/gabriel_oliveira_inpasa_com_br/Documents/Área de Trabalho/CarteirinhaTreinamentos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="818" documentId="8_{FF07DBE4-2E43-45A4-A665-4C1273F6EE3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{078108DD-B6E5-4D21-BDD8-713570A7F6DE}"/>
+  <xr:revisionPtr revIDLastSave="821" documentId="8_{FF07DBE4-2E43-45A4-A665-4C1273F6EE3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A98C7D06-C1DF-4B5A-8E4F-DD0A0B730B77}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{593E7210-4473-4407-B4A2-ADC98FF555AA}"/>
   </bookViews>
@@ -602,7 +602,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -654,6 +654,9 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -661,6 +664,85 @@
     <cellStyle name="Normal 3" xfId="2" xr:uid="{EE9E7E5F-D59A-4B50-B096-F1D1FDE85294}"/>
   </cellStyles>
   <dxfs count="31">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color indexed="63"/>
+        <name val="Verdana"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="62"/>
+        </left>
+        <right style="thin">
+          <color indexed="62"/>
+        </right>
+        <top style="thin">
+          <color indexed="62"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="62"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color indexed="63"/>
+        <name val="Verdana"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="62"/>
+        </left>
+        <right style="thin">
+          <color indexed="62"/>
+        </right>
+        <top style="thin">
+          <color indexed="62"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="62"/>
+        </bottom>
+      </border>
+    </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
       <fill>
@@ -1566,84 +1648,6 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color indexed="63"/>
-        <name val="Verdana"/>
-        <charset val="1"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="62"/>
-        </left>
-        <right style="thin">
-          <color indexed="62"/>
-        </right>
-        <top style="thin">
-          <color indexed="62"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="62"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color indexed="63"/>
-        <name val="Verdana"/>
-        <charset val="1"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="62"/>
-        </left>
-        <right style="thin">
-          <color indexed="62"/>
-        </right>
-        <top style="thin">
-          <color indexed="62"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="62"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <border outline="0">
         <top style="thin">
           <color indexed="64"/>
@@ -1709,30 +1713,30 @@
     <sortCondition ref="A1:A94"/>
   </sortState>
   <tableColumns count="27">
-    <tableColumn id="1" xr3:uid="{184AE877-3641-41C7-900B-1E7AD0E1F8A3}" name="COD_FUNCIONARIO" dataDxfId="26"/>
-    <tableColumn id="2" xr3:uid="{EB67A5EA-7205-48F9-882A-F209D22A1243}" name="NOME" dataDxfId="25"/>
-    <tableColumn id="3" xr3:uid="{69510624-4559-4E59-89BC-64A565B9BB57}" name="DATA_ADMISSAO" dataDxfId="24"/>
-    <tableColumn id="4" xr3:uid="{C06A02E0-7E8C-4862-895A-03B6FE271372}" name="SITUACAO" dataDxfId="23"/>
-    <tableColumn id="5" xr3:uid="{18D13C7A-03B1-4D60-A51A-C716B57BE435}" name="RE_GESTOR" dataDxfId="22"/>
-    <tableColumn id="6" xr3:uid="{30CD7042-5180-4611-ACA7-2EB91D677411}" name="NOME_GESTOR" dataDxfId="21"/>
-    <tableColumn id="7" xr3:uid="{77F42019-71B9-44E5-B478-AE3F85065A37}" name="ESCALA" dataDxfId="20"/>
-    <tableColumn id="8" xr3:uid="{526A9DDA-A3A6-4A5D-A0C0-FDEA372603A5}" name="DEPARTAMENTO" dataDxfId="19"/>
-    <tableColumn id="9" xr3:uid="{5AEEB211-DB54-4F9D-BF1D-2BE2453A2F8C}" name="OBJ_CUSTO_FUNC" dataDxfId="18"/>
-    <tableColumn id="10" xr3:uid="{226E638F-8AA0-4859-B65C-918CA8D65F2D}" name="COD_CARGO" dataDxfId="17"/>
-    <tableColumn id="11" xr3:uid="{B785FBF6-E67F-4283-9A54-471CFB1B34DD}" name="CARGO" dataDxfId="16"/>
-    <tableColumn id="12" xr3:uid="{E5276929-3681-40FF-B65E-68CAFE1F8D1B}" name="COD_CURSO_REQUISITO" dataDxfId="15"/>
-    <tableColumn id="13" xr3:uid="{15199CE7-A63D-4EF0-9794-AEA746B7CA95}" name="TIPO" dataDxfId="14"/>
-    <tableColumn id="14" xr3:uid="{193B57CD-B438-41ED-B8C8-1D50AAE8FF57}" name="DESCRICAO" dataDxfId="13"/>
-    <tableColumn id="15" xr3:uid="{73C1AFB5-ED55-4ACF-90F8-1C73DCC264B6}" name="NOTA" dataDxfId="12"/>
-    <tableColumn id="16" xr3:uid="{507F5164-81DC-4102-B191-CB3650039EF8}" name="STATUS" dataDxfId="11"/>
-    <tableColumn id="17" xr3:uid="{E844C6D9-5DDA-44FC-A4F9-B12F244A8CB1}" name="EMPRESA" dataDxfId="10"/>
-    <tableColumn id="18" xr3:uid="{0B1F22A2-D4A7-4F15-B3F5-E14A2DAB744B}" name="FILIAL" dataDxfId="9"/>
-    <tableColumn id="19" xr3:uid="{955FBFB2-5133-4C0D-A384-C56D065A44C7}" name="SETOR" dataDxfId="8"/>
-    <tableColumn id="20" xr3:uid="{93208434-83E7-4ADA-9C20-65CE8282579A}" name="NOME_SETOR" dataDxfId="7"/>
-    <tableColumn id="21" xr3:uid="{371B351D-E994-464A-A1AE-23716963AFDC}" name="DATA_CURSO" dataDxfId="6"/>
-    <tableColumn id="22" xr3:uid="{D8258EEF-44D3-4421-8B1B-1431587B18DC}" name="TIPO_RENOVACAO" dataDxfId="5"/>
-    <tableColumn id="23" xr3:uid="{5DFCDE90-0FF1-4B98-8D7D-1039C19D5169}" name="VENCIDO" dataDxfId="4"/>
-    <tableColumn id="24" xr3:uid="{159A9C21-8097-47F7-8A06-07FEEDFFBB5C}" name="STATUS_GERAL" dataDxfId="3" dataCellStyle="Normal 3">
+    <tableColumn id="1" xr3:uid="{184AE877-3641-41C7-900B-1E7AD0E1F8A3}" name="COD_FUNCIONARIO" dataDxfId="0"/>
+    <tableColumn id="2" xr3:uid="{EB67A5EA-7205-48F9-882A-F209D22A1243}" name="NOME" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{69510624-4559-4E59-89BC-64A565B9BB57}" name="DATA_ADMISSAO" dataDxfId="26"/>
+    <tableColumn id="4" xr3:uid="{C06A02E0-7E8C-4862-895A-03B6FE271372}" name="SITUACAO" dataDxfId="25"/>
+    <tableColumn id="5" xr3:uid="{18D13C7A-03B1-4D60-A51A-C716B57BE435}" name="RE_GESTOR" dataDxfId="24"/>
+    <tableColumn id="6" xr3:uid="{30CD7042-5180-4611-ACA7-2EB91D677411}" name="NOME_GESTOR" dataDxfId="23"/>
+    <tableColumn id="7" xr3:uid="{77F42019-71B9-44E5-B478-AE3F85065A37}" name="ESCALA" dataDxfId="22"/>
+    <tableColumn id="8" xr3:uid="{526A9DDA-A3A6-4A5D-A0C0-FDEA372603A5}" name="DEPARTAMENTO" dataDxfId="21"/>
+    <tableColumn id="9" xr3:uid="{5AEEB211-DB54-4F9D-BF1D-2BE2453A2F8C}" name="OBJ_CUSTO_FUNC" dataDxfId="20"/>
+    <tableColumn id="10" xr3:uid="{226E638F-8AA0-4859-B65C-918CA8D65F2D}" name="COD_CARGO" dataDxfId="19"/>
+    <tableColumn id="11" xr3:uid="{B785FBF6-E67F-4283-9A54-471CFB1B34DD}" name="CARGO" dataDxfId="18"/>
+    <tableColumn id="12" xr3:uid="{E5276929-3681-40FF-B65E-68CAFE1F8D1B}" name="COD_CURSO_REQUISITO" dataDxfId="17"/>
+    <tableColumn id="13" xr3:uid="{15199CE7-A63D-4EF0-9794-AEA746B7CA95}" name="TIPO" dataDxfId="16"/>
+    <tableColumn id="14" xr3:uid="{193B57CD-B438-41ED-B8C8-1D50AAE8FF57}" name="DESCRICAO" dataDxfId="15"/>
+    <tableColumn id="15" xr3:uid="{73C1AFB5-ED55-4ACF-90F8-1C73DCC264B6}" name="NOTA" dataDxfId="14"/>
+    <tableColumn id="16" xr3:uid="{507F5164-81DC-4102-B191-CB3650039EF8}" name="STATUS" dataDxfId="13"/>
+    <tableColumn id="17" xr3:uid="{E844C6D9-5DDA-44FC-A4F9-B12F244A8CB1}" name="EMPRESA" dataDxfId="12"/>
+    <tableColumn id="18" xr3:uid="{0B1F22A2-D4A7-4F15-B3F5-E14A2DAB744B}" name="FILIAL" dataDxfId="11"/>
+    <tableColumn id="19" xr3:uid="{955FBFB2-5133-4C0D-A384-C56D065A44C7}" name="SETOR" dataDxfId="10"/>
+    <tableColumn id="20" xr3:uid="{93208434-83E7-4ADA-9C20-65CE8282579A}" name="NOME_SETOR" dataDxfId="9"/>
+    <tableColumn id="21" xr3:uid="{371B351D-E994-464A-A1AE-23716963AFDC}" name="DATA_CURSO" dataDxfId="8"/>
+    <tableColumn id="22" xr3:uid="{D8258EEF-44D3-4421-8B1B-1431587B18DC}" name="TIPO_RENOVACAO" dataDxfId="7"/>
+    <tableColumn id="23" xr3:uid="{5DFCDE90-0FF1-4B98-8D7D-1039C19D5169}" name="VENCIDO" dataDxfId="6"/>
+    <tableColumn id="24" xr3:uid="{159A9C21-8097-47F7-8A06-07FEEDFFBB5C}" name="STATUS_GERAL" dataDxfId="5" dataCellStyle="Normal 3">
       <calculatedColumnFormula>IF(Tabela1[[#This Row],[DATA_CURSO]]="",
 "PENDENTE",
 IF(Tabela1[[#This Row],[TIPO_RENOVACAO]]="QUANDO NECESSARIO",
@@ -1743,13 +1747,13 @@
 "EM DIA – vence em "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa")),
 "NÃO É NECESSÁRIO RENOVAR")))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="25" xr3:uid="{574EBF64-B992-4010-9BB2-AE0DCD761B79}" name="FILIAL_NOME" dataDxfId="2">
+    <tableColumn id="25" xr3:uid="{574EBF64-B992-4010-9BB2-AE0DCD761B79}" name="FILIAL_NOME" dataDxfId="4">
       <calculatedColumnFormula>IF(Tabela1[[#This Row],[FILIAL]]=1,"SINOP",IF(Tabela1[[#This Row],[FILIAL]]=2,"DOURADOS",IF(Tabela1[[#This Row],[FILIAL]]=3,"NOVA MUTUM",IF(Tabela1[[#This Row],[FILIAL]]=4,"FULLING",IF(Tabela1[[#This Row],[FILIAL]]=5,"SÃO PAULO",IF(Tabela1[[#This Row],[FILIAL]]=6,"SIDROLÂNDIA",IF(Tabela1[[#This Row],[FILIAL]]=8,"BALSAS",IF(Tabela1[[#This Row],[FILIAL]]=10,"LUIS EDUARDO MAGALHÃES",""))))))))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="28" xr3:uid="{87287027-A2D8-4ABD-982C-E2B5B5BAE061}" name="TRILHA DE TREINAMENTO " dataDxfId="1">
+    <tableColumn id="28" xr3:uid="{87287027-A2D8-4ABD-982C-E2B5B5BAE061}" name="TRILHA DE TREINAMENTO " dataDxfId="3">
       <calculatedColumnFormula>VLOOKUP(N2,RENOVAÇÃO!A:D,4,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="29" xr3:uid="{F36556D1-D2C2-43A0-AC4E-4F7EA9CD21CB}" name="TREINAMENTO_STATUS_GERAL" dataDxfId="0">
+    <tableColumn id="29" xr3:uid="{F36556D1-D2C2-43A0-AC4E-4F7EA9CD21CB}" name="TREINAMENTO_STATUS_GERAL" dataDxfId="2">
       <calculatedColumnFormula>CONCATENATE("• ",
     Tabela1[[#This Row],[DESCRICAO]], " - ",Tabela1[[#This Row],[STATUS_GERAL]])</calculatedColumnFormula>
     </tableColumn>
@@ -2191,7 +2195,7 @@
       </c>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A2" s="10">
+      <c r="A2" s="19">
         <v>1</v>
       </c>
       <c r="B2" s="7" t="s">
@@ -2285,7 +2289,7 @@
       </c>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A3" s="10">
+      <c r="A3" s="19">
         <v>7</v>
       </c>
       <c r="B3" s="7" t="s">
@@ -2379,7 +2383,7 @@
       </c>
     </row>
     <row r="4" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A4" s="10">
+      <c r="A4" s="19">
         <v>7</v>
       </c>
       <c r="B4" s="7" t="s">
@@ -2471,7 +2475,7 @@
       </c>
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A5" s="10">
+      <c r="A5" s="19">
         <v>7</v>
       </c>
       <c r="B5" s="7" t="s">
@@ -2565,7 +2569,7 @@
       </c>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A6" s="10">
+      <c r="A6" s="19">
         <v>7</v>
       </c>
       <c r="B6" s="7" t="s">
@@ -2659,7 +2663,7 @@
       </c>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A7" s="10">
+      <c r="A7" s="19">
         <v>33</v>
       </c>
       <c r="B7" s="7" t="s">
@@ -2751,7 +2755,7 @@
       </c>
     </row>
     <row r="8" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A8" s="10">
+      <c r="A8" s="19">
         <v>33</v>
       </c>
       <c r="B8" s="7" t="s">
@@ -2843,7 +2847,7 @@
       </c>
     </row>
     <row r="9" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A9" s="10">
+      <c r="A9" s="19">
         <v>33</v>
       </c>
       <c r="B9" s="7" t="s">
@@ -2937,7 +2941,7 @@
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A10" s="10">
+      <c r="A10" s="19">
         <v>33</v>
       </c>
       <c r="B10" s="7" t="s">
@@ -3029,7 +3033,7 @@
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A11" s="10">
+      <c r="A11" s="19">
         <v>33</v>
       </c>
       <c r="B11" s="7" t="s">
@@ -3123,7 +3127,7 @@
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A12" s="10">
+      <c r="A12" s="19">
         <v>37</v>
       </c>
       <c r="B12" s="7" t="s">
@@ -3215,7 +3219,7 @@
       </c>
     </row>
     <row r="13" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A13" s="10">
+      <c r="A13" s="19">
         <v>37</v>
       </c>
       <c r="B13" s="7" t="s">
@@ -3309,7 +3313,7 @@
       </c>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A14" s="10">
+      <c r="A14" s="19">
         <v>37</v>
       </c>
       <c r="B14" s="7" t="s">
@@ -3403,7 +3407,7 @@
       </c>
     </row>
     <row r="15" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A15" s="10">
+      <c r="A15" s="19">
         <v>37</v>
       </c>
       <c r="B15" s="7" t="s">
@@ -3495,7 +3499,7 @@
       </c>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A16" s="10">
+      <c r="A16" s="19">
         <v>45</v>
       </c>
       <c r="B16" s="7" t="s">
@@ -3589,7 +3593,7 @@
       </c>
     </row>
     <row r="17" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A17" s="10">
+      <c r="A17" s="19">
         <v>45</v>
       </c>
       <c r="B17" s="7" t="s">
@@ -3683,7 +3687,7 @@
       </c>
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A18" s="10">
+      <c r="A18" s="19">
         <v>45</v>
       </c>
       <c r="B18" s="7" t="s">
@@ -3777,7 +3781,7 @@
       </c>
     </row>
     <row r="19" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A19" s="10">
+      <c r="A19" s="19">
         <v>59</v>
       </c>
       <c r="B19" s="7" t="s">
@@ -3871,7 +3875,7 @@
       </c>
     </row>
     <row r="20" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A20" s="10">
+      <c r="A20" s="19">
         <v>59</v>
       </c>
       <c r="B20" s="7" t="s">
@@ -3965,7 +3969,7 @@
       </c>
     </row>
     <row r="21" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A21" s="10">
+      <c r="A21" s="19">
         <v>59</v>
       </c>
       <c r="B21" s="7" t="s">
@@ -4057,7 +4061,7 @@
       </c>
     </row>
     <row r="22" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A22" s="10">
+      <c r="A22" s="19">
         <v>59</v>
       </c>
       <c r="B22" s="7" t="s">
@@ -4149,7 +4153,7 @@
       </c>
     </row>
     <row r="23" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A23" s="10">
+      <c r="A23" s="19">
         <v>59</v>
       </c>
       <c r="B23" s="7" t="s">
@@ -4243,7 +4247,7 @@
       </c>
     </row>
     <row r="24" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A24" s="10">
+      <c r="A24" s="19">
         <v>68</v>
       </c>
       <c r="B24" s="7" t="s">
@@ -4337,7 +4341,7 @@
       </c>
     </row>
     <row r="25" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A25" s="10">
+      <c r="A25" s="19">
         <v>70</v>
       </c>
       <c r="B25" s="7" t="s">
@@ -4425,7 +4429,7 @@
       </c>
     </row>
     <row r="26" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A26" s="10">
+      <c r="A26" s="19">
         <v>70</v>
       </c>
       <c r="B26" s="7" t="s">
@@ -4519,7 +4523,7 @@
       </c>
     </row>
     <row r="27" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A27" s="10">
+      <c r="A27" s="19">
         <v>70</v>
       </c>
       <c r="B27" s="7" t="s">
@@ -4613,7 +4617,7 @@
       </c>
     </row>
     <row r="28" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A28" s="10">
+      <c r="A28" s="19">
         <v>70</v>
       </c>
       <c r="B28" s="7" t="s">
@@ -4705,7 +4709,7 @@
       </c>
     </row>
     <row r="29" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A29" s="10">
+      <c r="A29" s="19">
         <v>74</v>
       </c>
       <c r="B29" s="7" t="s">
@@ -4799,7 +4803,7 @@
       </c>
     </row>
     <row r="30" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A30" s="10">
+      <c r="A30" s="19">
         <v>74</v>
       </c>
       <c r="B30" s="7" t="s">
@@ -4893,7 +4897,7 @@
       </c>
     </row>
     <row r="31" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A31" s="10">
+      <c r="A31" s="19">
         <v>74</v>
       </c>
       <c r="B31" s="7" t="s">
@@ -4987,7 +4991,7 @@
       </c>
     </row>
     <row r="32" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A32" s="10">
+      <c r="A32" s="19">
         <v>74</v>
       </c>
       <c r="B32" s="7" t="s">
@@ -5081,7 +5085,7 @@
       </c>
     </row>
     <row r="33" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A33" s="10">
+      <c r="A33" s="19">
         <v>74</v>
       </c>
       <c r="B33" s="7" t="s">
@@ -5175,7 +5179,7 @@
       </c>
     </row>
     <row r="34" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A34" s="10">
+      <c r="A34" s="19">
         <v>74</v>
       </c>
       <c r="B34" s="7" t="s">
@@ -5269,7 +5273,7 @@
       </c>
     </row>
     <row r="35" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A35" s="10">
+      <c r="A35" s="19">
         <v>96</v>
       </c>
       <c r="B35" s="7" t="s">
@@ -5361,7 +5365,7 @@
       </c>
     </row>
     <row r="36" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A36" s="10">
+      <c r="A36" s="19">
         <v>104</v>
       </c>
       <c r="B36" s="7" t="s">
@@ -5455,7 +5459,7 @@
       </c>
     </row>
     <row r="37" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A37" s="10">
+      <c r="A37" s="19">
         <v>104</v>
       </c>
       <c r="B37" s="7" t="s">
@@ -5549,7 +5553,7 @@
       </c>
     </row>
     <row r="38" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A38" s="10">
+      <c r="A38" s="19">
         <v>127</v>
       </c>
       <c r="B38" s="7" t="s">
@@ -5643,7 +5647,7 @@
       </c>
     </row>
     <row r="39" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A39" s="10">
+      <c r="A39" s="19">
         <v>127</v>
       </c>
       <c r="B39" s="7" t="s">
@@ -5737,7 +5741,7 @@
       </c>
     </row>
     <row r="40" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A40" s="10">
+      <c r="A40" s="19">
         <v>136</v>
       </c>
       <c r="B40" s="7" t="s">
@@ -5829,7 +5833,7 @@
       </c>
     </row>
     <row r="41" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A41" s="10">
+      <c r="A41" s="19">
         <v>136</v>
       </c>
       <c r="B41" s="7" t="s">
@@ -5921,7 +5925,7 @@
       </c>
     </row>
     <row r="42" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A42" s="10">
+      <c r="A42" s="19">
         <v>136</v>
       </c>
       <c r="B42" s="7" t="s">
@@ -6015,7 +6019,7 @@
       </c>
     </row>
     <row r="43" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A43" s="10">
+      <c r="A43" s="19">
         <v>136</v>
       </c>
       <c r="B43" s="7" t="s">
@@ -6109,7 +6113,7 @@
       </c>
     </row>
     <row r="44" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A44" s="10">
+      <c r="A44" s="19">
         <v>141</v>
       </c>
       <c r="B44" s="7" t="s">
@@ -6203,7 +6207,7 @@
       </c>
     </row>
     <row r="45" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A45" s="10">
+      <c r="A45" s="19">
         <v>143</v>
       </c>
       <c r="B45" s="7" t="s">
@@ -6297,7 +6301,7 @@
       </c>
     </row>
     <row r="46" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A46" s="10">
+      <c r="A46" s="19">
         <v>143</v>
       </c>
       <c r="B46" s="7" t="s">
@@ -6391,7 +6395,7 @@
       </c>
     </row>
     <row r="47" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A47" s="10">
+      <c r="A47" s="19">
         <v>143</v>
       </c>
       <c r="B47" s="7" t="s">
@@ -6485,7 +6489,7 @@
       </c>
     </row>
     <row r="48" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A48" s="10">
+      <c r="A48" s="19">
         <v>145</v>
       </c>
       <c r="B48" s="7" t="s">
@@ -6577,7 +6581,7 @@
       </c>
     </row>
     <row r="49" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A49" s="10">
+      <c r="A49" s="19">
         <v>145</v>
       </c>
       <c r="B49" s="7" t="s">
@@ -6671,7 +6675,7 @@
       </c>
     </row>
     <row r="50" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A50" s="10">
+      <c r="A50" s="19">
         <v>145</v>
       </c>
       <c r="B50" s="7" t="s">
@@ -6765,7 +6769,7 @@
       </c>
     </row>
     <row r="51" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A51" s="10">
+      <c r="A51" s="19">
         <v>145</v>
       </c>
       <c r="B51" s="7" t="s">
@@ -6859,7 +6863,7 @@
       </c>
     </row>
     <row r="52" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A52" s="10">
+      <c r="A52" s="19">
         <v>159</v>
       </c>
       <c r="B52" s="7" t="s">
@@ -6953,7 +6957,7 @@
       </c>
     </row>
     <row r="53" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A53" s="10">
+      <c r="A53" s="19">
         <v>159</v>
       </c>
       <c r="B53" s="7" t="s">
@@ -7047,7 +7051,7 @@
       </c>
     </row>
     <row r="54" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A54" s="10">
+      <c r="A54" s="19">
         <v>171</v>
       </c>
       <c r="B54" s="7" t="s">
@@ -7141,7 +7145,7 @@
       </c>
     </row>
     <row r="55" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A55" s="10">
+      <c r="A55" s="19">
         <v>171</v>
       </c>
       <c r="B55" s="7" t="s">
@@ -7233,7 +7237,7 @@
       </c>
     </row>
     <row r="56" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A56" s="10">
+      <c r="A56" s="19">
         <v>183</v>
       </c>
       <c r="B56" s="7" t="s">
@@ -7327,7 +7331,7 @@
       </c>
     </row>
     <row r="57" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A57" s="10">
+      <c r="A57" s="19">
         <v>183</v>
       </c>
       <c r="B57" s="7" t="s">
@@ -7421,7 +7425,7 @@
       </c>
     </row>
     <row r="58" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A58" s="10">
+      <c r="A58" s="19">
         <v>183</v>
       </c>
       <c r="B58" s="7" t="s">
@@ -7513,7 +7517,7 @@
       </c>
     </row>
     <row r="59" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A59" s="10">
+      <c r="A59" s="19">
         <v>188</v>
       </c>
       <c r="B59" s="7" t="s">
@@ -7605,7 +7609,7 @@
       </c>
     </row>
     <row r="60" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A60" s="10">
+      <c r="A60" s="19">
         <v>189</v>
       </c>
       <c r="B60" s="7" t="s">
@@ -7699,7 +7703,7 @@
       </c>
     </row>
     <row r="61" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A61" s="10">
+      <c r="A61" s="19">
         <v>192</v>
       </c>
       <c r="B61" s="7" t="s">
@@ -7793,7 +7797,7 @@
       </c>
     </row>
     <row r="62" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A62" s="10">
+      <c r="A62" s="19">
         <v>193</v>
       </c>
       <c r="B62" s="7" t="s">
@@ -7887,7 +7891,7 @@
       </c>
     </row>
     <row r="63" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A63" s="10">
+      <c r="A63" s="19">
         <v>193</v>
       </c>
       <c r="B63" s="7" t="s">
@@ -7979,7 +7983,7 @@
       </c>
     </row>
     <row r="64" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A64" s="10">
+      <c r="A64" s="19">
         <v>193</v>
       </c>
       <c r="B64" s="7" t="s">
@@ -8073,7 +8077,7 @@
       </c>
     </row>
     <row r="65" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A65" s="10">
+      <c r="A65" s="19">
         <v>193</v>
       </c>
       <c r="B65" s="7" t="s">
@@ -8167,7 +8171,7 @@
       </c>
     </row>
     <row r="66" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A66" s="10">
+      <c r="A66" s="19">
         <v>199</v>
       </c>
       <c r="B66" s="7" t="s">
@@ -8259,7 +8263,7 @@
       </c>
     </row>
     <row r="67" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A67" s="10">
+      <c r="A67" s="19">
         <v>201</v>
       </c>
       <c r="B67" s="7" t="s">
@@ -8351,7 +8355,7 @@
       </c>
     </row>
     <row r="68" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A68" s="10">
+      <c r="A68" s="19">
         <v>201</v>
       </c>
       <c r="B68" s="7" t="s">
@@ -8445,7 +8449,7 @@
       </c>
     </row>
     <row r="69" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A69" s="10">
+      <c r="A69" s="19">
         <v>207</v>
       </c>
       <c r="B69" s="7" t="s">
@@ -8539,7 +8543,7 @@
       </c>
     </row>
     <row r="70" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A70" s="10">
+      <c r="A70" s="19">
         <v>207</v>
       </c>
       <c r="B70" s="7" t="s">
@@ -8631,7 +8635,7 @@
       </c>
     </row>
     <row r="71" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A71" s="10">
+      <c r="A71" s="19">
         <v>207</v>
       </c>
       <c r="B71" s="7" t="s">
@@ -8725,7 +8729,7 @@
       </c>
     </row>
     <row r="72" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A72" s="10">
+      <c r="A72" s="19">
         <v>207</v>
       </c>
       <c r="B72" s="7" t="s">
@@ -8819,7 +8823,7 @@
       </c>
     </row>
     <row r="73" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A73" s="10">
+      <c r="A73" s="19">
         <v>208</v>
       </c>
       <c r="B73" s="7" t="s">
@@ -8913,7 +8917,7 @@
       </c>
     </row>
     <row r="74" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A74" s="10">
+      <c r="A74" s="19">
         <v>208</v>
       </c>
       <c r="B74" s="7" t="s">
@@ -9007,7 +9011,7 @@
       </c>
     </row>
     <row r="75" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A75" s="10">
+      <c r="A75" s="19">
         <v>208</v>
       </c>
       <c r="B75" s="7" t="s">
@@ -9101,7 +9105,7 @@
       </c>
     </row>
     <row r="76" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A76" s="10">
+      <c r="A76" s="19">
         <v>208</v>
       </c>
       <c r="B76" s="7" t="s">
@@ -9195,7 +9199,7 @@
       </c>
     </row>
     <row r="77" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A77" s="10">
+      <c r="A77" s="19">
         <v>208</v>
       </c>
       <c r="B77" s="7" t="s">
@@ -9289,7 +9293,7 @@
       </c>
     </row>
     <row r="78" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A78" s="10">
+      <c r="A78" s="19">
         <v>208</v>
       </c>
       <c r="B78" s="7" t="s">
@@ -9383,7 +9387,7 @@
       </c>
     </row>
     <row r="79" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A79" s="10">
+      <c r="A79" s="19">
         <v>208</v>
       </c>
       <c r="B79" s="7" t="s">
@@ -9477,7 +9481,7 @@
       </c>
     </row>
     <row r="80" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A80" s="10">
+      <c r="A80" s="19">
         <v>212</v>
       </c>
       <c r="B80" s="7" t="s">
@@ -9569,7 +9573,7 @@
       </c>
     </row>
     <row r="81" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A81" s="10">
+      <c r="A81" s="19">
         <v>212</v>
       </c>
       <c r="B81" s="7" t="s">
@@ -9663,7 +9667,7 @@
       </c>
     </row>
     <row r="82" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A82" s="10">
+      <c r="A82" s="19">
         <v>212</v>
       </c>
       <c r="B82" s="7" t="s">
@@ -9757,7 +9761,7 @@
       </c>
     </row>
     <row r="83" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A83" s="10">
+      <c r="A83" s="19">
         <v>212</v>
       </c>
       <c r="B83" s="7" t="s">
@@ -9849,7 +9853,7 @@
       </c>
     </row>
     <row r="84" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A84" s="10">
+      <c r="A84" s="19">
         <v>225</v>
       </c>
       <c r="B84" s="7" t="s">
@@ -9943,7 +9947,7 @@
       </c>
     </row>
     <row r="85" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A85" s="10">
+      <c r="A85" s="19">
         <v>225</v>
       </c>
       <c r="B85" s="7" t="s">
@@ -10035,7 +10039,7 @@
       </c>
     </row>
     <row r="86" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A86" s="10">
+      <c r="A86" s="19">
         <v>233</v>
       </c>
       <c r="B86" s="7" t="s">
@@ -10127,7 +10131,7 @@
       </c>
     </row>
     <row r="87" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A87" s="10">
+      <c r="A87" s="19">
         <v>233</v>
       </c>
       <c r="B87" s="7" t="s">
@@ -10219,7 +10223,7 @@
       </c>
     </row>
     <row r="88" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A88" s="10">
+      <c r="A88" s="19">
         <v>233</v>
       </c>
       <c r="B88" s="7" t="s">
@@ -10313,7 +10317,7 @@
       </c>
     </row>
     <row r="89" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A89" s="10">
+      <c r="A89" s="19">
         <v>240</v>
       </c>
       <c r="B89" s="7" t="s">
@@ -10407,7 +10411,7 @@
       </c>
     </row>
     <row r="90" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A90" s="10">
+      <c r="A90" s="19">
         <v>240</v>
       </c>
       <c r="B90" s="7" t="s">
@@ -10501,7 +10505,7 @@
       </c>
     </row>
     <row r="91" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A91" s="10">
+      <c r="A91" s="19">
         <v>243</v>
       </c>
       <c r="B91" s="7" t="s">
@@ -10593,7 +10597,7 @@
       </c>
     </row>
     <row r="92" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A92" s="10">
+      <c r="A92" s="19">
         <v>243</v>
       </c>
       <c r="B92" s="7" t="s">
@@ -10685,7 +10689,7 @@
       </c>
     </row>
     <row r="93" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A93" s="10">
+      <c r="A93" s="19">
         <v>243</v>
       </c>
       <c r="B93" s="7" t="s">
@@ -10779,7 +10783,7 @@
       </c>
     </row>
     <row r="94" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A94" s="10">
+      <c r="A94" s="19">
         <v>243</v>
       </c>
       <c r="B94" s="7"/>

--- a/Treinamentos Normativos.xlsx
+++ b/Treinamentos Normativos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://inpasabr-my.sharepoint.com/personal/gabriel_oliveira_inpasa_com_br/Documents/Área de Trabalho/CarteirinhaTreinamentos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="821" documentId="8_{FF07DBE4-2E43-45A4-A665-4C1273F6EE3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A98C7D06-C1DF-4B5A-8E4F-DD0A0B730B77}"/>
+  <xr:revisionPtr revIDLastSave="845" documentId="8_{FF07DBE4-2E43-45A4-A665-4C1273F6EE3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8DB62CDF-EB66-4163-8BA7-0F1CA6212EF3}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{593E7210-4473-4407-B4A2-ADC98FF555AA}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{593E7210-4473-4407-B4A2-ADC98FF555AA}"/>
   </bookViews>
   <sheets>
     <sheet name="BASE" sheetId="2" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1300" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1296" uniqueCount="127">
   <si>
     <t>DESCRIÇÃO</t>
   </si>
@@ -436,7 +436,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -474,11 +474,6 @@
       <color indexed="63"/>
       <name val="Verdana"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <sz val="10"/>
@@ -600,9 +595,9 @@
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -616,7 +611,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -641,21 +636,14 @@
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -664,85 +652,6 @@
     <cellStyle name="Normal 3" xfId="2" xr:uid="{EE9E7E5F-D59A-4B50-B096-F1D1FDE85294}"/>
   </cellStyles>
   <dxfs count="31">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color indexed="63"/>
-        <name val="Verdana"/>
-        <charset val="1"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="62"/>
-        </left>
-        <right style="thin">
-          <color indexed="62"/>
-        </right>
-        <top style="thin">
-          <color indexed="62"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="62"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color indexed="63"/>
-        <name val="Verdana"/>
-        <charset val="1"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="62"/>
-        </left>
-        <right style="thin">
-          <color indexed="62"/>
-        </right>
-        <top style="thin">
-          <color indexed="62"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="62"/>
-        </bottom>
-      </border>
-    </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
       <fill>
@@ -1648,6 +1557,85 @@
       </border>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color indexed="63"/>
+        <name val="Verdana"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="62"/>
+        </left>
+        <right style="thin">
+          <color indexed="62"/>
+        </right>
+        <top style="thin">
+          <color indexed="62"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="62"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color indexed="63"/>
+        <name val="Verdana"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="62"/>
+        </left>
+        <right style="thin">
+          <color indexed="62"/>
+        </right>
+        <top style="thin">
+          <color indexed="62"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="62"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <border outline="0">
         <top style="thin">
           <color indexed="64"/>
@@ -1707,36 +1695,36 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{CC51E1EE-5D8F-4463-B3AC-3E0288975F6D}" name="Tabela1" displayName="Tabela1" ref="A1:AA94" totalsRowShown="0" headerRowDxfId="30" dataDxfId="28" headerRowBorderDxfId="29" tableBorderDxfId="27">
-  <autoFilter ref="A1:AA94" xr:uid="{CC51E1EE-5D8F-4463-B3AC-3E0288975F6D}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AA94">
-    <sortCondition ref="A1:A94"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{CC51E1EE-5D8F-4463-B3AC-3E0288975F6D}" name="Tabela1" displayName="Tabela1" ref="A1:AA93" totalsRowShown="0" headerRowDxfId="30" dataDxfId="28" headerRowBorderDxfId="29" tableBorderDxfId="27">
+  <autoFilter ref="A1:AA93" xr:uid="{CC51E1EE-5D8F-4463-B3AC-3E0288975F6D}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AA93">
+    <sortCondition ref="A1:A93"/>
   </sortState>
   <tableColumns count="27">
-    <tableColumn id="1" xr3:uid="{184AE877-3641-41C7-900B-1E7AD0E1F8A3}" name="COD_FUNCIONARIO" dataDxfId="0"/>
-    <tableColumn id="2" xr3:uid="{EB67A5EA-7205-48F9-882A-F209D22A1243}" name="NOME" dataDxfId="1"/>
-    <tableColumn id="3" xr3:uid="{69510624-4559-4E59-89BC-64A565B9BB57}" name="DATA_ADMISSAO" dataDxfId="26"/>
-    <tableColumn id="4" xr3:uid="{C06A02E0-7E8C-4862-895A-03B6FE271372}" name="SITUACAO" dataDxfId="25"/>
-    <tableColumn id="5" xr3:uid="{18D13C7A-03B1-4D60-A51A-C716B57BE435}" name="RE_GESTOR" dataDxfId="24"/>
-    <tableColumn id="6" xr3:uid="{30CD7042-5180-4611-ACA7-2EB91D677411}" name="NOME_GESTOR" dataDxfId="23"/>
-    <tableColumn id="7" xr3:uid="{77F42019-71B9-44E5-B478-AE3F85065A37}" name="ESCALA" dataDxfId="22"/>
-    <tableColumn id="8" xr3:uid="{526A9DDA-A3A6-4A5D-A0C0-FDEA372603A5}" name="DEPARTAMENTO" dataDxfId="21"/>
-    <tableColumn id="9" xr3:uid="{5AEEB211-DB54-4F9D-BF1D-2BE2453A2F8C}" name="OBJ_CUSTO_FUNC" dataDxfId="20"/>
-    <tableColumn id="10" xr3:uid="{226E638F-8AA0-4859-B65C-918CA8D65F2D}" name="COD_CARGO" dataDxfId="19"/>
-    <tableColumn id="11" xr3:uid="{B785FBF6-E67F-4283-9A54-471CFB1B34DD}" name="CARGO" dataDxfId="18"/>
-    <tableColumn id="12" xr3:uid="{E5276929-3681-40FF-B65E-68CAFE1F8D1B}" name="COD_CURSO_REQUISITO" dataDxfId="17"/>
-    <tableColumn id="13" xr3:uid="{15199CE7-A63D-4EF0-9794-AEA746B7CA95}" name="TIPO" dataDxfId="16"/>
-    <tableColumn id="14" xr3:uid="{193B57CD-B438-41ED-B8C8-1D50AAE8FF57}" name="DESCRICAO" dataDxfId="15"/>
-    <tableColumn id="15" xr3:uid="{73C1AFB5-ED55-4ACF-90F8-1C73DCC264B6}" name="NOTA" dataDxfId="14"/>
-    <tableColumn id="16" xr3:uid="{507F5164-81DC-4102-B191-CB3650039EF8}" name="STATUS" dataDxfId="13"/>
-    <tableColumn id="17" xr3:uid="{E844C6D9-5DDA-44FC-A4F9-B12F244A8CB1}" name="EMPRESA" dataDxfId="12"/>
-    <tableColumn id="18" xr3:uid="{0B1F22A2-D4A7-4F15-B3F5-E14A2DAB744B}" name="FILIAL" dataDxfId="11"/>
-    <tableColumn id="19" xr3:uid="{955FBFB2-5133-4C0D-A384-C56D065A44C7}" name="SETOR" dataDxfId="10"/>
-    <tableColumn id="20" xr3:uid="{93208434-83E7-4ADA-9C20-65CE8282579A}" name="NOME_SETOR" dataDxfId="9"/>
-    <tableColumn id="21" xr3:uid="{371B351D-E994-464A-A1AE-23716963AFDC}" name="DATA_CURSO" dataDxfId="8"/>
-    <tableColumn id="22" xr3:uid="{D8258EEF-44D3-4421-8B1B-1431587B18DC}" name="TIPO_RENOVACAO" dataDxfId="7"/>
-    <tableColumn id="23" xr3:uid="{5DFCDE90-0FF1-4B98-8D7D-1039C19D5169}" name="VENCIDO" dataDxfId="6"/>
-    <tableColumn id="24" xr3:uid="{159A9C21-8097-47F7-8A06-07FEEDFFBB5C}" name="STATUS_GERAL" dataDxfId="5" dataCellStyle="Normal 3">
+    <tableColumn id="1" xr3:uid="{184AE877-3641-41C7-900B-1E7AD0E1F8A3}" name="COD_FUNCIONARIO" dataDxfId="26"/>
+    <tableColumn id="2" xr3:uid="{EB67A5EA-7205-48F9-882A-F209D22A1243}" name="NOME" dataDxfId="25"/>
+    <tableColumn id="3" xr3:uid="{69510624-4559-4E59-89BC-64A565B9BB57}" name="DATA_ADMISSAO" dataDxfId="24"/>
+    <tableColumn id="4" xr3:uid="{C06A02E0-7E8C-4862-895A-03B6FE271372}" name="SITUACAO" dataDxfId="23"/>
+    <tableColumn id="5" xr3:uid="{18D13C7A-03B1-4D60-A51A-C716B57BE435}" name="RE_GESTOR" dataDxfId="22"/>
+    <tableColumn id="6" xr3:uid="{30CD7042-5180-4611-ACA7-2EB91D677411}" name="NOME_GESTOR" dataDxfId="21"/>
+    <tableColumn id="7" xr3:uid="{77F42019-71B9-44E5-B478-AE3F85065A37}" name="ESCALA" dataDxfId="20"/>
+    <tableColumn id="8" xr3:uid="{526A9DDA-A3A6-4A5D-A0C0-FDEA372603A5}" name="DEPARTAMENTO" dataDxfId="19"/>
+    <tableColumn id="9" xr3:uid="{5AEEB211-DB54-4F9D-BF1D-2BE2453A2F8C}" name="OBJ_CUSTO_FUNC" dataDxfId="18"/>
+    <tableColumn id="10" xr3:uid="{226E638F-8AA0-4859-B65C-918CA8D65F2D}" name="COD_CARGO" dataDxfId="17"/>
+    <tableColumn id="11" xr3:uid="{B785FBF6-E67F-4283-9A54-471CFB1B34DD}" name="CARGO" dataDxfId="16"/>
+    <tableColumn id="12" xr3:uid="{E5276929-3681-40FF-B65E-68CAFE1F8D1B}" name="COD_CURSO_REQUISITO" dataDxfId="15"/>
+    <tableColumn id="13" xr3:uid="{15199CE7-A63D-4EF0-9794-AEA746B7CA95}" name="TIPO" dataDxfId="14"/>
+    <tableColumn id="14" xr3:uid="{193B57CD-B438-41ED-B8C8-1D50AAE8FF57}" name="DESCRICAO" dataDxfId="13"/>
+    <tableColumn id="15" xr3:uid="{73C1AFB5-ED55-4ACF-90F8-1C73DCC264B6}" name="NOTA" dataDxfId="12"/>
+    <tableColumn id="16" xr3:uid="{507F5164-81DC-4102-B191-CB3650039EF8}" name="STATUS" dataDxfId="11"/>
+    <tableColumn id="17" xr3:uid="{E844C6D9-5DDA-44FC-A4F9-B12F244A8CB1}" name="EMPRESA" dataDxfId="10"/>
+    <tableColumn id="18" xr3:uid="{0B1F22A2-D4A7-4F15-B3F5-E14A2DAB744B}" name="FILIAL" dataDxfId="9"/>
+    <tableColumn id="19" xr3:uid="{955FBFB2-5133-4C0D-A384-C56D065A44C7}" name="SETOR" dataDxfId="8"/>
+    <tableColumn id="20" xr3:uid="{93208434-83E7-4ADA-9C20-65CE8282579A}" name="NOME_SETOR" dataDxfId="7"/>
+    <tableColumn id="21" xr3:uid="{371B351D-E994-464A-A1AE-23716963AFDC}" name="DATA_CURSO" dataDxfId="6"/>
+    <tableColumn id="22" xr3:uid="{D8258EEF-44D3-4421-8B1B-1431587B18DC}" name="TIPO_RENOVACAO" dataDxfId="5"/>
+    <tableColumn id="23" xr3:uid="{5DFCDE90-0FF1-4B98-8D7D-1039C19D5169}" name="VENCIDO" dataDxfId="4"/>
+    <tableColumn id="24" xr3:uid="{159A9C21-8097-47F7-8A06-07FEEDFFBB5C}" name="STATUS_GERAL" dataDxfId="3" dataCellStyle="Normal 3">
       <calculatedColumnFormula>IF(Tabela1[[#This Row],[DATA_CURSO]]="",
 "PENDENTE",
 IF(Tabela1[[#This Row],[TIPO_RENOVACAO]]="QUANDO NECESSARIO",
@@ -1747,13 +1735,13 @@
 "EM DIA – vence em "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa")),
 "NÃO É NECESSÁRIO RENOVAR")))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="25" xr3:uid="{574EBF64-B992-4010-9BB2-AE0DCD761B79}" name="FILIAL_NOME" dataDxfId="4">
+    <tableColumn id="25" xr3:uid="{574EBF64-B992-4010-9BB2-AE0DCD761B79}" name="FILIAL_NOME" dataDxfId="2">
       <calculatedColumnFormula>IF(Tabela1[[#This Row],[FILIAL]]=1,"SINOP",IF(Tabela1[[#This Row],[FILIAL]]=2,"DOURADOS",IF(Tabela1[[#This Row],[FILIAL]]=3,"NOVA MUTUM",IF(Tabela1[[#This Row],[FILIAL]]=4,"FULLING",IF(Tabela1[[#This Row],[FILIAL]]=5,"SÃO PAULO",IF(Tabela1[[#This Row],[FILIAL]]=6,"SIDROLÂNDIA",IF(Tabela1[[#This Row],[FILIAL]]=8,"BALSAS",IF(Tabela1[[#This Row],[FILIAL]]=10,"LUIS EDUARDO MAGALHÃES",""))))))))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="28" xr3:uid="{87287027-A2D8-4ABD-982C-E2B5B5BAE061}" name="TRILHA DE TREINAMENTO " dataDxfId="3">
+    <tableColumn id="28" xr3:uid="{87287027-A2D8-4ABD-982C-E2B5B5BAE061}" name="TRILHA DE TREINAMENTO " dataDxfId="1">
       <calculatedColumnFormula>VLOOKUP(N2,RENOVAÇÃO!A:D,4,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="29" xr3:uid="{F36556D1-D2C2-43A0-AC4E-4F7EA9CD21CB}" name="TREINAMENTO_STATUS_GERAL" dataDxfId="2">
+    <tableColumn id="29" xr3:uid="{F36556D1-D2C2-43A0-AC4E-4F7EA9CD21CB}" name="TREINAMENTO_STATUS_GERAL" dataDxfId="0">
       <calculatedColumnFormula>CONCATENATE("• ",
     Tabela1[[#This Row],[DESCRICAO]], " - ",Tabela1[[#This Row],[STATUS_GERAL]])</calculatedColumnFormula>
     </tableColumn>
@@ -2079,124 +2067,124 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE66411B-270E-4B7F-B5A0-513C2E9AA64C}">
-  <dimension ref="A1:AA94"/>
+  <dimension ref="A1:AA93"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20.33203125" customWidth="1"/>
     <col min="2" max="2" width="30.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.33203125" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="14.33203125" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="15.77734375" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="35.5546875" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="29.44140625" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="20" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="21.6640625" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="16.88671875" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="35.44140625" hidden="1" customWidth="1"/>
-    <col min="12" max="12" width="27.6640625" hidden="1" customWidth="1"/>
-    <col min="13" max="13" width="9.44140625" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="58.33203125" hidden="1" customWidth="1"/>
-    <col min="15" max="15" width="10.21875" hidden="1" customWidth="1"/>
-    <col min="16" max="16" width="11.88671875" hidden="1" customWidth="1"/>
-    <col min="17" max="17" width="13.77734375" hidden="1" customWidth="1"/>
-    <col min="18" max="18" width="10.5546875" hidden="1" customWidth="1"/>
-    <col min="19" max="19" width="11.21875" hidden="1" customWidth="1"/>
-    <col min="20" max="20" width="23.21875" hidden="1" customWidth="1"/>
-    <col min="21" max="21" width="17.33203125" hidden="1" customWidth="1"/>
-    <col min="22" max="22" width="21.77734375" hidden="1" customWidth="1"/>
-    <col min="23" max="23" width="13.77734375" hidden="1" customWidth="1"/>
-    <col min="24" max="24" width="29.88671875" hidden="1" customWidth="1"/>
-    <col min="25" max="25" width="24.109375" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="15.33203125" customWidth="1"/>
+    <col min="4" max="4" width="14.33203125" customWidth="1"/>
+    <col min="5" max="5" width="15.77734375" customWidth="1"/>
+    <col min="6" max="6" width="35.5546875" customWidth="1"/>
+    <col min="7" max="7" width="29.44140625" customWidth="1"/>
+    <col min="8" max="8" width="20" customWidth="1"/>
+    <col min="9" max="9" width="21.6640625" customWidth="1"/>
+    <col min="10" max="10" width="16.88671875" customWidth="1"/>
+    <col min="11" max="11" width="35.44140625" customWidth="1"/>
+    <col min="12" max="12" width="27.6640625" customWidth="1"/>
+    <col min="13" max="13" width="9.44140625" customWidth="1"/>
+    <col min="14" max="14" width="58.33203125" customWidth="1"/>
+    <col min="15" max="15" width="10.21875" customWidth="1"/>
+    <col min="16" max="16" width="11.88671875" customWidth="1"/>
+    <col min="17" max="17" width="13.77734375" customWidth="1"/>
+    <col min="18" max="18" width="10.5546875" customWidth="1"/>
+    <col min="19" max="19" width="11.21875" customWidth="1"/>
+    <col min="20" max="20" width="23.21875" customWidth="1"/>
+    <col min="21" max="21" width="17.33203125" customWidth="1"/>
+    <col min="22" max="22" width="21.77734375" customWidth="1"/>
+    <col min="23" max="23" width="13.77734375" customWidth="1"/>
+    <col min="24" max="24" width="29.88671875" customWidth="1"/>
+    <col min="25" max="25" width="24.109375" customWidth="1"/>
     <col min="26" max="26" width="31.21875" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="111.88671875" style="16" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="111.88671875" style="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="B1" s="18" t="s">
+      <c r="B1" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="C1" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="D1" s="18" t="s">
+      <c r="D1" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="E1" s="18" t="s">
+      <c r="E1" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="F1" s="18" t="s">
+      <c r="F1" s="16" t="s">
         <v>78</v>
       </c>
-      <c r="G1" s="18" t="s">
+      <c r="G1" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="H1" s="18" t="s">
+      <c r="H1" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="I1" s="18" t="s">
+      <c r="I1" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="J1" s="18" t="s">
+      <c r="J1" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="K1" s="18" t="s">
+      <c r="K1" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="L1" s="18" t="s">
+      <c r="L1" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="M1" s="18" t="s">
+      <c r="M1" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="N1" s="18" t="s">
+      <c r="N1" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="O1" s="18" t="s">
+      <c r="O1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="P1" s="18" t="s">
+      <c r="P1" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="Q1" s="18" t="s">
+      <c r="Q1" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="R1" s="18" t="s">
+      <c r="R1" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="S1" s="18" t="s">
+      <c r="S1" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="T1" s="18" t="s">
+      <c r="T1" s="16" t="s">
         <v>92</v>
       </c>
-      <c r="U1" s="18" t="s">
+      <c r="U1" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="V1" s="18" t="s">
+      <c r="V1" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="W1" s="18" t="s">
+      <c r="W1" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="X1" s="17" t="s">
+      <c r="X1" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="Y1" s="17" t="s">
+      <c r="Y1" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="Z1" s="17" t="s">
+      <c r="Z1" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="AA1" s="17" t="s">
+      <c r="AA1" s="15" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A2" s="19">
-        <v>1</v>
+      <c r="A2" s="10">
+        <v>2</v>
       </c>
       <c r="B2" s="7" t="s">
         <v>121</v>
@@ -2289,8 +2277,8 @@
       </c>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A3" s="19">
-        <v>7</v>
+      <c r="A3" s="10">
+        <v>2</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>121</v>
@@ -2383,8 +2371,8 @@
       </c>
     </row>
     <row r="4" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A4" s="19">
-        <v>7</v>
+      <c r="A4" s="10">
+        <v>2</v>
       </c>
       <c r="B4" s="7" t="s">
         <v>121</v>
@@ -2475,8 +2463,8 @@
       </c>
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A5" s="19">
-        <v>7</v>
+      <c r="A5" s="10">
+        <v>2</v>
       </c>
       <c r="B5" s="7" t="s">
         <v>121</v>
@@ -2569,8 +2557,8 @@
       </c>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A6" s="19">
-        <v>7</v>
+      <c r="A6" s="10">
+        <v>2</v>
       </c>
       <c r="B6" s="7" t="s">
         <v>121</v>
@@ -2663,8 +2651,8 @@
       </c>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A7" s="19">
-        <v>33</v>
+      <c r="A7" s="10">
+        <v>2</v>
       </c>
       <c r="B7" s="7" t="s">
         <v>121</v>
@@ -2755,8 +2743,8 @@
       </c>
     </row>
     <row r="8" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A8" s="19">
-        <v>33</v>
+      <c r="A8" s="10">
+        <v>2</v>
       </c>
       <c r="B8" s="7" t="s">
         <v>121</v>
@@ -2847,8 +2835,8 @@
       </c>
     </row>
     <row r="9" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A9" s="19">
-        <v>33</v>
+      <c r="A9" s="10">
+        <v>2</v>
       </c>
       <c r="B9" s="7" t="s">
         <v>121</v>
@@ -2941,8 +2929,8 @@
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A10" s="19">
-        <v>33</v>
+      <c r="A10" s="10">
+        <v>2</v>
       </c>
       <c r="B10" s="7" t="s">
         <v>121</v>
@@ -3033,8 +3021,8 @@
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A11" s="19">
-        <v>33</v>
+      <c r="A11" s="10">
+        <v>2</v>
       </c>
       <c r="B11" s="7" t="s">
         <v>121</v>
@@ -3127,8 +3115,8 @@
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A12" s="19">
-        <v>37</v>
+      <c r="A12" s="10">
+        <v>2</v>
       </c>
       <c r="B12" s="7" t="s">
         <v>121</v>
@@ -3219,8 +3207,8 @@
       </c>
     </row>
     <row r="13" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A13" s="19">
-        <v>37</v>
+      <c r="A13" s="10">
+        <v>2</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>121</v>
@@ -3313,8 +3301,8 @@
       </c>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A14" s="19">
-        <v>37</v>
+      <c r="A14" s="10">
+        <v>2</v>
       </c>
       <c r="B14" s="7" t="s">
         <v>121</v>
@@ -3407,8 +3395,8 @@
       </c>
     </row>
     <row r="15" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A15" s="19">
-        <v>37</v>
+      <c r="A15" s="10">
+        <v>2</v>
       </c>
       <c r="B15" s="7" t="s">
         <v>121</v>
@@ -3499,8 +3487,8 @@
       </c>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A16" s="19">
-        <v>45</v>
+      <c r="A16" s="10">
+        <v>2</v>
       </c>
       <c r="B16" s="7" t="s">
         <v>121</v>
@@ -3593,8 +3581,8 @@
       </c>
     </row>
     <row r="17" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A17" s="19">
-        <v>45</v>
+      <c r="A17" s="10">
+        <v>2</v>
       </c>
       <c r="B17" s="7" t="s">
         <v>121</v>
@@ -3687,8 +3675,8 @@
       </c>
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A18" s="19">
-        <v>45</v>
+      <c r="A18" s="10">
+        <v>2</v>
       </c>
       <c r="B18" s="7" t="s">
         <v>121</v>
@@ -3781,8 +3769,8 @@
       </c>
     </row>
     <row r="19" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A19" s="19">
-        <v>59</v>
+      <c r="A19" s="10">
+        <v>2</v>
       </c>
       <c r="B19" s="7" t="s">
         <v>121</v>
@@ -3875,8 +3863,8 @@
       </c>
     </row>
     <row r="20" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A20" s="19">
-        <v>59</v>
+      <c r="A20" s="10">
+        <v>2</v>
       </c>
       <c r="B20" s="7" t="s">
         <v>121</v>
@@ -3969,8 +3957,8 @@
       </c>
     </row>
     <row r="21" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A21" s="19">
-        <v>59</v>
+      <c r="A21" s="10">
+        <v>2</v>
       </c>
       <c r="B21" s="7" t="s">
         <v>121</v>
@@ -4061,8 +4049,8 @@
       </c>
     </row>
     <row r="22" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A22" s="19">
-        <v>59</v>
+      <c r="A22" s="10">
+        <v>2</v>
       </c>
       <c r="B22" s="7" t="s">
         <v>121</v>
@@ -4153,8 +4141,8 @@
       </c>
     </row>
     <row r="23" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A23" s="19">
-        <v>59</v>
+      <c r="A23" s="10">
+        <v>2</v>
       </c>
       <c r="B23" s="7" t="s">
         <v>121</v>
@@ -4247,8 +4235,8 @@
       </c>
     </row>
     <row r="24" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A24" s="19">
-        <v>68</v>
+      <c r="A24" s="10">
+        <v>2</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>121</v>
@@ -4341,8 +4329,8 @@
       </c>
     </row>
     <row r="25" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A25" s="19">
-        <v>70</v>
+      <c r="A25" s="10">
+        <v>2</v>
       </c>
       <c r="B25" s="7" t="s">
         <v>121</v>
@@ -4429,8 +4417,8 @@
       </c>
     </row>
     <row r="26" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A26" s="19">
-        <v>70</v>
+      <c r="A26" s="10">
+        <v>2</v>
       </c>
       <c r="B26" s="7" t="s">
         <v>121</v>
@@ -4523,8 +4511,8 @@
       </c>
     </row>
     <row r="27" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A27" s="19">
-        <v>70</v>
+      <c r="A27" s="10">
+        <v>1</v>
       </c>
       <c r="B27" s="7" t="s">
         <v>122</v>
@@ -4617,8 +4605,8 @@
       </c>
     </row>
     <row r="28" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A28" s="19">
-        <v>70</v>
+      <c r="A28" s="10">
+        <v>1</v>
       </c>
       <c r="B28" s="7" t="s">
         <v>122</v>
@@ -4709,8 +4697,8 @@
       </c>
     </row>
     <row r="29" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A29" s="19">
-        <v>74</v>
+      <c r="A29" s="10">
+        <v>1</v>
       </c>
       <c r="B29" s="7" t="s">
         <v>122</v>
@@ -4803,8 +4791,8 @@
       </c>
     </row>
     <row r="30" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A30" s="19">
-        <v>74</v>
+      <c r="A30" s="10">
+        <v>1</v>
       </c>
       <c r="B30" s="7" t="s">
         <v>122</v>
@@ -4897,8 +4885,8 @@
       </c>
     </row>
     <row r="31" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A31" s="19">
-        <v>74</v>
+      <c r="A31" s="10">
+        <v>1</v>
       </c>
       <c r="B31" s="7" t="s">
         <v>122</v>
@@ -4991,8 +4979,8 @@
       </c>
     </row>
     <row r="32" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A32" s="19">
-        <v>74</v>
+      <c r="A32" s="10">
+        <v>1</v>
       </c>
       <c r="B32" s="7" t="s">
         <v>122</v>
@@ -5085,8 +5073,8 @@
       </c>
     </row>
     <row r="33" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A33" s="19">
-        <v>74</v>
+      <c r="A33" s="10">
+        <v>1</v>
       </c>
       <c r="B33" s="7" t="s">
         <v>122</v>
@@ -5179,8 +5167,8 @@
       </c>
     </row>
     <row r="34" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A34" s="19">
-        <v>74</v>
+      <c r="A34" s="10">
+        <v>1</v>
       </c>
       <c r="B34" s="7" t="s">
         <v>122</v>
@@ -5273,8 +5261,8 @@
       </c>
     </row>
     <row r="35" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A35" s="19">
-        <v>96</v>
+      <c r="A35" s="10">
+        <v>1</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>122</v>
@@ -5365,8 +5353,8 @@
       </c>
     </row>
     <row r="36" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A36" s="19">
-        <v>104</v>
+      <c r="A36" s="10">
+        <v>1</v>
       </c>
       <c r="B36" s="7" t="s">
         <v>122</v>
@@ -5459,8 +5447,8 @@
       </c>
     </row>
     <row r="37" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A37" s="19">
-        <v>104</v>
+      <c r="A37" s="10">
+        <v>1</v>
       </c>
       <c r="B37" s="7" t="s">
         <v>122</v>
@@ -5553,8 +5541,8 @@
       </c>
     </row>
     <row r="38" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A38" s="19">
-        <v>127</v>
+      <c r="A38" s="10">
+        <v>1</v>
       </c>
       <c r="B38" s="7" t="s">
         <v>122</v>
@@ -5647,8 +5635,8 @@
       </c>
     </row>
     <row r="39" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A39" s="19">
-        <v>127</v>
+      <c r="A39" s="10">
+        <v>1</v>
       </c>
       <c r="B39" s="7" t="s">
         <v>122</v>
@@ -5741,8 +5729,8 @@
       </c>
     </row>
     <row r="40" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A40" s="19">
-        <v>136</v>
+      <c r="A40" s="10">
+        <v>1</v>
       </c>
       <c r="B40" s="7" t="s">
         <v>122</v>
@@ -5833,8 +5821,8 @@
       </c>
     </row>
     <row r="41" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A41" s="19">
-        <v>136</v>
+      <c r="A41" s="10">
+        <v>1</v>
       </c>
       <c r="B41" s="7" t="s">
         <v>122</v>
@@ -5925,8 +5913,8 @@
       </c>
     </row>
     <row r="42" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A42" s="19">
-        <v>136</v>
+      <c r="A42" s="10">
+        <v>1</v>
       </c>
       <c r="B42" s="7" t="s">
         <v>122</v>
@@ -6019,8 +6007,8 @@
       </c>
     </row>
     <row r="43" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A43" s="19">
-        <v>136</v>
+      <c r="A43" s="10">
+        <v>1</v>
       </c>
       <c r="B43" s="7" t="s">
         <v>122</v>
@@ -6113,8 +6101,8 @@
       </c>
     </row>
     <row r="44" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A44" s="19">
-        <v>141</v>
+      <c r="A44" s="10">
+        <v>1</v>
       </c>
       <c r="B44" s="7" t="s">
         <v>122</v>
@@ -6207,8 +6195,8 @@
       </c>
     </row>
     <row r="45" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A45" s="19">
-        <v>143</v>
+      <c r="A45" s="10">
+        <v>1</v>
       </c>
       <c r="B45" s="7" t="s">
         <v>122</v>
@@ -6301,8 +6289,8 @@
       </c>
     </row>
     <row r="46" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A46" s="19">
-        <v>143</v>
+      <c r="A46" s="10">
+        <v>1</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>122</v>
@@ -6395,8 +6383,8 @@
       </c>
     </row>
     <row r="47" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A47" s="19">
-        <v>143</v>
+      <c r="A47" s="10">
+        <v>1</v>
       </c>
       <c r="B47" s="7" t="s">
         <v>122</v>
@@ -6489,8 +6477,8 @@
       </c>
     </row>
     <row r="48" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A48" s="19">
-        <v>145</v>
+      <c r="A48" s="10">
+        <v>1</v>
       </c>
       <c r="B48" s="7" t="s">
         <v>122</v>
@@ -6581,8 +6569,8 @@
       </c>
     </row>
     <row r="49" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A49" s="19">
-        <v>145</v>
+      <c r="A49" s="10">
+        <v>4</v>
       </c>
       <c r="B49" s="7" t="s">
         <v>123</v>
@@ -6675,8 +6663,8 @@
       </c>
     </row>
     <row r="50" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A50" s="19">
-        <v>145</v>
+      <c r="A50" s="10">
+        <v>4</v>
       </c>
       <c r="B50" s="7" t="s">
         <v>123</v>
@@ -6769,8 +6757,8 @@
       </c>
     </row>
     <row r="51" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A51" s="19">
-        <v>145</v>
+      <c r="A51" s="10">
+        <v>4</v>
       </c>
       <c r="B51" s="7" t="s">
         <v>123</v>
@@ -6863,8 +6851,8 @@
       </c>
     </row>
     <row r="52" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A52" s="19">
-        <v>159</v>
+      <c r="A52" s="10">
+        <v>4</v>
       </c>
       <c r="B52" s="7" t="s">
         <v>123</v>
@@ -6957,8 +6945,8 @@
       </c>
     </row>
     <row r="53" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A53" s="19">
-        <v>159</v>
+      <c r="A53" s="10">
+        <v>4</v>
       </c>
       <c r="B53" s="7" t="s">
         <v>123</v>
@@ -7051,8 +7039,8 @@
       </c>
     </row>
     <row r="54" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A54" s="19">
-        <v>171</v>
+      <c r="A54" s="10">
+        <v>4</v>
       </c>
       <c r="B54" s="7" t="s">
         <v>123</v>
@@ -7145,8 +7133,8 @@
       </c>
     </row>
     <row r="55" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A55" s="19">
-        <v>171</v>
+      <c r="A55" s="10">
+        <v>4</v>
       </c>
       <c r="B55" s="7" t="s">
         <v>123</v>
@@ -7237,8 +7225,8 @@
       </c>
     </row>
     <row r="56" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A56" s="19">
-        <v>183</v>
+      <c r="A56" s="10">
+        <v>4</v>
       </c>
       <c r="B56" s="7" t="s">
         <v>123</v>
@@ -7331,8 +7319,8 @@
       </c>
     </row>
     <row r="57" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A57" s="19">
-        <v>183</v>
+      <c r="A57" s="10">
+        <v>4</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>123</v>
@@ -7425,8 +7413,8 @@
       </c>
     </row>
     <row r="58" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A58" s="19">
-        <v>183</v>
+      <c r="A58" s="10">
+        <v>4</v>
       </c>
       <c r="B58" s="7" t="s">
         <v>123</v>
@@ -7517,8 +7505,8 @@
       </c>
     </row>
     <row r="59" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A59" s="19">
-        <v>188</v>
+      <c r="A59" s="10">
+        <v>4</v>
       </c>
       <c r="B59" s="7" t="s">
         <v>123</v>
@@ -7609,8 +7597,8 @@
       </c>
     </row>
     <row r="60" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A60" s="19">
-        <v>189</v>
+      <c r="A60" s="10">
+        <v>4</v>
       </c>
       <c r="B60" s="7" t="s">
         <v>123</v>
@@ -7703,8 +7691,8 @@
       </c>
     </row>
     <row r="61" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A61" s="19">
-        <v>192</v>
+      <c r="A61" s="10">
+        <v>4</v>
       </c>
       <c r="B61" s="7" t="s">
         <v>123</v>
@@ -7797,8 +7785,8 @@
       </c>
     </row>
     <row r="62" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A62" s="19">
-        <v>193</v>
+      <c r="A62" s="10">
+        <v>4</v>
       </c>
       <c r="B62" s="7" t="s">
         <v>123</v>
@@ -7891,8 +7879,8 @@
       </c>
     </row>
     <row r="63" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A63" s="19">
-        <v>193</v>
+      <c r="A63" s="10">
+        <v>4</v>
       </c>
       <c r="B63" s="7" t="s">
         <v>123</v>
@@ -7983,8 +7971,8 @@
       </c>
     </row>
     <row r="64" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A64" s="19">
-        <v>193</v>
+      <c r="A64" s="10">
+        <v>4</v>
       </c>
       <c r="B64" s="7" t="s">
         <v>123</v>
@@ -8077,8 +8065,8 @@
       </c>
     </row>
     <row r="65" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A65" s="19">
-        <v>193</v>
+      <c r="A65" s="10">
+        <v>4</v>
       </c>
       <c r="B65" s="7" t="s">
         <v>123</v>
@@ -8171,8 +8159,8 @@
       </c>
     </row>
     <row r="66" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A66" s="19">
-        <v>199</v>
+      <c r="A66" s="10">
+        <v>4</v>
       </c>
       <c r="B66" s="7" t="s">
         <v>123</v>
@@ -8263,8 +8251,8 @@
       </c>
     </row>
     <row r="67" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A67" s="19">
-        <v>201</v>
+      <c r="A67" s="10">
+        <v>4</v>
       </c>
       <c r="B67" s="7" t="s">
         <v>123</v>
@@ -8355,8 +8343,8 @@
       </c>
     </row>
     <row r="68" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A68" s="19">
-        <v>201</v>
+      <c r="A68" s="10">
+        <v>4</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>123</v>
@@ -8449,8 +8437,8 @@
       </c>
     </row>
     <row r="69" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A69" s="19">
-        <v>207</v>
+      <c r="A69" s="10">
+        <v>4</v>
       </c>
       <c r="B69" s="7" t="s">
         <v>123</v>
@@ -8543,8 +8531,8 @@
       </c>
     </row>
     <row r="70" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A70" s="19">
-        <v>207</v>
+      <c r="A70" s="10">
+        <v>4</v>
       </c>
       <c r="B70" s="7" t="s">
         <v>123</v>
@@ -8635,8 +8623,8 @@
       </c>
     </row>
     <row r="71" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A71" s="19">
-        <v>207</v>
+      <c r="A71" s="10">
+        <v>4</v>
       </c>
       <c r="B71" s="7" t="s">
         <v>123</v>
@@ -8729,8 +8717,8 @@
       </c>
     </row>
     <row r="72" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A72" s="19">
-        <v>207</v>
+      <c r="A72" s="10">
+        <v>3</v>
       </c>
       <c r="B72" s="7" t="s">
         <v>124</v>
@@ -8823,8 +8811,8 @@
       </c>
     </row>
     <row r="73" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A73" s="19">
-        <v>208</v>
+      <c r="A73" s="10">
+        <v>3</v>
       </c>
       <c r="B73" s="7" t="s">
         <v>124</v>
@@ -8917,8 +8905,8 @@
       </c>
     </row>
     <row r="74" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A74" s="19">
-        <v>208</v>
+      <c r="A74" s="10">
+        <v>3</v>
       </c>
       <c r="B74" s="7" t="s">
         <v>124</v>
@@ -9011,8 +8999,8 @@
       </c>
     </row>
     <row r="75" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A75" s="19">
-        <v>208</v>
+      <c r="A75" s="10">
+        <v>3</v>
       </c>
       <c r="B75" s="7" t="s">
         <v>124</v>
@@ -9105,8 +9093,8 @@
       </c>
     </row>
     <row r="76" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A76" s="19">
-        <v>208</v>
+      <c r="A76" s="10">
+        <v>3</v>
       </c>
       <c r="B76" s="7" t="s">
         <v>124</v>
@@ -9199,8 +9187,8 @@
       </c>
     </row>
     <row r="77" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A77" s="19">
-        <v>208</v>
+      <c r="A77" s="10">
+        <v>3</v>
       </c>
       <c r="B77" s="7" t="s">
         <v>124</v>
@@ -9293,8 +9281,8 @@
       </c>
     </row>
     <row r="78" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A78" s="19">
-        <v>208</v>
+      <c r="A78" s="10">
+        <v>3</v>
       </c>
       <c r="B78" s="7" t="s">
         <v>124</v>
@@ -9387,8 +9375,8 @@
       </c>
     </row>
     <row r="79" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A79" s="19">
-        <v>208</v>
+      <c r="A79" s="10">
+        <v>3</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>124</v>
@@ -9481,8 +9469,8 @@
       </c>
     </row>
     <row r="80" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A80" s="19">
-        <v>212</v>
+      <c r="A80" s="10">
+        <v>3</v>
       </c>
       <c r="B80" s="7" t="s">
         <v>124</v>
@@ -9573,8 +9561,8 @@
       </c>
     </row>
     <row r="81" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A81" s="19">
-        <v>212</v>
+      <c r="A81" s="10">
+        <v>3</v>
       </c>
       <c r="B81" s="7" t="s">
         <v>124</v>
@@ -9667,8 +9655,8 @@
       </c>
     </row>
     <row r="82" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A82" s="19">
-        <v>212</v>
+      <c r="A82" s="10">
+        <v>3</v>
       </c>
       <c r="B82" s="7" t="s">
         <v>124</v>
@@ -9761,8 +9749,8 @@
       </c>
     </row>
     <row r="83" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A83" s="19">
-        <v>212</v>
+      <c r="A83" s="10">
+        <v>3</v>
       </c>
       <c r="B83" s="7" t="s">
         <v>124</v>
@@ -9853,8 +9841,8 @@
       </c>
     </row>
     <row r="84" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A84" s="19">
-        <v>225</v>
+      <c r="A84" s="10">
+        <v>3</v>
       </c>
       <c r="B84" s="7" t="s">
         <v>124</v>
@@ -9947,8 +9935,8 @@
       </c>
     </row>
     <row r="85" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A85" s="19">
-        <v>225</v>
+      <c r="A85" s="10">
+        <v>3</v>
       </c>
       <c r="B85" s="7" t="s">
         <v>124</v>
@@ -10039,8 +10027,8 @@
       </c>
     </row>
     <row r="86" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A86" s="19">
-        <v>233</v>
+      <c r="A86" s="10">
+        <v>3</v>
       </c>
       <c r="B86" s="7" t="s">
         <v>124</v>
@@ -10131,8 +10119,8 @@
       </c>
     </row>
     <row r="87" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A87" s="19">
-        <v>233</v>
+      <c r="A87" s="10">
+        <v>3</v>
       </c>
       <c r="B87" s="7" t="s">
         <v>124</v>
@@ -10223,8 +10211,8 @@
       </c>
     </row>
     <row r="88" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A88" s="19">
-        <v>233</v>
+      <c r="A88" s="10">
+        <v>3</v>
       </c>
       <c r="B88" s="7" t="s">
         <v>124</v>
@@ -10317,8 +10305,8 @@
       </c>
     </row>
     <row r="89" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A89" s="19">
-        <v>240</v>
+      <c r="A89" s="10">
+        <v>3</v>
       </c>
       <c r="B89" s="7" t="s">
         <v>124</v>
@@ -10411,8 +10399,8 @@
       </c>
     </row>
     <row r="90" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A90" s="19">
-        <v>240</v>
+      <c r="A90" s="10">
+        <v>3</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>124</v>
@@ -10505,8 +10493,8 @@
       </c>
     </row>
     <row r="91" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A91" s="19">
-        <v>243</v>
+      <c r="A91" s="10">
+        <v>3</v>
       </c>
       <c r="B91" s="7" t="s">
         <v>124</v>
@@ -10597,8 +10585,8 @@
       </c>
     </row>
     <row r="92" spans="1:27" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A92" s="19">
-        <v>243</v>
+      <c r="A92" s="10">
+        <v>3</v>
       </c>
       <c r="B92" s="7" t="s">
         <v>124</v>
@@ -10689,8 +10677,8 @@
       </c>
     </row>
     <row r="93" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A93" s="19">
-        <v>243</v>
+      <c r="A93" s="10">
+        <v>3</v>
       </c>
       <c r="B93" s="7" t="s">
         <v>124</v>
@@ -10782,76 +10770,8 @@
         <v>• NR 35 - TRABALHO EM ALTURA - EM DIA – vence em 04/10/26</v>
       </c>
     </row>
-    <row r="94" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A94" s="19">
-        <v>243</v>
-      </c>
-      <c r="B94" s="7"/>
-      <c r="C94" s="8"/>
-      <c r="D94" s="7"/>
-      <c r="E94" s="6"/>
-      <c r="F94" s="7"/>
-      <c r="G94" s="7"/>
-      <c r="H94" s="7"/>
-      <c r="I94" s="6"/>
-      <c r="J94" s="6"/>
-      <c r="K94" s="7"/>
-      <c r="L94" s="6"/>
-      <c r="M94" s="7"/>
-      <c r="N94" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="O94" s="9"/>
-      <c r="P94" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="Q94" s="10">
-        <v>1</v>
-      </c>
-      <c r="R94" s="10">
-        <v>3</v>
-      </c>
-      <c r="S94" s="10">
-        <v>102</v>
-      </c>
-      <c r="T94" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="U94" s="11">
-        <v>45489</v>
-      </c>
-      <c r="V94" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="W94" s="10"/>
-      <c r="X94" s="14" t="str">
-        <f ca="1">IF(Tabela1[[#This Row],[DATA_CURSO]]="",
-"PENDENTE",
-IF(Tabela1[[#This Row],[TIPO_RENOVACAO]]="QUANDO NECESSARIO",
-"EM DIA – não é necessário renovar",
-IFERROR(
-IF(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0))&lt;TODAY(),
-"VENCIDO – "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa"),
-"EM DIA – vence em "&amp;TEXT(SUM(Tabela1[[#This Row],[DATA_CURSO]],VLOOKUP(Tabela1[[#This Row],[DESCRICAO]],RENOVAÇÃO!A:C,3,0)),"dd/mm/aa")),
-"NÃO É NECESSÁRIO RENOVAR")))</f>
-        <v>EM DIA – não é necessário renovar</v>
-      </c>
-      <c r="Y94" s="12" t="str">
-        <f>IF(Tabela1[[#This Row],[FILIAL]]=1,"SINOP",IF(Tabela1[[#This Row],[FILIAL]]=2,"DOURADOS",IF(Tabela1[[#This Row],[FILIAL]]=3,"NOVA MUTUM",IF(Tabela1[[#This Row],[FILIAL]]=4,"FULLING",IF(Tabela1[[#This Row],[FILIAL]]=5,"SÃO PAULO",IF(Tabela1[[#This Row],[FILIAL]]=6,"SIDROLÂNDIA",IF(Tabela1[[#This Row],[FILIAL]]=8,"BALSAS",IF(Tabela1[[#This Row],[FILIAL]]=10,"LUIS EDUARDO MAGALHÃES",""))))))))</f>
-        <v>NOVA MUTUM</v>
-      </c>
-      <c r="Z94" s="15" t="str">
-        <f>VLOOKUP(N94,RENOVAÇÃO!A:D,4,0)</f>
-        <v>TRILHA SEGURANÇA DO TRABALHO</v>
-      </c>
-      <c r="AA94" s="16" t="str">
-        <f ca="1">CONCATENATE("• ",
-    Tabela1[[#This Row],[DESCRICAO]], " - ",Tabela1[[#This Row],[STATUS_GERAL]])</f>
-        <v>• NR 26 - SINALIZAÇÃO DE SEGURANÇA - EM DIA – não é necessário renovar</v>
-      </c>
-    </row>
   </sheetData>
-  <phoneticPr fontId="9" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
